--- a/latest/season_plan_spond.xlsx
+++ b/latest/season_plan_spond.xlsx
@@ -1274,47 +1274,47 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>31.10.2026</t>
+          <t>01.11.2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>JU12 Turnering — Skien ishall</t>
+          <t>U11 Turnering — Holmen ishall</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Holmen ishall</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Skien, Frisk Asker, Ringerike, Kongsberg/Tønsberg</t>
+          <t>Holmen, Jar, Frisk Asker, Tønsberg</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Skien, Frisk Asker Orange, Ringerike 2, Kongsberg/Tønsberg</t>
+          <t>Holmen Hockey Hvit, Jar Gul, Frisk Asker 4, Jar Blå, Tønsberg Hvit, Frisk Asker 1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1331,42 +1331,42 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>U11 Turnering — Holmen ishall</t>
+          <t>U8 Turnering — Bugården ishall</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Holmen ishall</t>
+          <t>Bugården ishall</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U8</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Sandefjord Penguins</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Holmen, Jar, Frisk Asker, Tønsberg</t>
+          <t>Sandefjord Penguins, Frisk Asker, Holmen, Jar, Jutul, Ringerike</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Holmen Hockey Hvit, Jar Gul, Frisk Asker 4, Jar Blå, Tønsberg Hvit, Frisk Asker 1</t>
+          <t>Sandefjord, Frisk Asker 5, Holmen Hockey Rød, Jar Rød, Jutul Hvit, Jutul Gul, Ringerike 2, Holmen Hockey Hvit</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1383,42 +1383,42 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>U8 Turnering — Bugården ishall</t>
+          <t>U9 Turnering — Skien ishall</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bugården ishall</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>U9</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins, Frisk Asker, Holmen, Jar, Jutul, Ringerike</t>
+          <t>Skien, Frisk Asker, Holmen, Jar, Jutul, Tønsberg, Kongsberg</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Sandefjord, Frisk Asker 5, Holmen Hockey Rød, Jar Rød, Jutul Hvit, Jutul Gul, Ringerike 2, Holmen Hockey Hvit</t>
+          <t>Skien, Frisk Asker 3, Holmen Hockey Hvit, Jar Hvit, Jutul Rød, Frisk Asker 4, Tønsberg, Kongsberg</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1435,42 +1435,42 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>U9 Turnering — Skien ishall</t>
+          <t>U12 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Skien, Frisk Asker, Holmen, Jar, Jutul, Tønsberg, Kongsberg</t>
+          <t>Ringerike, Jar, Tønsberg, Frisk Asker</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Skien, Frisk Asker 3, Holmen Hockey Hvit, Jar Hvit, Jutul Rød, Frisk Asker 4, Tønsberg, Kongsberg</t>
+          <t>Ringerike 1, Jar Blå, Tønsberg Hvit, Frisk Asker 2</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1482,12 +1482,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>01.11.2026</t>
+          <t>07.11.2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>U12 Turnering — Askerhallen</t>
+          <t>U10 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1497,17 +1497,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1517,12 +1517,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Ringerike, Jar, Tønsberg, Frisk Asker</t>
+          <t>Frisk Asker, Jar, Holmen, Ringerike, Jutul</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Ringerike 1, Jar Blå, Tønsberg Hvit, Frisk Asker 2</t>
+          <t>Frisk Asker 6, Jar Grønn, Holmen Hockey Rød, Ringerike 4, Jutul Grønn, Frisk Asker 3</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1539,42 +1539,42 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>U10 Turnering — Askerhallen</t>
+          <t>U11 Turnering — Holmen ishall</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Holmen ishall</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Holmen, Ringerike, Jutul</t>
+          <t>Ringerike, Tønsberg, Jar, Holmen, Frisk Asker, Jutul</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Frisk Asker 6, Jar Grønn, Holmen Hockey Rød, Ringerike 4, Jutul Grønn, Frisk Asker 3</t>
+          <t>Ringerike Svart, Tønsberg Hvit, Jar Svart, Holmen Hockey Rød, Frisk Asker 2, Jutul Grønn</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1591,42 +1591,42 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>U11 Turnering — Holmen ishall</t>
+          <t>JU8 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Holmen ishall</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>JU8</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Ringerike, Tønsberg, Jar, Holmen, Frisk Asker, Jutul</t>
+          <t>Frisk Asker, Jar, Jutul, Skien</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Ringerike Svart, Tønsberg Hvit, Jar Svart, Holmen Hockey Rød, Frisk Asker 2, Jutul Grønn</t>
+          <t>Frisk Asker, Jar, Jutul Kittens, Skien</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1643,42 +1643,42 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>JU8 Turnering — Baerum ishall</t>
+          <t>U12 Turnering — Schjongshallen</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Schjongshallen</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>JU8</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Jutul, Skien</t>
+          <t>Ringerike, Jar, Frisk Asker, Holmen</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Jutul Kittens, Skien</t>
+          <t>Ringerike 2, Jar Rød, Frisk Asker 3, Holmen Hockey Rød</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1690,12 +1690,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07.11.2026</t>
+          <t>08.11.2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>U12 Turnering — Schjongshallen</t>
+          <t>JU12 Turnering — Schjongshallen</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1705,17 +1705,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>JU12</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Ringerike, Jar, Frisk Asker, Holmen</t>
+          <t>Ringerike, Frisk Asker, Jutul</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Ringerike 2, Jar Rød, Frisk Asker 3, Holmen Hockey Rød</t>
+          <t>Ringerike 2, Frisk Asker Orange, Frisk Asker Svart, Jutul/Jar Kittens</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1747,42 +1747,42 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>JU12 Turnering — Schjongshallen</t>
+          <t>JU10 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Schjongshallen</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>JU10</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Ringerike, Frisk Asker, Jutul</t>
+          <t>Frisk Asker, Jar, Ringerike, Skien</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Ringerike 2, Frisk Asker Orange, Frisk Asker Svart, Jutul/Jar Kittens</t>
+          <t>Frisk Asker Orange, Frisk Asker Svart, Jar Rød, Ringerike 1, Skien, Jar Blå</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1799,42 +1799,42 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>JU10 Turnering — Askerhallen</t>
+          <t>U11 Turnering — Kongsberghallen</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Kongsberghallen</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>JU10</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Ringerike, Skien</t>
+          <t>Jar, Frisk Asker, Kongsberg, Tønsberg</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Frisk Asker Orange, Frisk Asker Svart, Jar Rød, Ringerike 1, Skien, Jar Blå</t>
+          <t>Jar Hvit, Frisk Asker 4, Jar Lilla, Kongsberg, Tønsberg Grå, Jar Oransje</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1851,42 +1851,42 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>U11 Turnering — Kongsberghallen</t>
+          <t>U10 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kongsberghallen</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Jar, Frisk Asker, Kongsberg, Tønsberg</t>
+          <t>Frisk Asker, Jar, Holmen, Ringerike, Tønsberg</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Jar Hvit, Frisk Asker 4, Jar Lilla, Kongsberg, Tønsberg Grå, Jar Oransje</t>
+          <t>Frisk Asker 2, Jar Rød, Holmen Hockey Rød, Holmen Hockey Blå, Ringerike 3, Tønsberg</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1903,42 +1903,42 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>U10 Turnering — Askerhallen</t>
+          <t>U12 Turnering — Schjongshallen</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Schjongshallen</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Holmen, Ringerike, Tønsberg</t>
+          <t>Ringerike, Jar, Kongsberg, Frisk Asker</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Frisk Asker 2, Jar Rød, Holmen Hockey Rød, Holmen Hockey Blå, Ringerike 3, Tønsberg</t>
+          <t>Ringerike 2, Jar Svart, Kongsberg, Frisk Asker 2</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -1950,47 +1950,47 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08.11.2026</t>
+          <t>14.11.2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>U12 Turnering — Schjongshallen</t>
+          <t>U10 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Schjongshallen</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Ringerike, Jar, Kongsberg, Frisk Asker</t>
+          <t>Frisk Asker, Jar, Holmen, Ringerike</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Ringerike 2, Jar Svart, Kongsberg, Frisk Asker 2</t>
+          <t>Frisk Asker 4, Jar Grønn, Holmen Hockey Hvit, Ringerike 3, Jar Gul, Frisk Asker 5</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2007,42 +2007,42 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>U10 Turnering — Askerhallen</t>
+          <t>U8 Turnering — Holmen ishall</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Holmen ishall</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U8</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Holmen, Ringerike</t>
+          <t>Holmen, Skien, Jar, Frisk Asker, Jutul, Ringerike</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Frisk Asker 4, Jar Grønn, Holmen Hockey Hvit, Ringerike 3, Jar Gul, Frisk Asker 5</t>
+          <t>Holmen Hockey Rød, Skien, Jar Svart, Frisk Asker 4, Frisk Asker 1, Jutul Rød, Ringerike 1, Jar Rød</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>U8 Turnering — Holmen ishall</t>
+          <t>U9 Turnering — Holmen ishall</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2069,17 +2069,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>U9</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2089,12 +2089,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Holmen, Skien, Jar, Frisk Asker, Jutul, Ringerike</t>
+          <t>Holmen, Jar, Frisk Asker, Skien, Jutul</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Holmen Hockey Rød, Skien, Jar Svart, Frisk Asker 4, Frisk Asker 1, Jutul Rød, Ringerike 1, Jar Rød</t>
+          <t>Holmen Hockey Rød, Holmen Hockey Sort, Jar Blå, Jar Hvit, Frisk Asker 4, Skien, Jutul Grønn, Frisk Asker 2</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2111,42 +2111,42 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>U9 Turnering — Holmen ishall</t>
+          <t>U10 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Holmen ishall</t>
+          <t>Jar Isforum</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Holmen, Jar, Frisk Asker, Skien, Jutul</t>
+          <t>Frisk Asker, Jar, Holmen, Ringerike, Jutul</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Holmen Hockey Rød, Holmen Hockey Sort, Jar Blå, Jar Hvit, Frisk Asker 4, Skien, Jutul Grønn, Frisk Asker 2</t>
+          <t>Frisk Asker 6, Jar Svart, Holmen Hockey Blå, Ringerike 2, Jutul Rød, Jar Rød</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2163,42 +2163,42 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>U10 Turnering — Jar Isforum</t>
+          <t>U11 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jar Isforum</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Holmen, Ringerike, Jutul</t>
+          <t>Jar, Kongsberg, Tønsberg, Sandefjord Penguins, Frisk Asker, Jutul</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Frisk Asker 6, Jar Svart, Holmen Hockey Blå, Ringerike 2, Jutul Rød, Jar Rød</t>
+          <t>Jar Blå, Kongsberg, Tønsberg Rød, Sandefjord, Frisk Asker 4, Jutul Rød</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2215,24 +2215,24 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>U11 Turnering — Baerum ishall</t>
+          <t>U11 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Jar Isforum</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
           <t>17:20</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>19:40</t>
-        </is>
-      </c>
       <c r="F35" t="inlineStr">
         <is>
           <t>U11</t>
@@ -2240,17 +2240,17 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Jar, Kongsberg, Tønsberg, Sandefjord Penguins, Frisk Asker, Jutul</t>
+          <t>Jar, Frisk Asker, Holmen, Ringerike</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Jar Blå, Kongsberg, Tønsberg Rød, Sandefjord, Frisk Asker 4, Jutul Rød</t>
+          <t>Jar Grønn, Jar Rød, Frisk Asker 1, Holmen Hockey Rød, Frisk Asker 2, Ringerike Gul</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2267,42 +2267,42 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>U11 Turnering — Jar Isforum</t>
+          <t>U12 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Jar Isforum</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Jar, Frisk Asker, Holmen, Ringerike</t>
+          <t>Frisk Asker, Jutul, Jar, Tønsberg</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Jar Grønn, Jar Rød, Frisk Asker 1, Holmen Hockey Rød, Frisk Asker 2, Ringerike Gul</t>
+          <t>Frisk Asker 1, Jutul Grønn, Jar Hvit, Tønsberg Rød</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2314,47 +2314,47 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>14.11.2026</t>
+          <t>15.11.2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>U12 Turnering — Askerhallen</t>
+          <t>JU12 Turnering — Skien ishall</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>JU12</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jutul, Jar, Tønsberg</t>
+          <t>Skien, Frisk Asker, Ringerike, Kongsberg/Tønsberg</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Frisk Asker 1, Jutul Grønn, Jar Hvit, Tønsberg Rød</t>
+          <t>Skien, Frisk Asker Svart, Ringerike 1, Kongsberg/Tønsberg</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2371,42 +2371,42 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>JU12 Turnering — Skien ishall</t>
+          <t>U12 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Jar Isforum</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Skien, Frisk Asker, Ringerike, Kongsberg/Tønsberg</t>
+          <t>Jar, Holmen, Ringerike, Frisk Asker</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Skien, Frisk Asker Svart, Ringerike 1, Kongsberg/Tønsberg</t>
+          <t>Jar Rød, Holmen Hockey Hvit, Ringerike 2, Frisk Asker 3</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2423,12 +2423,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>U12 Turnering — Jar Isforum</t>
+          <t>U12 Turnering — Tonsberghallen</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Jar Isforum</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2448,17 +2448,17 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Jar, Holmen, Ringerike, Frisk Asker</t>
+          <t>Tønsberg, Jar, Ringerike, Frisk Asker</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Jar Rød, Holmen Hockey Hvit, Ringerike 2, Frisk Asker 3</t>
+          <t>Tønsberg Grå, Jar Svart, Ringerike 1, Frisk Asker 2</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2475,22 +2475,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>U12 Turnering — Tonsberghallen</t>
+          <t>U12 Turnering — Kongsberghallen</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Kongsberghallen</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2500,17 +2500,17 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Tønsberg, Jar, Ringerike, Frisk Asker</t>
+          <t>Jar, Kongsberg, Tønsberg, Jutul</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Tønsberg Grå, Jar Svart, Ringerike 1, Frisk Asker 2</t>
+          <t>Jar Blå, Kongsberg, Tønsberg Hvit, Jutul Rød</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2527,12 +2527,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>U12 Turnering — Kongsberghallen</t>
+          <t>U10 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Kongsberghallen</t>
+          <t>Jar Isforum</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2542,27 +2542,27 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Jar, Kongsberg, Tønsberg, Jutul</t>
+          <t>Jar, Jutul, Holmen, Frisk Asker</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Jar Blå, Kongsberg, Tønsberg Hvit, Jutul Rød</t>
+          <t>Jar Blå, Jutul Grønn, Jutul Hvit, Holmen Hockey Blå, Jar Hvit, Frisk Asker 2</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2574,47 +2574,47 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>15.11.2026</t>
+          <t>21.11.2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>U10 Turnering — Jar Isforum</t>
+          <t>AVLYST: JU8 Turnering — Schjongshallen</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Jar Isforum</t>
+          <t>Schjongshallen</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>JU8</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Jar, Jutul, Holmen, Frisk Asker</t>
+          <t>Frisk Asker, Jar, Jutul, Ringerike, Skien</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Jar Blå, Jutul Grønn, Jutul Hvit, Holmen Hockey Blå, Jar Hvit, Frisk Asker 2</t>
+          <t>Frisk Asker, Jar, Jutul Kittens, Ringerike 1, Skien</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2631,42 +2631,42 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>AVLYST: JU8 Turnering — Schjongshallen</t>
+          <t>U10 Turnering — Holmen ishall</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Schjongshallen</t>
+          <t>Holmen ishall</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>JU8</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Jutul, Ringerike, Skien</t>
+          <t>Holmen, Frisk Asker, Jar, Jutul, Ringerike, Tønsberg</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Jutul Kittens, Ringerike 1, Skien</t>
+          <t>Holmen Hockey Hvit, Frisk Asker 1, Jar Rød, Jutul Rød, Ringerike 1, Tønsberg</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2683,42 +2683,42 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>U10 Turnering — Holmen ishall</t>
+          <t>U9 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Holmen ishall</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U9</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Holmen, Frisk Asker, Jar, Jutul, Ringerike, Tønsberg</t>
+          <t>Jutul, Holmen, Frisk Asker, Jar, Kongsberg, Tønsberg</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Holmen Hockey Hvit, Frisk Asker 1, Jar Rød, Jutul Rød, Ringerike 1, Tønsberg</t>
+          <t>Jutul Rød, Jutul Grønn, Holmen Hockey Sort, Frisk Asker 2, Jar Rød, Kongsberg, Frisk Asker 4, Tønsberg</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2735,42 +2735,42 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>U9 Turnering — Baerum ishall</t>
+          <t>JU12 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>JU12</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Jutul, Holmen, Frisk Asker, Jar, Kongsberg, Tønsberg</t>
+          <t>Frisk Asker, Ringerike, Jutul, Skien</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Jutul Rød, Jutul Grønn, Holmen Hockey Sort, Frisk Asker 2, Jar Rød, Kongsberg, Frisk Asker 4, Tønsberg</t>
+          <t>Frisk Asker Orange, Ringerike 2, Jutul/Jar Kittens, Skien</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2787,42 +2787,42 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>JU12 Turnering — Askerhallen</t>
+          <t>U11 Turnering — Schjongshallen</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Schjongshallen</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Frisk Asker, Ringerike, Jutul, Skien</t>
+          <t>Skien, Jar, Frisk Asker, Jutul, Ringerike</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Frisk Asker Orange, Ringerike 2, Jutul/Jar Kittens, Skien</t>
+          <t>Skien, Jar Oransje, Jar Rød, Frisk Asker 2, Jutul Grønn, Ringerike Svart</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2839,42 +2839,42 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>U11 Turnering — Schjongshallen</t>
+          <t>U8 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Schjongshallen</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U8</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Skien, Jar, Frisk Asker, Jutul, Ringerike</t>
+          <t>Frisk Asker, Holmen, Jutul, Kongsberg, Jar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Skien, Jar Oransje, Jar Rød, Frisk Asker 2, Jutul Grønn, Ringerike Svart</t>
+          <t>Frisk Asker 1, Frisk Asker 4, Holmen Hockey Hvit, Jutul Grønn, Jutul Hvit, Kongsberg, Jar Blå, Holmen Hockey Blå</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -2891,42 +2891,42 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>U8 Turnering — Askerhallen</t>
+          <t>U11 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Jar Isforum</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Frisk Asker, Holmen, Jutul, Kongsberg, Jar</t>
+          <t>Kongsberg, Jar, Frisk Asker, Jutul, Tønsberg</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Frisk Asker 1, Frisk Asker 4, Holmen Hockey Hvit, Jutul Grønn, Jutul Hvit, Kongsberg, Jar Blå, Holmen Hockey Blå</t>
+          <t>Kongsberg, Jar Hvit, Frisk Asker 4, Jutul Rød, Tønsberg Grå, Jar Blå</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2938,47 +2938,47 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>21.11.2026</t>
+          <t>22.11.2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>U11 Turnering — Jar Isforum</t>
+          <t>U10 Turnering — Schjongshallen</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Jar Isforum</t>
+          <t>Schjongshallen</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Kongsberg, Jar, Frisk Asker, Jutul, Tønsberg</t>
+          <t>Ringerike, Frisk Asker, Jar, Tønsberg, Holmen, Jutul</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Kongsberg, Jar Hvit, Frisk Asker 4, Jutul Rød, Tønsberg Grå, Jar Blå</t>
+          <t>Ringerike 2, Frisk Asker 2, Jar Grønn, Tønsberg, Holmen Hockey Hvit, Jutul Hvit</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3005,12 +3005,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Ringerike, Frisk Asker, Jar, Tønsberg, Holmen, Jutul</t>
+          <t>Kongsberg, Jar, Jutul, Frisk Asker, Ringerike</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Ringerike 2, Frisk Asker 2, Jar Grønn, Tønsberg, Holmen Hockey Hvit, Jutul Hvit</t>
+          <t>Kongsberg, Jar Gul, Jutul Grønn, Jar Blå, Frisk Asker 6, Ringerike 4</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3047,42 +3047,42 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>U10 Turnering — Schjongshallen</t>
+          <t>U12 Turnering — Holmen ishall</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Schjongshallen</t>
+          <t>Holmen ishall</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Kongsberg, Jar, Jutul, Frisk Asker, Ringerike</t>
+          <t>Frisk Asker, Tønsberg, Jar, Holmen</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Kongsberg, Jar Gul, Jutul Grønn, Jar Blå, Frisk Asker 6, Ringerike 4</t>
+          <t>Frisk Asker 1, Tønsberg Grå, Jar Hvit, Holmen Hockey Rød</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3099,42 +3099,42 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>U12 Turnering — Holmen ishall</t>
+          <t>U8 Turnering — Skien ishall</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Holmen ishall</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U8</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Frisk Asker, Tønsberg, Jar, Holmen</t>
+          <t>Skien, Jutul, Frisk Asker, Holmen, Jar, Sandefjord Penguins</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Frisk Asker 1, Tønsberg Grå, Jar Hvit, Holmen Hockey Rød</t>
+          <t>Skien, Jutul Grønn, Frisk Asker 4, Holmen Hockey Sort, Jar Hvit, Jar Blå, Frisk Asker 5, Sandefjord</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3151,42 +3151,42 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>U8 Turnering — Skien ishall</t>
+          <t>JU12 Turnering — Kongsberghallen</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Kongsberghallen</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>JU12</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Skien, Jutul, Frisk Asker, Holmen, Jar, Sandefjord Penguins</t>
+          <t>Kongsberg/Tønsberg, Frisk Asker, Ringerike</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Skien, Jutul Grønn, Frisk Asker 4, Holmen Hockey Sort, Jar Hvit, Jar Blå, Frisk Asker 5, Sandefjord</t>
+          <t>Kongsberg/Tønsberg, Frisk Asker Svart, Ringerike 1</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3203,42 +3203,42 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>JU12 Turnering — Kongsberghallen</t>
+          <t>U11 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Kongsberghallen</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Kongsberg/Tønsberg, Frisk Asker, Ringerike</t>
+          <t>Jar, Frisk Asker, Holmen, Jutul</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Kongsberg/Tønsberg, Frisk Asker Svart, Ringerike 1</t>
+          <t>Jar Blå, Frisk Asker 1, Frisk Asker 2, Holmen Hockey Hvit, Jutul Grønn, Jar Oransje</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3255,42 +3255,42 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>U11 Turnering — Askerhallen</t>
+          <t>U9 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Jar Isforum</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U9</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Jar, Frisk Asker, Holmen, Jutul</t>
+          <t>Jutul, Frisk Asker, Holmen, Jar</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Jar Blå, Frisk Asker 1, Frisk Asker 2, Holmen Hockey Hvit, Jutul Grønn, Jar Oransje</t>
+          <t>Jutul Grønn, Jutul Hvit, Frisk Asker 1, Holmen Hockey Hvit, Jar Rød, Frisk Asker 2, Holmen Hockey Sort, Jar Blå</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3302,47 +3302,47 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>22.11.2026</t>
+          <t>28.11.2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>U9 Turnering — Jar Isforum</t>
+          <t>U12 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Jar Isforum</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Jutul, Frisk Asker, Holmen, Jar</t>
+          <t>Ringerike, Jar, Tønsberg, Jutul</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Jutul Grønn, Jutul Hvit, Frisk Asker 1, Holmen Hockey Hvit, Jar Rød, Frisk Asker 2, Holmen Hockey Sort, Jar Blå</t>
+          <t>Ringerike 2, Jar Rød, Tønsberg Rød, Jutul Rød</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>U12 Turnering — Baerum ishall</t>
+          <t>U10 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3369,17 +3369,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
           <t>18:20</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3389,12 +3389,12 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Ringerike, Jar, Tønsberg, Jutul</t>
+          <t>Jutul, Jar, Holmen, Ringerike, Frisk Asker</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Ringerike 2, Jar Rød, Tønsberg Rød, Jutul Rød</t>
+          <t>Jutul Hvit, Jar Blå, Holmen Hockey Sort, Ringerike 1, Jar Svart, Frisk Asker 1</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3411,42 +3411,42 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>U10 Turnering — Baerum ishall</t>
+          <t>JU12 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>JU12</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Jutul, Jar, Holmen, Ringerike, Frisk Asker</t>
+          <t>Frisk Asker, Ringerike, Jutul, Skien</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Jutul Hvit, Jar Blå, Holmen Hockey Sort, Ringerike 1, Jar Svart, Frisk Asker 1</t>
+          <t>Frisk Asker Orange, Ringerike 1, Jutul/Jar Kittens, Skien</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3463,7 +3463,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>JU12 Turnering — Askerhallen</t>
+          <t>U11 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3473,17 +3473,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Frisk Asker, Ringerike, Jutul, Skien</t>
+          <t>Frisk Asker, Jar, Ringerike, Tønsberg, Holmen</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Frisk Asker Orange, Ringerike 1, Jutul/Jar Kittens, Skien</t>
+          <t>Frisk Asker 4, Jar Grønn, Ringerike Svart, Tønsberg Rød, Holmen Hockey Hvit, Jar Rød</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -3515,42 +3515,42 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>U11 Turnering — Askerhallen</t>
+          <t>U12 Turnering — Tonsberghallen</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Ringerike, Tønsberg, Holmen</t>
+          <t>Jar, Tønsberg, Frisk Asker, Jutul</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Frisk Asker 4, Jar Grønn, Ringerike Svart, Tønsberg Rød, Holmen Hockey Hvit, Jar Rød</t>
+          <t>Jar Svart, Tønsberg Hvit, Frisk Asker 1, Jutul Grønn</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -3567,42 +3567,42 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>U12 Turnering — Tonsberghallen</t>
+          <t>U11 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Jar Isforum</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Jar, Tønsberg, Frisk Asker, Jutul</t>
+          <t>Jar, Frisk Asker, Kongsberg, Jutul</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Jar Svart, Tønsberg Hvit, Frisk Asker 1, Jutul Grønn</t>
+          <t>Jar Gul, Jar Hvit, Jar Svart, Frisk Asker 1, Kongsberg, Jutul Rød</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -3614,22 +3614,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>28.11.2026</t>
+          <t>29.11.2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>U11 Turnering — Jar Isforum</t>
+          <t>JU8 Turnering — Skien ishall</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Jar Isforum</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3639,22 +3639,22 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>JU8</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Jar, Frisk Asker, Kongsberg, Jutul</t>
+          <t>Frisk Asker, Jar, Jutul, Skien</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Jar Gul, Jar Hvit, Jar Svart, Frisk Asker 1, Kongsberg, Jutul Rød</t>
+          <t>Frisk Asker, Jar, Jutul Kittens, Skien</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -3671,42 +3671,42 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>JU8 Turnering — Skien ishall</t>
+          <t>JU12 Turnering — Schjongshallen</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Schjongshallen</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>JU8</t>
+          <t>JU12</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Jutul, Skien</t>
+          <t>Ringerike, Frisk Asker, Jutul, Kongsberg/Tønsberg</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Jutul Kittens, Skien</t>
+          <t>Ringerike 2, Frisk Asker Svart, Jutul/Jar Kittens, Kongsberg/Tønsberg</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -3723,42 +3723,42 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>JU12 Turnering — Schjongshallen</t>
+          <t>U12 Turnering — Holmen ishall</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Schjongshallen</t>
+          <t>Holmen ishall</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Ringerike, Frisk Asker, Jutul, Kongsberg/Tønsberg</t>
+          <t>Holmen, Kongsberg, Frisk Asker, Tønsberg</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Ringerike 2, Frisk Asker Svart, Jutul/Jar Kittens, Kongsberg/Tønsberg</t>
+          <t>Holmen Hockey Hvit, Kongsberg, Frisk Asker 2, Tønsberg Grå</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -3775,42 +3775,42 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>U12 Turnering — Holmen ishall</t>
+          <t>U8 Turnering — Schjongshallen</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Holmen ishall</t>
+          <t>Schjongshallen</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U8</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Holmen, Kongsberg, Frisk Asker, Tønsberg</t>
+          <t>Ringerike, Sandefjord Penguins, Jar, Frisk Asker, Jutul, Holmen</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Holmen Hockey Hvit, Kongsberg, Frisk Asker 2, Tønsberg Grå</t>
+          <t>Ringerike 1, Sandefjord, Jar Rød, Frisk Asker 3, Jutul Hvit, Frisk Asker 4, Holmen Hockey Blå, Jar Hvit</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -3827,42 +3827,42 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>U8 Turnering — Schjongshallen</t>
+          <t>U11 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Schjongshallen</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Ringerike, Sandefjord Penguins, Jar, Frisk Asker, Jutul, Holmen</t>
+          <t>Jar, Frisk Asker, Sandefjord Penguins, Ringerike, Skien</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Ringerike 1, Sandefjord, Jar Rød, Frisk Asker 3, Jutul Hvit, Frisk Asker 4, Holmen Hockey Blå, Jar Hvit</t>
+          <t>Jar Gul, Jar Oransje, Frisk Asker 3, Sandefjord, Ringerike Svart, Skien</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -3879,42 +3879,42 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>U11 Turnering — Askerhallen</t>
+          <t>U12 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Jar Isforum</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Jar, Frisk Asker, Sandefjord Penguins, Ringerike, Skien</t>
+          <t>Jar, Frisk Asker, Holmen</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Jar Gul, Jar Oransje, Frisk Asker 3, Sandefjord, Ringerike Svart, Skien</t>
+          <t>Jar Blå, Frisk Asker 3, Holmen Hockey Rød, Jar Hvit</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -3926,12 +3926,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>29.11.2026</t>
+          <t>05.12.2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>U12 Turnering — Jar Isforum</t>
+          <t>JU10 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3941,17 +3941,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>JU10</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Jar, Frisk Asker, Holmen</t>
+          <t>Jar, Frisk Asker, Ringerike, Skien</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Jar Blå, Frisk Asker 3, Holmen Hockey Rød, Jar Hvit</t>
+          <t>Jar Hvit, Jar Rød, Jar Blå, Frisk Asker Orange, Ringerike 1, Skien</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -3978,47 +3978,47 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>05.12.2026</t>
+          <t>06.12.2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>JU10 Turnering — Jar Isforum</t>
+          <t>U8 Turnering — Tonsberghallen</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Jar Isforum</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>JU10</t>
+          <t>U8</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Jar, Frisk Asker, Ringerike, Skien</t>
+          <t>Tønsberg, Frisk Asker, Holmen, Jar, Jutul, Kongsberg</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Jar Hvit, Jar Rød, Jar Blå, Frisk Asker Orange, Ringerike 1, Skien</t>
+          <t>Tønsberg, Frisk Asker 3, Holmen Hockey Rød, Jar Svart, Jutul Gul, Holmen Hockey Sort, Frisk Asker 5, Kongsberg</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4030,27 +4030,27 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>06.12.2026</t>
+          <t>12.12.2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>U8 Turnering — Tonsberghallen</t>
+          <t>U8 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -4060,17 +4060,17 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Tønsberg, Frisk Asker, Holmen, Jar, Jutul, Kongsberg</t>
+          <t>Jutul, Frisk Asker, Holmen, Tønsberg, Ringerike, Jar</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Tønsberg, Frisk Asker 3, Holmen Hockey Rød, Jar Svart, Jutul Gul, Holmen Hockey Sort, Frisk Asker 5, Kongsberg</t>
+          <t>Jutul Hvit, Jutul Grønn, Frisk Asker 1, Holmen Hockey Hvit, Tønsberg, Ringerike 1, Frisk Asker 3, Jar Blå</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4087,42 +4087,42 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>U8 Turnering — Baerum ishall</t>
+          <t>JU12 Turnering — Skien ishall</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>JU12</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Jutul, Frisk Asker, Holmen, Tønsberg, Ringerike, Jar</t>
+          <t>Skien, Frisk Asker, Ringerike, Kongsberg/Tønsberg</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Jutul Hvit, Jutul Grønn, Frisk Asker 1, Holmen Hockey Hvit, Tønsberg, Ringerike 1, Frisk Asker 3, Jar Blå</t>
+          <t>Skien, Frisk Asker Orange, Ringerike 2, Kongsberg/Tønsberg</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">

--- a/latest/season_plan_spond.xlsx
+++ b/latest/season_plan_spond.xlsx
@@ -1222,47 +1222,47 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>31.10.2026</t>
+          <t>01.11.2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>U9 Turnering — Bugården ishall</t>
+          <t>U11 Turnering — Holmen ishall</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bugården ishall</t>
+          <t>Holmen ishall</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins, Frisk Asker, Skien, Holmen, Kongsberg, Ringerike, Tønsberg</t>
+          <t>Holmen, Jar, Frisk Asker, Tønsberg</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Sandefjord, Frisk Asker 3, Frisk Asker 1, Skien, Holmen Hockey Sort, Kongsberg, Ringerike 1, Tønsberg</t>
+          <t>Holmen Hockey Hvit, Jar Gul, Frisk Asker 4, Jar Blå, Tønsberg Hvit, Frisk Asker 1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1279,42 +1279,42 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>U11 Turnering — Holmen ishall</t>
+          <t>U8 Turnering — Bugården ishall</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Holmen ishall</t>
+          <t>Bugården ishall</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U8</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Sandefjord Penguins</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Holmen, Jar, Frisk Asker, Tønsberg</t>
+          <t>Sandefjord Penguins, Frisk Asker, Holmen, Jar, Jutul, Ringerike</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Holmen Hockey Hvit, Jar Gul, Frisk Asker 4, Jar Blå, Tønsberg Hvit, Frisk Asker 1</t>
+          <t>Sandefjord, Frisk Asker 5, Holmen Hockey Rød, Jar Rød, Jutul Hvit, Jutul Gul, Ringerike 2, Holmen Hockey Hvit</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1331,42 +1331,42 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>U8 Turnering — Bugården ishall</t>
+          <t>U9 Turnering — Skien ishall</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bugården ishall</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>U9</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins, Frisk Asker, Holmen, Jar, Jutul, Ringerike</t>
+          <t>Skien, Frisk Asker, Holmen, Jar, Jutul, Tønsberg, Kongsberg</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Sandefjord, Frisk Asker 5, Holmen Hockey Rød, Jar Rød, Jutul Hvit, Jutul Gul, Ringerike 2, Holmen Hockey Hvit</t>
+          <t>Skien, Frisk Asker 3, Holmen Hockey Hvit, Jar Hvit, Jutul Rød, Frisk Asker 4, Tønsberg, Kongsberg</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1383,42 +1383,42 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>U9 Turnering — Skien ishall</t>
+          <t>U12 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Skien, Frisk Asker, Holmen, Jar, Jutul, Tønsberg, Kongsberg</t>
+          <t>Ringerike, Jar, Tønsberg, Frisk Asker</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Skien, Frisk Asker 3, Holmen Hockey Hvit, Jar Hvit, Jutul Rød, Frisk Asker 4, Tønsberg, Kongsberg</t>
+          <t>Ringerike 1, Jar Blå, Tønsberg Hvit, Frisk Asker 2</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1430,12 +1430,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>01.11.2026</t>
+          <t>07.11.2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>U12 Turnering — Askerhallen</t>
+          <t>U10 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1445,17 +1445,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Ringerike, Jar, Tønsberg, Frisk Asker</t>
+          <t>Frisk Asker, Jar, Holmen, Ringerike, Jutul</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Ringerike 1, Jar Blå, Tønsberg Hvit, Frisk Asker 2</t>
+          <t>Frisk Asker 6, Jar Grønn, Holmen Hockey Rød, Ringerike 4, Jutul Grønn, Frisk Asker 3</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1487,42 +1487,42 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>U10 Turnering — Askerhallen</t>
+          <t>U11 Turnering — Holmen ishall</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Holmen ishall</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Holmen, Ringerike, Jutul</t>
+          <t>Ringerike, Tønsberg, Jar, Holmen, Frisk Asker, Jutul</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Frisk Asker 6, Jar Grønn, Holmen Hockey Rød, Ringerike 4, Jutul Grønn, Frisk Asker 3</t>
+          <t>Ringerike Svart, Tønsberg Hvit, Jar Svart, Holmen Hockey Rød, Frisk Asker 2, Jutul Grønn</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1539,42 +1539,42 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>U11 Turnering — Holmen ishall</t>
+          <t>JU8 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Holmen ishall</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>JU8</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Ringerike, Tønsberg, Jar, Holmen, Frisk Asker, Jutul</t>
+          <t>Frisk Asker, Jar, Jutul, Skien</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Ringerike Svart, Tønsberg Hvit, Jar Svart, Holmen Hockey Rød, Frisk Asker 2, Jutul Grønn</t>
+          <t>Frisk Asker, Jar, Jutul Kittens, Skien</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1591,42 +1591,42 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>JU8 Turnering — Baerum ishall</t>
+          <t>U12 Turnering — Schjongshallen</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Schjongshallen</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>JU8</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Jutul, Skien</t>
+          <t>Ringerike, Jar, Frisk Asker, Holmen</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Jutul Kittens, Skien</t>
+          <t>Ringerike 2, Jar Rød, Frisk Asker 3, Holmen Hockey Rød</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1638,12 +1638,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07.11.2026</t>
+          <t>08.11.2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>U12 Turnering — Schjongshallen</t>
+          <t>JU12 Turnering — Schjongshallen</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1653,17 +1653,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>JU12</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Ringerike, Jar, Frisk Asker, Holmen</t>
+          <t>Ringerike, Frisk Asker, Jutul</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Ringerike 2, Jar Rød, Frisk Asker 3, Holmen Hockey Rød</t>
+          <t>Ringerike 2, Frisk Asker Orange, Frisk Asker Svart, Jutul/Jar Kittens</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1695,42 +1695,42 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>JU12 Turnering — Schjongshallen</t>
+          <t>JU10 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Schjongshallen</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>JU10</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Ringerike, Frisk Asker, Jutul</t>
+          <t>Frisk Asker, Jar, Ringerike, Skien</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Ringerike 2, Frisk Asker Orange, Frisk Asker Svart, Jutul/Jar Kittens</t>
+          <t>Frisk Asker Orange, Frisk Asker Svart, Jar Rød, Ringerike 1, Skien, Jar Blå</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1747,42 +1747,42 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>JU10 Turnering — Askerhallen</t>
+          <t>U11 Turnering — Kongsberghallen</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Kongsberghallen</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>JU10</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Ringerike, Skien</t>
+          <t>Jar, Frisk Asker, Kongsberg, Tønsberg</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Frisk Asker Orange, Frisk Asker Svart, Jar Rød, Ringerike 1, Skien, Jar Blå</t>
+          <t>Jar Hvit, Frisk Asker 4, Jar Lilla, Kongsberg, Tønsberg Grå, Jar Oransje</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1799,42 +1799,42 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>U11 Turnering — Kongsberghallen</t>
+          <t>U10 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kongsberghallen</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Jar, Frisk Asker, Kongsberg, Tønsberg</t>
+          <t>Frisk Asker, Jar, Holmen, Ringerike, Tønsberg</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Jar Hvit, Frisk Asker 4, Jar Lilla, Kongsberg, Tønsberg Grå, Jar Oransje</t>
+          <t>Frisk Asker 2, Jar Rød, Holmen Hockey Rød, Holmen Hockey Blå, Ringerike 3, Tønsberg</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1851,42 +1851,42 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>U10 Turnering — Askerhallen</t>
+          <t>U12 Turnering — Schjongshallen</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Schjongshallen</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Holmen, Ringerike, Tønsberg</t>
+          <t>Ringerike, Jar, Kongsberg, Frisk Asker</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Frisk Asker 2, Jar Rød, Holmen Hockey Rød, Holmen Hockey Blå, Ringerike 3, Tønsberg</t>
+          <t>Ringerike 2, Jar Svart, Kongsberg, Frisk Asker 2</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1898,47 +1898,47 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08.11.2026</t>
+          <t>14.11.2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>U12 Turnering — Schjongshallen</t>
+          <t>U10 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Schjongshallen</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Ringerike, Jar, Kongsberg, Frisk Asker</t>
+          <t>Frisk Asker, Jar, Holmen, Ringerike</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Ringerike 2, Jar Svart, Kongsberg, Frisk Asker 2</t>
+          <t>Frisk Asker 4, Jar Grønn, Holmen Hockey Hvit, Ringerike 3, Jar Gul, Frisk Asker 5</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -1955,42 +1955,42 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>U10 Turnering — Askerhallen</t>
+          <t>U8 Turnering — Holmen ishall</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Holmen ishall</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U8</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Holmen, Ringerike</t>
+          <t>Holmen, Skien, Jar, Frisk Asker, Jutul, Ringerike</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Frisk Asker 4, Jar Grønn, Holmen Hockey Hvit, Ringerike 3, Jar Gul, Frisk Asker 5</t>
+          <t>Holmen Hockey Rød, Skien, Jar Svart, Frisk Asker 4, Frisk Asker 1, Jutul Rød, Ringerike 1, Jar Rød</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>U8 Turnering — Holmen ishall</t>
+          <t>U9 Turnering — Holmen ishall</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2017,17 +2017,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>U9</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2037,12 +2037,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Holmen, Skien, Jar, Frisk Asker, Jutul, Ringerike</t>
+          <t>Holmen, Jar, Frisk Asker, Skien, Jutul</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Holmen Hockey Rød, Skien, Jar Svart, Frisk Asker 4, Frisk Asker 1, Jutul Rød, Ringerike 1, Jar Rød</t>
+          <t>Holmen Hockey Rød, Holmen Hockey Sort, Jar Blå, Jar Hvit, Frisk Asker 4, Skien, Jutul Grønn, Frisk Asker 2</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2059,42 +2059,42 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>U9 Turnering — Holmen ishall</t>
+          <t>U10 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Holmen ishall</t>
+          <t>Jar Isforum</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Holmen, Jar, Frisk Asker, Skien, Jutul</t>
+          <t>Frisk Asker, Jar, Holmen, Ringerike, Jutul</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Holmen Hockey Rød, Holmen Hockey Sort, Jar Blå, Jar Hvit, Frisk Asker 4, Skien, Jutul Grønn, Frisk Asker 2</t>
+          <t>Frisk Asker 6, Jar Svart, Holmen Hockey Blå, Ringerike 2, Jutul Rød, Jar Rød</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2111,42 +2111,42 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>U10 Turnering — Jar Isforum</t>
+          <t>U11 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Jar Isforum</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Holmen, Ringerike, Jutul</t>
+          <t>Jar, Kongsberg, Tønsberg, Sandefjord Penguins, Frisk Asker, Jutul</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Frisk Asker 6, Jar Svart, Holmen Hockey Blå, Ringerike 2, Jutul Rød, Jar Rød</t>
+          <t>Jar Blå, Kongsberg, Tønsberg Rød, Sandefjord, Frisk Asker 4, Jutul Rød</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2163,24 +2163,24 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>U11 Turnering — Baerum ishall</t>
+          <t>U11 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Jar Isforum</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
           <t>17:20</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>19:40</t>
-        </is>
-      </c>
       <c r="F34" t="inlineStr">
         <is>
           <t>U11</t>
@@ -2188,17 +2188,17 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Jar, Kongsberg, Tønsberg, Sandefjord Penguins, Frisk Asker, Jutul</t>
+          <t>Jar, Frisk Asker, Holmen, Ringerike</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Jar Blå, Kongsberg, Tønsberg Rød, Sandefjord, Frisk Asker 4, Jutul Rød</t>
+          <t>Jar Grønn, Jar Rød, Frisk Asker 1, Holmen Hockey Rød, Frisk Asker 2, Ringerike Gul</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2215,42 +2215,42 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>U11 Turnering — Jar Isforum</t>
+          <t>U12 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Jar Isforum</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Jar, Frisk Asker, Holmen, Ringerike</t>
+          <t>Frisk Asker, Jutul, Jar, Tønsberg</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Jar Grønn, Jar Rød, Frisk Asker 1, Holmen Hockey Rød, Frisk Asker 2, Ringerike Gul</t>
+          <t>Frisk Asker 1, Jutul Grønn, Jar Hvit, Tønsberg Rød</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2262,47 +2262,47 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>14.11.2026</t>
+          <t>15.11.2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>U12 Turnering — Askerhallen</t>
+          <t>JU12 Turnering — Skien ishall</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>JU12</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jutul, Jar, Tønsberg</t>
+          <t>Skien, Frisk Asker, Ringerike, Kongsberg/Tønsberg</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Frisk Asker 1, Jutul Grønn, Jar Hvit, Tønsberg Rød</t>
+          <t>Skien, Frisk Asker Svart, Ringerike 1, Kongsberg/Tønsberg</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2319,42 +2319,42 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>JU12 Turnering — Skien ishall</t>
+          <t>U12 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Jar Isforum</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Skien, Frisk Asker, Ringerike, Kongsberg/Tønsberg</t>
+          <t>Jar, Holmen, Ringerike, Frisk Asker</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Skien, Frisk Asker Svart, Ringerike 1, Kongsberg/Tønsberg</t>
+          <t>Jar Rød, Holmen Hockey Hvit, Ringerike 2, Frisk Asker 3</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>U12 Turnering — Jar Isforum</t>
+          <t>U12 Turnering — Tonsberghallen</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Jar Isforum</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2396,17 +2396,17 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Jar, Holmen, Ringerike, Frisk Asker</t>
+          <t>Tønsberg, Jar, Ringerike, Frisk Asker</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Jar Rød, Holmen Hockey Hvit, Ringerike 2, Frisk Asker 3</t>
+          <t>Tønsberg Grå, Jar Svart, Ringerike 1, Frisk Asker 2</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2423,22 +2423,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>U12 Turnering — Tonsberghallen</t>
+          <t>U12 Turnering — Kongsberghallen</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Kongsberghallen</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2448,17 +2448,17 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Tønsberg, Jar, Ringerike, Frisk Asker</t>
+          <t>Jar, Kongsberg, Tønsberg, Jutul</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Tønsberg Grå, Jar Svart, Ringerike 1, Frisk Asker 2</t>
+          <t>Jar Blå, Kongsberg, Tønsberg Hvit, Jutul Rød</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>U12 Turnering — Kongsberghallen</t>
+          <t>U10 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Kongsberghallen</t>
+          <t>Jar Isforum</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2490,27 +2490,27 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Jar, Kongsberg, Tønsberg, Jutul</t>
+          <t>Jar, Jutul, Holmen, Frisk Asker</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Jar Blå, Kongsberg, Tønsberg Hvit, Jutul Rød</t>
+          <t>Jar Blå, Jutul Grønn, Jutul Hvit, Holmen Hockey Blå, Jar Hvit, Frisk Asker 2</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2522,47 +2522,47 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>15.11.2026</t>
+          <t>21.11.2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>U10 Turnering — Jar Isforum</t>
+          <t>AVLYST: JU8 Turnering — Schjongshallen</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Jar Isforum</t>
+          <t>Schjongshallen</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>JU8</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Jar, Jutul, Holmen, Frisk Asker</t>
+          <t>Frisk Asker, Jar, Jutul, Ringerike, Skien</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Jar Blå, Jutul Grønn, Jutul Hvit, Holmen Hockey Blå, Jar Hvit, Frisk Asker 2</t>
+          <t>Frisk Asker, Jar, Jutul Kittens, Ringerike 1, Skien</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2579,42 +2579,42 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>AVLYST: JU8 Turnering — Schjongshallen</t>
+          <t>U10 Turnering — Holmen ishall</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Schjongshallen</t>
+          <t>Holmen ishall</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>JU8</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Jutul, Ringerike, Skien</t>
+          <t>Holmen, Frisk Asker, Jar, Jutul, Ringerike, Tønsberg</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Jutul Kittens, Ringerike 1, Skien</t>
+          <t>Holmen Hockey Hvit, Frisk Asker 1, Jar Rød, Jutul Rød, Ringerike 1, Tønsberg</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2631,42 +2631,42 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>U10 Turnering — Holmen ishall</t>
+          <t>U9 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Holmen ishall</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U9</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Holmen, Frisk Asker, Jar, Jutul, Ringerike, Tønsberg</t>
+          <t>Jutul, Holmen, Frisk Asker, Jar, Kongsberg, Tønsberg</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Holmen Hockey Hvit, Frisk Asker 1, Jar Rød, Jutul Rød, Ringerike 1, Tønsberg</t>
+          <t>Jutul Rød, Jutul Grønn, Holmen Hockey Sort, Frisk Asker 2, Jar Rød, Kongsberg, Frisk Asker 4, Tønsberg</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2683,42 +2683,42 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>U9 Turnering — Baerum ishall</t>
+          <t>JU12 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>JU12</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Jutul, Holmen, Frisk Asker, Jar, Kongsberg, Tønsberg</t>
+          <t>Frisk Asker, Ringerike, Jutul, Skien</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Jutul Rød, Jutul Grønn, Holmen Hockey Sort, Frisk Asker 2, Jar Rød, Kongsberg, Frisk Asker 4, Tønsberg</t>
+          <t>Frisk Asker Orange, Ringerike 2, Jutul/Jar Kittens, Skien</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2735,42 +2735,42 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>JU12 Turnering — Askerhallen</t>
+          <t>U11 Turnering — Schjongshallen</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Schjongshallen</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Frisk Asker, Ringerike, Jutul, Skien</t>
+          <t>Skien, Jar, Frisk Asker, Jutul, Ringerike</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Frisk Asker Orange, Ringerike 2, Jutul/Jar Kittens, Skien</t>
+          <t>Skien, Jar Oransje, Jar Rød, Frisk Asker 2, Jutul Grønn, Ringerike Svart</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2787,42 +2787,42 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>U11 Turnering — Schjongshallen</t>
+          <t>U8 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Schjongshallen</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U8</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Skien, Jar, Frisk Asker, Jutul, Ringerike</t>
+          <t>Frisk Asker, Holmen, Jutul, Kongsberg, Jar</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Skien, Jar Oransje, Jar Rød, Frisk Asker 2, Jutul Grønn, Ringerike Svart</t>
+          <t>Frisk Asker 1, Frisk Asker 4, Holmen Hockey Hvit, Jutul Grønn, Jutul Hvit, Kongsberg, Jar Blå, Holmen Hockey Blå</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2839,42 +2839,42 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>U8 Turnering — Askerhallen</t>
+          <t>U11 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Jar Isforum</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Frisk Asker, Holmen, Jutul, Kongsberg, Jar</t>
+          <t>Kongsberg, Jar, Frisk Asker, Jutul, Tønsberg</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Frisk Asker 1, Frisk Asker 4, Holmen Hockey Hvit, Jutul Grønn, Jutul Hvit, Kongsberg, Jar Blå, Holmen Hockey Blå</t>
+          <t>Kongsberg, Jar Hvit, Frisk Asker 4, Jutul Rød, Tønsberg Grå, Jar Blå</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -2886,47 +2886,47 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>21.11.2026</t>
+          <t>22.11.2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>U11 Turnering — Jar Isforum</t>
+          <t>U10 Turnering — Schjongshallen</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Jar Isforum</t>
+          <t>Schjongshallen</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Kongsberg, Jar, Frisk Asker, Jutul, Tønsberg</t>
+          <t>Ringerike, Frisk Asker, Jar, Tønsberg, Holmen, Jutul</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Kongsberg, Jar Hvit, Frisk Asker 4, Jutul Rød, Tønsberg Grå, Jar Blå</t>
+          <t>Ringerike 2, Frisk Asker 2, Jar Grønn, Tønsberg, Holmen Hockey Hvit, Jutul Hvit</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Ringerike, Frisk Asker, Jar, Tønsberg, Holmen, Jutul</t>
+          <t>Kongsberg, Jar, Jutul, Frisk Asker, Ringerike</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Ringerike 2, Frisk Asker 2, Jar Grønn, Tønsberg, Holmen Hockey Hvit, Jutul Hvit</t>
+          <t>Kongsberg, Jar Gul, Jutul Grønn, Jar Blå, Frisk Asker 6, Ringerike 4</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -2995,42 +2995,42 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>U10 Turnering — Schjongshallen</t>
+          <t>U12 Turnering — Holmen ishall</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Schjongshallen</t>
+          <t>Holmen ishall</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Kongsberg, Jar, Jutul, Frisk Asker, Ringerike</t>
+          <t>Frisk Asker, Tønsberg, Jar, Holmen</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Kongsberg, Jar Gul, Jutul Grønn, Jar Blå, Frisk Asker 6, Ringerike 4</t>
+          <t>Frisk Asker 1, Tønsberg Grå, Jar Hvit, Holmen Hockey Rød</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3047,42 +3047,42 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>U12 Turnering — Holmen ishall</t>
+          <t>U8 Turnering — Skien ishall</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Holmen ishall</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U8</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Frisk Asker, Tønsberg, Jar, Holmen</t>
+          <t>Skien, Jutul, Frisk Asker, Holmen, Jar, Sandefjord Penguins</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Frisk Asker 1, Tønsberg Grå, Jar Hvit, Holmen Hockey Rød</t>
+          <t>Skien, Jutul Grønn, Frisk Asker 4, Holmen Hockey Sort, Jar Hvit, Jar Blå, Frisk Asker 5, Sandefjord</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3099,42 +3099,42 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>U8 Turnering — Skien ishall</t>
+          <t>JU12 Turnering — Kongsberghallen</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Kongsberghallen</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>JU12</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Skien, Jutul, Frisk Asker, Holmen, Jar, Sandefjord Penguins</t>
+          <t>Kongsberg/Tønsberg, Frisk Asker, Ringerike</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Skien, Jutul Grønn, Frisk Asker 4, Holmen Hockey Sort, Jar Hvit, Jar Blå, Frisk Asker 5, Sandefjord</t>
+          <t>Kongsberg/Tønsberg, Frisk Asker Svart, Ringerike 1</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3151,42 +3151,42 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>JU12 Turnering — Kongsberghallen</t>
+          <t>U11 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Kongsberghallen</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Kongsberg/Tønsberg, Frisk Asker, Ringerike</t>
+          <t>Jar, Frisk Asker, Holmen, Jutul</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Kongsberg/Tønsberg, Frisk Asker Svart, Ringerike 1</t>
+          <t>Jar Blå, Frisk Asker 1, Frisk Asker 2, Holmen Hockey Hvit, Jutul Grønn, Jar Oransje</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3203,42 +3203,42 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>U11 Turnering — Askerhallen</t>
+          <t>U9 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Jar Isforum</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U9</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Jar, Frisk Asker, Holmen, Jutul</t>
+          <t>Jutul, Frisk Asker, Holmen, Jar</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Jar Blå, Frisk Asker 1, Frisk Asker 2, Holmen Hockey Hvit, Jutul Grønn, Jar Oransje</t>
+          <t>Jutul Grønn, Jutul Hvit, Frisk Asker 1, Holmen Hockey Hvit, Jar Rød, Frisk Asker 2, Holmen Hockey Sort, Jar Blå</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3250,47 +3250,47 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>22.11.2026</t>
+          <t>28.11.2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>U9 Turnering — Jar Isforum</t>
+          <t>U12 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jar Isforum</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Jutul, Frisk Asker, Holmen, Jar</t>
+          <t>Ringerike, Jar, Tønsberg, Jutul</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Jutul Grønn, Jutul Hvit, Frisk Asker 1, Holmen Hockey Hvit, Jar Rød, Frisk Asker 2, Holmen Hockey Sort, Jar Blå</t>
+          <t>Ringerike 2, Jar Rød, Tønsberg Rød, Jutul Rød</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>U12 Turnering — Baerum ishall</t>
+          <t>U10 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3317,17 +3317,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
           <t>18:20</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3337,12 +3337,12 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Ringerike, Jar, Tønsberg, Jutul</t>
+          <t>Jutul, Jar, Holmen, Ringerike, Frisk Asker</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Ringerike 2, Jar Rød, Tønsberg Rød, Jutul Rød</t>
+          <t>Jutul Hvit, Jar Blå, Holmen Hockey Sort, Ringerike 1, Jar Svart, Frisk Asker 1</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3359,42 +3359,42 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>U10 Turnering — Baerum ishall</t>
+          <t>JU12 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>JU12</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Jutul, Jar, Holmen, Ringerike, Frisk Asker</t>
+          <t>Frisk Asker, Ringerike, Jutul, Skien</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Jutul Hvit, Jar Blå, Holmen Hockey Sort, Ringerike 1, Jar Svart, Frisk Asker 1</t>
+          <t>Frisk Asker Orange, Ringerike 1, Jutul/Jar Kittens, Skien</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JU12 Turnering — Askerhallen</t>
+          <t>U11 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3421,17 +3421,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3441,12 +3441,12 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Frisk Asker, Ringerike, Jutul, Skien</t>
+          <t>Frisk Asker, Jar, Ringerike, Tønsberg, Holmen</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Frisk Asker Orange, Ringerike 1, Jutul/Jar Kittens, Skien</t>
+          <t>Frisk Asker 4, Jar Grønn, Ringerike Svart, Tønsberg Rød, Holmen Hockey Hvit, Jar Rød</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3463,42 +3463,42 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>U11 Turnering — Askerhallen</t>
+          <t>U12 Turnering — Tonsberghallen</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Ringerike, Tønsberg, Holmen</t>
+          <t>Jar, Tønsberg, Frisk Asker, Jutul</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Frisk Asker 4, Jar Grønn, Ringerike Svart, Tønsberg Rød, Holmen Hockey Hvit, Jar Rød</t>
+          <t>Jar Svart, Tønsberg Hvit, Frisk Asker 1, Jutul Grønn</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -3515,42 +3515,42 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>U12 Turnering — Tonsberghallen</t>
+          <t>U11 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Jar Isforum</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Jar, Tønsberg, Frisk Asker, Jutul</t>
+          <t>Jar, Frisk Asker, Kongsberg, Jutul</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Jar Svart, Tønsberg Hvit, Frisk Asker 1, Jutul Grønn</t>
+          <t>Jar Gul, Jar Hvit, Jar Svart, Frisk Asker 1, Kongsberg, Jutul Rød</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -3562,22 +3562,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>28.11.2026</t>
+          <t>29.11.2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>U11 Turnering — Jar Isforum</t>
+          <t>JU8 Turnering — Skien ishall</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Jar Isforum</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3587,22 +3587,22 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>JU8</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Jar, Frisk Asker, Kongsberg, Jutul</t>
+          <t>Frisk Asker, Jar, Jutul, Skien</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Jar Gul, Jar Hvit, Jar Svart, Frisk Asker 1, Kongsberg, Jutul Rød</t>
+          <t>Frisk Asker, Jar, Jutul Kittens, Skien</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -3619,42 +3619,42 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>JU8 Turnering — Skien ishall</t>
+          <t>JU12 Turnering — Schjongshallen</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Schjongshallen</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>JU8</t>
+          <t>JU12</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Jutul, Skien</t>
+          <t>Ringerike, Frisk Asker, Jutul, Kongsberg/Tønsberg</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Jutul Kittens, Skien</t>
+          <t>Ringerike 2, Frisk Asker Svart, Jutul/Jar Kittens, Kongsberg/Tønsberg</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -3671,42 +3671,42 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>JU12 Turnering — Schjongshallen</t>
+          <t>U12 Turnering — Holmen ishall</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Schjongshallen</t>
+          <t>Holmen ishall</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Ringerike, Frisk Asker, Jutul, Kongsberg/Tønsberg</t>
+          <t>Holmen, Kongsberg, Frisk Asker, Tønsberg</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Ringerike 2, Frisk Asker Svart, Jutul/Jar Kittens, Kongsberg/Tønsberg</t>
+          <t>Holmen Hockey Hvit, Kongsberg, Frisk Asker 2, Tønsberg Grå</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -3723,42 +3723,42 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>U12 Turnering — Holmen ishall</t>
+          <t>U8 Turnering — Schjongshallen</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Holmen ishall</t>
+          <t>Schjongshallen</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U8</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Holmen, Kongsberg, Frisk Asker, Tønsberg</t>
+          <t>Ringerike, Sandefjord Penguins, Jar, Frisk Asker, Jutul, Holmen</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Holmen Hockey Hvit, Kongsberg, Frisk Asker 2, Tønsberg Grå</t>
+          <t>Ringerike 1, Sandefjord, Jar Rød, Frisk Asker 3, Jutul Hvit, Frisk Asker 4, Holmen Hockey Blå, Jar Hvit</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -3775,42 +3775,42 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>U8 Turnering — Schjongshallen</t>
+          <t>U11 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Schjongshallen</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Ringerike, Sandefjord Penguins, Jar, Frisk Asker, Jutul, Holmen</t>
+          <t>Jar, Frisk Asker, Sandefjord Penguins, Ringerike, Skien</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Ringerike 1, Sandefjord, Jar Rød, Frisk Asker 3, Jutul Hvit, Frisk Asker 4, Holmen Hockey Blå, Jar Hvit</t>
+          <t>Jar Gul, Jar Oransje, Frisk Asker 3, Sandefjord, Ringerike Svart, Skien</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -3827,42 +3827,42 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>U11 Turnering — Askerhallen</t>
+          <t>U12 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Jar Isforum</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Jar, Frisk Asker, Sandefjord Penguins, Ringerike, Skien</t>
+          <t>Jar, Frisk Asker, Holmen</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Jar Gul, Jar Oransje, Frisk Asker 3, Sandefjord, Ringerike Svart, Skien</t>
+          <t>Jar Blå, Frisk Asker 3, Holmen Hockey Rød, Jar Hvit</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -3874,12 +3874,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>29.11.2026</t>
+          <t>05.12.2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>U12 Turnering — Jar Isforum</t>
+          <t>JU10 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3889,17 +3889,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>JU10</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Jar, Frisk Asker, Holmen</t>
+          <t>Jar, Frisk Asker, Ringerike, Skien</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Jar Blå, Frisk Asker 3, Holmen Hockey Rød, Jar Hvit</t>
+          <t>Jar Hvit, Jar Rød, Jar Blå, Frisk Asker Orange, Ringerike 1, Skien</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -3926,47 +3926,47 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>05.12.2026</t>
+          <t>06.12.2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>JU10 Turnering — Jar Isforum</t>
+          <t>U9 Turnering — Bugården ishall</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Jar Isforum</t>
+          <t>Bugården ishall</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>JU10</t>
+          <t>U9</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Sandefjord Penguins</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Jar, Frisk Asker, Ringerike, Skien</t>
+          <t>Sandefjord Penguins, Frisk Asker, Skien, Holmen, Kongsberg, Ringerike, Tønsberg</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Jar Hvit, Jar Rød, Jar Blå, Frisk Asker Orange, Ringerike 1, Skien</t>
+          <t>Sandefjord, Frisk Asker 3, Frisk Asker 1, Skien, Holmen Hockey Sort, Kongsberg, Ringerike 1, Tønsberg</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">

--- a/latest/season_plan_spond.xlsx
+++ b/latest/season_plan_spond.xlsx
@@ -1029,12 +1029,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1289,12 +1289,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1705,12 +1705,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -4461,12 +4461,12 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -6427,42 +6427,42 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>U11 Turnering — Bugården ishall</t>
+          <t>U12 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Bugården ishall</t>
+          <t>Jar Isforum</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins, Jar, Frisk Asker, Ringerike</t>
+          <t>Jar, Kongsberg, Holmen, Jutul</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Sandefjord, Jar Gul, Frisk Asker 3, Ringerike Svart, Frisk Asker 4, Jar Lilla</t>
+          <t>Jar Hvit, Kongsberg, Holmen Hockey Rød, Jutul Rød</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -6479,42 +6479,42 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>U12 Turnering — Jar Isforum</t>
+          <t>U10 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Jar Isforum</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Jar, Kongsberg, Holmen, Jutul</t>
+          <t>Jutul, Jar, Holmen, Kongsberg</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Jar Hvit, Kongsberg, Holmen Hockey Rød, Jutul Rød</t>
+          <t>Jutul Grønn, Jar Grønn, Holmen Hockey Sort, Holmen Hockey Hvit, Kongsberg, Holmen Hockey Blå</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -6531,42 +6531,42 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>U10 Turnering — Baerum ishall</t>
+          <t>U12 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Jar Isforum</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Jutul, Jar, Holmen, Kongsberg</t>
+          <t>Jar, Jutul, Frisk Asker, Tønsberg</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Jutul Grønn, Jar Grønn, Holmen Hockey Sort, Holmen Hockey Hvit, Kongsberg, Holmen Hockey Blå</t>
+          <t>Jar Svart, Jutul Grønn, Frisk Asker 1, Tønsberg Grå</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>U12 Turnering — Jar Isforum</t>
+          <t>U7 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -6593,17 +6593,17 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U7</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -6613,12 +6613,12 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Jar, Jutul, Frisk Asker, Tønsberg</t>
+          <t>Jar, Jutul, Frisk Asker, Holmen, Tønsberg</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Jar Svart, Jutul Grønn, Frisk Asker 1, Tønsberg Grå</t>
+          <t>Jar Grønn, Jar Blå, Jutul Grønn, Jutul Hvit, Frisk Asker 2, Frisk Asker 3, Holmen Hockey Sort, Tønsberg</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -6630,47 +6630,47 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>24.01.2027</t>
+          <t>30.01.2027</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>U7 Turnering — Jar Isforum</t>
+          <t>JU12 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Jar Isforum</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>U7</t>
+          <t>JU12</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Jar, Jutul, Frisk Asker, Holmen, Tønsberg</t>
+          <t>Frisk Asker, Kongsberg/Tønsberg, Ringerike</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Jar Grønn, Jar Blå, Jutul Grønn, Jutul Hvit, Frisk Asker 2, Frisk Asker 3, Holmen Hockey Sort, Tønsberg</t>
+          <t>Frisk Asker Svart, Frisk Asker Orange, Kongsberg/Tønsberg, Ringerike 1</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -6687,42 +6687,42 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>JU12 Turnering — Askerhallen</t>
+          <t>U11 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Jar Isforum</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Frisk Asker, Kongsberg/Tønsberg, Ringerike</t>
+          <t>Jar, Tønsberg, Jutul, Kongsberg, Ringerike</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Frisk Asker Svart, Frisk Asker Orange, Kongsberg/Tønsberg, Ringerike 1</t>
+          <t>Jar Blå, Tønsberg Hvit, Jutul Rød, Kongsberg, Ringerike Gul, Jar Oransje</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -6739,42 +6739,42 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>U11 Turnering — Jar Isforum</t>
+          <t>U12 Turnering — Tonsberghallen</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Jar Isforum</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Jar, Tønsberg, Jutul, Kongsberg, Ringerike</t>
+          <t>Tønsberg, Jar, Ringerike, Frisk Asker</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Jar Blå, Tønsberg Hvit, Jutul Rød, Kongsberg, Ringerike Gul, Jar Oransje</t>
+          <t>Tønsberg Grå, Jar Rød, Ringerike 1, Frisk Asker 1</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -6791,42 +6791,42 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>U12 Turnering — Tonsberghallen</t>
+          <t>U9 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Jar Isforum</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U9</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Tønsberg, Jar, Ringerike, Frisk Asker</t>
+          <t>Jar, Holmen, Frisk Asker, Sandefjord Penguins, Jutul</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Tønsberg Grå, Jar Rød, Ringerike 1, Frisk Asker 1</t>
+          <t>Jar Blå, Jar Hvit, Holmen Hockey Hvit, Frisk Asker 2, Sandefjord, Frisk Asker 3, Holmen Hockey Sort, Jutul Rød</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -6843,42 +6843,42 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>U9 Turnering — Jar Isforum</t>
+          <t>U12 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Jar Isforum</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Jar, Holmen, Frisk Asker, Sandefjord Penguins, Jutul</t>
+          <t>Frisk Asker, Jar, Holmen, Tønsberg</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Jar Blå, Jar Hvit, Holmen Hockey Hvit, Frisk Asker 2, Sandefjord, Frisk Asker 3, Holmen Hockey Sort, Jutul Rød</t>
+          <t>Frisk Asker 3, Jar Svart, Holmen Hockey Rød, Tønsberg Hvit</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -6895,42 +6895,42 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>U12 Turnering — Askerhallen</t>
+          <t>U11 Turnering — Tonsberghallen</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Holmen, Tønsberg</t>
+          <t>Frisk Asker, Tønsberg, Jar, Skien</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Frisk Asker 3, Jar Svart, Holmen Hockey Rød, Tønsberg Hvit</t>
+          <t>Frisk Asker 4, Tønsberg Rød, Jar Lilla, Jar Svart, Skien, Tønsberg Grå</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -6947,42 +6947,42 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>U11 Turnering — Tonsberghallen</t>
+          <t>U8 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U8</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Frisk Asker, Tønsberg, Jar, Skien</t>
+          <t>Holmen, Ringerike, Jar, Sandefjord Penguins, Frisk Asker, Skien</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Frisk Asker 4, Tønsberg Rød, Jar Lilla, Jar Svart, Skien, Tønsberg Grå</t>
+          <t>Holmen Hockey Sort, Ringerike 2, Jar Blå, Sandefjord, Frisk Asker 3, Jar Svart, Frisk Asker 2, Skien</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -6994,12 +6994,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>30.01.2027</t>
+          <t>31.01.2027</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>U8 Turnering — Askerhallen</t>
+          <t>JU10 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -7009,17 +7009,17 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>JU10</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -7029,12 +7029,12 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Holmen, Ringerike, Jar, Sandefjord Penguins, Frisk Asker, Skien</t>
+          <t>Frisk Asker, Jar, Ringerike, Skien</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Holmen Hockey Sort, Ringerike 2, Jar Blå, Sandefjord, Frisk Asker 3, Jar Svart, Frisk Asker 2, Skien</t>
+          <t>Frisk Asker Orange, Frisk Asker Svart, Jar Blå, Ringerike 1, Skien, Jar Hvit</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -7051,42 +7051,42 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>JU10 Turnering — Askerhallen</t>
+          <t>U10 Turnering — Schjongshallen</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Schjongshallen</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>JU10</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Ringerike, Skien</t>
+          <t>Ringerike, Frisk Asker, Jar, Holmen</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Frisk Asker Orange, Frisk Asker Svart, Jar Blå, Ringerike 1, Skien, Jar Hvit</t>
+          <t>Ringerike 1, Frisk Asker 4, Jar Rød, Jar Gul, Holmen Hockey Rød, Ringerike 3</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -7103,12 +7103,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>U10 Turnering — Schjongshallen</t>
+          <t>U11 Turnering — Tonsberghallen</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Schjongshallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -7123,22 +7123,22 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Ringerike, Frisk Asker, Jar, Holmen</t>
+          <t>Tønsberg, Jar, Holmen, Kongsberg, Ringerike</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Ringerike 1, Frisk Asker 4, Jar Rød, Jar Gul, Holmen Hockey Rød, Ringerike 3</t>
+          <t>Tønsberg Rød, Jar Grønn, Holmen Hockey Rød, Kongsberg, Ringerike Svart, Jar Lilla</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -7155,42 +7155,42 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>U11 Turnering — Tonsberghallen</t>
+          <t>U12 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Jar Isforum</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Tønsberg, Jar, Holmen, Kongsberg, Ringerike</t>
+          <t>Holmen, Jar, Jutul, Ringerike</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Tønsberg Rød, Jar Grønn, Holmen Hockey Rød, Kongsberg, Ringerike Svart, Jar Lilla</t>
+          <t>Holmen Hockey Hvit, Jar Rød, Jutul Rød, Ringerike 2</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -7202,17 +7202,17 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>31.01.2027</t>
+          <t>06.02.2027</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>U12 Turnering — Jar Isforum</t>
+          <t>U10 Turnering — Holmen ishall</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Jar Isforum</t>
+          <t>Holmen ishall</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -7222,27 +7222,27 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Holmen, Jar, Jutul, Ringerike</t>
+          <t>Holmen, Frisk Asker, Jar, Jutul, Ringerike, Kongsberg</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Holmen Hockey Hvit, Jar Rød, Jutul Rød, Ringerike 2</t>
+          <t>Holmen Hockey Hvit, Frisk Asker 6, Jar Blå, Jutul Hvit, Ringerike 4, Kongsberg</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -7259,12 +7259,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>U10 Turnering — Holmen ishall</t>
+          <t>U12 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Holmen ishall</t>
+          <t>Jar Isforum</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -7274,27 +7274,27 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Holmen, Frisk Asker, Jar, Jutul, Ringerike, Kongsberg</t>
+          <t>Jar, Frisk Asker, Tønsberg, Jutul</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Holmen Hockey Hvit, Frisk Asker 6, Jar Blå, Jutul Hvit, Ringerike 4, Kongsberg</t>
+          <t>Jar Blå, Frisk Asker 2, Tønsberg Rød, Jutul Rød</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -7311,42 +7311,42 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>U12 Turnering — Jar Isforum</t>
+          <t>U7 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Jar Isforum</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U7</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Jar, Frisk Asker, Tønsberg, Jutul</t>
+          <t>Frisk Asker, Jar, Holmen, Jutul, Sandefjord Penguins</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Jar Blå, Frisk Asker 2, Tønsberg Rød, Jutul Rød</t>
+          <t>Frisk Asker 1, Jar Grønn, Jar Blå, Holmen Hockey Hvit, Jar Hvit, Jutul Grønn, Sandefjord, Holmen Hockey Rød</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -7363,42 +7363,42 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>U7 Turnering — Askerhallen</t>
+          <t>U12 Turnering — Schjongshallen</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Schjongshallen</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>U7</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Holmen, Jutul, Sandefjord Penguins</t>
+          <t>Ringerike, Holmen, Tønsberg</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Frisk Asker 1, Jar Grønn, Jar Blå, Holmen Hockey Hvit, Jar Hvit, Jutul Grønn, Sandefjord, Holmen Hockey Rød</t>
+          <t>Ringerike 1, Ringerike 2, Holmen Hockey Rød, Tønsberg Grå</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -7415,42 +7415,42 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>U12 Turnering — Schjongshallen</t>
+          <t>U11 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Schjongshallen</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Ringerike, Holmen, Tønsberg</t>
+          <t>Frisk Asker, Jar, Holmen, Sandefjord Penguins, Jutul, Tønsberg</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Ringerike 1, Ringerike 2, Holmen Hockey Rød, Tønsberg Grå</t>
+          <t>Frisk Asker 1, Jar Grønn, Holmen Hockey Rød, Sandefjord, Jutul Rød, Tønsberg Grå</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -7462,27 +7462,27 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>06.02.2027</t>
+          <t>07.02.2027</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>U11 Turnering — Askerhallen</t>
+          <t>U11 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Jar Isforum</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -7492,17 +7492,17 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Holmen, Sandefjord Penguins, Jutul, Tønsberg</t>
+          <t>Jar, Tønsberg, Frisk Asker, Sandefjord Penguins, Jutul</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Frisk Asker 1, Jar Grønn, Holmen Hockey Rød, Sandefjord, Jutul Rød, Tønsberg Grå</t>
+          <t>Jar Svart, Tønsberg Rød, Frisk Asker 3, Sandefjord, Jutul Rød, Jar Lilla</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -7514,47 +7514,47 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>07.02.2027</t>
+          <t>13.02.2027</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>U11 Turnering — Jar Isforum</t>
+          <t>JU12 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Jar Isforum</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>JU12</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Jar, Tønsberg, Frisk Asker, Sandefjord Penguins, Jutul</t>
+          <t>Jutul, Frisk Asker, Skien</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Jar Svart, Tønsberg Rød, Frisk Asker 3, Sandefjord, Jutul Rød, Jar Lilla</t>
+          <t>Jutul/Jar Kittens, Frisk Asker Orange, Skien</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>JU12 Turnering — Baerum ishall</t>
+          <t>U12 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -7581,17 +7581,17 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -7601,12 +7601,12 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Jutul, Frisk Asker, Skien</t>
+          <t>Kongsberg, Frisk Asker, Tønsberg, Jutul</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Jutul/Jar Kittens, Frisk Asker Orange, Skien</t>
+          <t>Kongsberg, Frisk Asker 3, Tønsberg Grå, Jutul Grønn</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -7623,42 +7623,42 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>U12 Turnering — Baerum ishall</t>
+          <t>U8 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Jar Isforum</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U8</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Kongsberg, Frisk Asker, Tønsberg, Jutul</t>
+          <t>Jar, Frisk Asker, Holmen, Jutul, Sandefjord Penguins</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Kongsberg, Frisk Asker 3, Tønsberg Grå, Jutul Grønn</t>
+          <t>Jar Svart, Frisk Asker 1, Holmen Hockey Blå, Frisk Asker 4, Jutul Rød, Holmen Hockey Hvit, Sandefjord, Jar Rød</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -7675,7 +7675,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>U8 Turnering — Jar Isforum</t>
+          <t>JU8 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -7685,17 +7685,17 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>JU8</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -7705,12 +7705,12 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Jar, Frisk Asker, Holmen, Jutul, Sandefjord Penguins</t>
+          <t>Frisk Asker, Jar, Jutul, Skien</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Jar Svart, Frisk Asker 1, Holmen Hockey Blå, Frisk Asker 4, Jutul Rød, Holmen Hockey Hvit, Sandefjord, Jar Rød</t>
+          <t>Frisk Asker, Jar, Jutul Kittens, Skien</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -7727,42 +7727,42 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>JU8 Turnering — Jar Isforum</t>
+          <t>U11 Turnering — Schjongshallen</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Jar Isforum</t>
+          <t>Schjongshallen</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>JU8</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Jutul, Skien</t>
+          <t>Ringerike, Tønsberg, Jar, Holmen</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Jutul Kittens, Skien</t>
+          <t>Ringerike Svart, Ringerike Gul, Tønsberg Rød, Jar Oransje, Holmen Hockey Rød, Jar Grønn</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -7779,42 +7779,42 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>U11 Turnering — Schjongshallen</t>
+          <t>U12 Turnering — Tonsberghallen</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Schjongshallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Ringerike, Tønsberg, Jar, Holmen</t>
+          <t>Jar, Ringerike, Frisk Asker, Tønsberg</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Ringerike Svart, Ringerike Gul, Tønsberg Rød, Jar Oransje, Holmen Hockey Rød, Jar Grønn</t>
+          <t>Jar Hvit, Ringerike 2, Frisk Asker 2, Tønsberg Rød</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -7826,47 +7826,47 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>13.02.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>U12 Turnering — Tonsberghallen</t>
+          <t>U10 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Jar Isforum</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Jar, Ringerike, Frisk Asker, Tønsberg</t>
+          <t>Jar, Holmen, Frisk Asker, Ringerike</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Jar Hvit, Ringerike 2, Frisk Asker 2, Tønsberg Rød</t>
+          <t>Jar Svart, Jar Rød, Holmen Hockey Blå, Frisk Asker 5, Ringerike 4, Ringerike 2</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -7883,42 +7883,42 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>U10 Turnering — Jar Isforum</t>
+          <t>U11 Turnering — Holmen ishall</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Jar Isforum</t>
+          <t>Holmen ishall</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Jar, Holmen, Frisk Asker, Ringerike</t>
+          <t>Holmen, Frisk Asker, Ringerike, Jar</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Jar Svart, Jar Rød, Holmen Hockey Blå, Frisk Asker 5, Ringerike 4, Ringerike 2</t>
+          <t>Holmen Hockey Rød, Frisk Asker 3, Frisk Asker 4, Ringerike Gul, Jar Hvit, Jar Blå</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -7935,42 +7935,42 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>U11 Turnering — Holmen ishall</t>
+          <t>U12 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Holmen ishall</t>
+          <t>Jar Isforum</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Holmen, Frisk Asker, Ringerike, Jar</t>
+          <t>Jar, Frisk Asker, Holmen</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Holmen Hockey Rød, Frisk Asker 3, Frisk Asker 4, Ringerike Gul, Jar Hvit, Jar Blå</t>
+          <t>Jar Svart, Frisk Asker 2, Holmen Hockey Rød, Holmen Hockey Hvit</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -7987,42 +7987,42 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>U12 Turnering — Jar Isforum</t>
+          <t>U7 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Jar Isforum</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U7</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Jar, Frisk Asker, Holmen</t>
+          <t>Jutul, Jar, Sandefjord Penguins, Holmen, Frisk Asker</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Jar Svart, Frisk Asker 2, Holmen Hockey Rød, Holmen Hockey Hvit</t>
+          <t>Jutul Rød, Jutul Hvit, Jar Svart, Sandefjord, Holmen Hockey Hvit, Jar Hvit, Frisk Asker 2, Jar Blå</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -8039,42 +8039,42 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>U7 Turnering — Baerum ishall</t>
+          <t>U9 Turnering — Schjongshallen</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Schjongshallen</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>U7</t>
+          <t>U9</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Jutul, Jar, Sandefjord Penguins, Holmen, Frisk Asker</t>
+          <t>Ringerike, Jutul, Frisk Asker, Holmen, Jar</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Jutul Rød, Jutul Hvit, Jar Svart, Sandefjord, Holmen Hockey Hvit, Jar Hvit, Frisk Asker 2, Jar Blå</t>
+          <t>Ringerike 1, Jutul Rød, Frisk Asker 3, Holmen Hockey Rød, Jar Rød, Frisk Asker 1, Jar Hvit, Holmen Hockey Sort</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -8086,47 +8086,47 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>20.02.2027</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>U9 Turnering — Schjongshallen</t>
+          <t>U10 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Schjongshallen</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Ringerike, Jutul, Frisk Asker, Holmen, Jar</t>
+          <t>Frisk Asker, Jar, Ringerike, Kongsberg, Jutul, Tønsberg</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Ringerike 1, Jutul Rød, Frisk Asker 3, Holmen Hockey Rød, Jar Rød, Frisk Asker 1, Jar Hvit, Holmen Hockey Sort</t>
+          <t>Frisk Asker 5, Jar Hvit, Ringerike 1, Kongsberg, Jutul Rød, Tønsberg</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -8143,42 +8143,42 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>U10 Turnering — Askerhallen</t>
+          <t>U7 Turnering — Holmen ishall</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Holmen ishall</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U7</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Ringerike, Kongsberg, Jutul, Tønsberg</t>
+          <t>Holmen, Jar, Jutul, Frisk Asker, Tønsberg</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Frisk Asker 5, Jar Hvit, Ringerike 1, Kongsberg, Jutul Rød, Tønsberg</t>
+          <t>Holmen Hockey Hvit, Holmen Hockey Sort, Jar Grønn, Jutul Rød, Frisk Asker 2, Jar Rød, Frisk Asker 1, Tønsberg</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -8195,42 +8195,42 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>U7 Turnering — Holmen ishall</t>
+          <t>U8 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Holmen ishall</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>U7</t>
+          <t>U8</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Holmen, Jar, Jutul, Frisk Asker, Tønsberg</t>
+          <t>Jutul, Kongsberg, Jar, Ringerike, Tønsberg, Skien, Holmen</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Holmen Hockey Hvit, Holmen Hockey Sort, Jar Grønn, Jutul Rød, Frisk Asker 2, Jar Rød, Frisk Asker 1, Tønsberg</t>
+          <t>Jutul Gul, Jutul Hvit, Kongsberg, Jar Hvit, Ringerike 2, Tønsberg, Skien, Holmen Hockey Hvit</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -8247,42 +8247,42 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>U8 Turnering — Baerum ishall</t>
+          <t>U10 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Jar Isforum</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Jutul, Kongsberg, Jar, Ringerike, Tønsberg, Skien, Holmen</t>
+          <t>Jutul, Frisk Asker, Jar, Holmen, Ringerike</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Jutul Gul, Jutul Hvit, Kongsberg, Jar Hvit, Ringerike 2, Tønsberg, Skien, Holmen Hockey Hvit</t>
+          <t>Jutul Hvit, Frisk Asker 3, Jar Rød, Holmen Hockey Rød, Ringerike 2, Frisk Asker 2</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -8299,7 +8299,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>U10 Turnering — Jar Isforum</t>
+          <t>JU10 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -8309,17 +8309,17 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>JU10</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -8329,12 +8329,12 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Jutul, Frisk Asker, Jar, Holmen, Ringerike</t>
+          <t>Jar, Frisk Asker, Ringerike, Skien</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Jutul Hvit, Frisk Asker 3, Jar Rød, Holmen Hockey Rød, Ringerike 2, Frisk Asker 2</t>
+          <t>Jar Hvit, Jar Rød, Frisk Asker Orange, Ringerike 1, Skien, Frisk Asker Svart</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -8351,42 +8351,42 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>JU10 Turnering — Jar Isforum</t>
+          <t>U9 Turnering — Kongsberghallen</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Jar Isforum</t>
+          <t>Kongsberghallen</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>JU10</t>
+          <t>U9</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Jar, Frisk Asker, Ringerike, Skien</t>
+          <t>Kongsberg, Frisk Asker, Jar, Jutul, Sandefjord Penguins, Ringerike</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Jar Hvit, Jar Rød, Frisk Asker Orange, Ringerike 1, Skien, Frisk Asker Svart</t>
+          <t>Kongsberg, Frisk Asker 2, Jar Rød, Jutul Rød, Jutul Hvit, Sandefjord, Ringerike 1, Jar Hvit</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -8403,42 +8403,42 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>U9 Turnering — Kongsberghallen</t>
+          <t>U11 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Kongsberghallen</t>
+          <t>Jar Isforum</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Kongsberg, Frisk Asker, Jar, Jutul, Sandefjord Penguins, Ringerike</t>
+          <t>Jar, Holmen, Ringerike, Tønsberg, Sandefjord Penguins</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Kongsberg, Frisk Asker 2, Jar Rød, Jutul Rød, Jutul Hvit, Sandefjord, Ringerike 1, Jar Hvit</t>
+          <t>Jar Oransje, Jar Lilla, Holmen Hockey Hvit, Ringerike Gul, Tønsberg Hvit, Sandefjord</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -8450,47 +8450,47 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>20.02.2027</t>
+          <t>21.02.2027</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>U11 Turnering — Jar Isforum</t>
+          <t>JU12 Turnering — Schjongshallen</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Jar Isforum</t>
+          <t>Schjongshallen</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>JU12</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Jar, Holmen, Ringerike, Tønsberg, Sandefjord Penguins</t>
+          <t>Ringerike, Jutul, Kongsberg/Tønsberg</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Jar Oransje, Jar Lilla, Holmen Hockey Hvit, Ringerike Gul, Tønsberg Hvit, Sandefjord</t>
+          <t>Ringerike 2, Ringerike 1, Jutul/Jar Kittens, Kongsberg/Tønsberg</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -8507,42 +8507,42 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>JU12 Turnering — Schjongshallen</t>
+          <t>U11 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Schjongshallen</t>
+          <t>Jar Isforum</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Ringerike, Jutul, Kongsberg/Tønsberg</t>
+          <t>Jar, Frisk Asker, Tønsberg, Ringerike, Holmen</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Ringerike 2, Ringerike 1, Jutul/Jar Kittens, Kongsberg/Tønsberg</t>
+          <t>Jar Svart, Jar Blå, Frisk Asker 3, Tønsberg Grå, Ringerike Svart, Holmen Hockey Hvit</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -8559,42 +8559,42 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>U11 Turnering — Jar Isforum</t>
+          <t>U12 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Jar Isforum</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Jar, Frisk Asker, Tønsberg, Ringerike, Holmen</t>
+          <t>Frisk Asker, Jar, Tønsberg, Holmen</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Jar Svart, Jar Blå, Frisk Asker 3, Tønsberg Grå, Ringerike Svart, Holmen Hockey Hvit</t>
+          <t>Frisk Asker 3, Jar Rød, Tønsberg Hvit, Holmen Hockey Rød</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -8611,42 +8611,42 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>U12 Turnering — Askerhallen</t>
+          <t>U8 Turnering — Holmen ishall</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Holmen ishall</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U8</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Tønsberg, Holmen</t>
+          <t>Holmen, Frisk Asker, Jutul, Jar, Ringerike</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Frisk Asker 3, Jar Rød, Tønsberg Hvit, Holmen Hockey Rød</t>
+          <t>Holmen Hockey Rød, Holmen Hockey Sort, Frisk Asker 2, Frisk Asker 4, Jutul Grønn, Jar Svart, Ringerike 1, Jar Blå</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -8663,42 +8663,42 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>U8 Turnering — Holmen ishall</t>
+          <t>U9 Turnering — Tonsberghallen</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Holmen ishall</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>U9</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Holmen, Frisk Asker, Jutul, Jar, Ringerike</t>
+          <t>Tønsberg, Holmen, Kongsberg, Jutul, Sandefjord Penguins, Skien, Frisk Asker</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Holmen Hockey Rød, Holmen Hockey Sort, Frisk Asker 2, Frisk Asker 4, Jutul Grønn, Jar Svart, Ringerike 1, Jar Blå</t>
+          <t>Tønsberg, Holmen Hockey Rød, Holmen Hockey Sort, Kongsberg, Jutul Grønn, Sandefjord, Skien, Frisk Asker 2</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -8715,42 +8715,42 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>U9 Turnering — Tonsberghallen</t>
+          <t>U10 Turnering — Kongsberghallen</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Kongsberghallen</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Tønsberg, Holmen, Kongsberg, Jutul, Sandefjord Penguins, Skien, Frisk Asker</t>
+          <t>Kongsberg, Jar, Ringerike, Frisk Asker, Holmen, Jutul</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Tønsberg, Holmen Hockey Rød, Holmen Hockey Sort, Kongsberg, Jutul Grønn, Sandefjord, Skien, Frisk Asker 2</t>
+          <t>Kongsberg, Jar Gul, Ringerike 3, Frisk Asker 1, Holmen Hockey Hvit, Jutul Rød</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -8762,47 +8762,47 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>21.02.2027</t>
+          <t>27.02.2027</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>U10 Turnering — Kongsberghallen</t>
+          <t>AVLYST: U12 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Kongsberghallen</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Kongsberg, Jar, Ringerike, Frisk Asker, Holmen, Jutul</t>
+          <t>Frisk Asker, Jar, Tønsberg</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>Kongsberg, Jar Gul, Ringerike 3, Frisk Asker 1, Holmen Hockey Hvit, Jutul Rød</t>
+          <t>Frisk Asker 3, Jar Hvit, Tønsberg Rød, Jar Blå</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -8819,42 +8819,42 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>AVLYST: U12 Turnering — Askerhallen</t>
+          <t>AVLYST: U11 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Jar Isforum</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Tønsberg</t>
+          <t>Jar, Frisk Asker, Skien</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>Frisk Asker 3, Jar Hvit, Tønsberg Rød, Jar Blå</t>
+          <t>Jar Lilla, Jar Rød, Jar Hvit, Frisk Asker 3, Skien, Frisk Asker 2</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -8866,12 +8866,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>27.02.2027</t>
+          <t>06.03.2027</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>AVLYST: U11 Turnering — Jar Isforum</t>
+          <t>U11 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -8901,12 +8901,12 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Jar, Frisk Asker, Skien</t>
+          <t>Jar, Tønsberg, Frisk Asker, Jutul</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Jar Lilla, Jar Rød, Jar Hvit, Frisk Asker 3, Skien, Frisk Asker 2</t>
+          <t>Jar Gul, Jar Rød, Tønsberg Grå, Frisk Asker 2, Jutul Rød, Frisk Asker 1</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -8923,7 +8923,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>U11 Turnering — Jar Isforum</t>
+          <t>JU10 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -8933,17 +8933,17 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>JU10</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -8953,12 +8953,12 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Jar, Tønsberg, Frisk Asker, Jutul</t>
+          <t>Jar, Frisk Asker, Ringerike, Skien</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Jar Gul, Jar Rød, Tønsberg Grå, Frisk Asker 2, Jutul Rød, Frisk Asker 1</t>
+          <t>Jar Rød, Jar Blå, Frisk Asker Orange, Ringerike 1, Skien</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -8975,42 +8975,42 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>JU10 Turnering — Jar Isforum</t>
+          <t>JU12 Turnering — Schjongshallen</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Jar Isforum</t>
+          <t>Schjongshallen</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>JU10</t>
+          <t>JU12</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Jar, Frisk Asker, Ringerike, Skien</t>
+          <t>Ringerike, Frisk Asker</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Jar Rød, Jar Blå, Frisk Asker Orange, Ringerike 1, Skien</t>
+          <t>Ringerike 1, Ringerike 2, Frisk Asker Orange, Frisk Asker Svart</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -9027,42 +9027,42 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>JU12 Turnering — Schjongshallen</t>
+          <t>U10 Turnering — Holmen ishall</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Schjongshallen</t>
+          <t>Holmen ishall</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Ringerike, Frisk Asker</t>
+          <t>Frisk Asker, Jar, Ringerike, Tønsberg, Holmen</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>Ringerike 1, Ringerike 2, Frisk Asker Orange, Frisk Asker Svart</t>
+          <t>Frisk Asker 4, Jar Blå, Frisk Asker 1, Ringerike 4, Tønsberg, Holmen Hockey Sort</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -9079,42 +9079,42 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>U10 Turnering — Holmen ishall</t>
+          <t>U12 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Holmen ishall</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Ringerike, Tønsberg, Holmen</t>
+          <t>Jutul, Jar, Ringerike, Holmen</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>Frisk Asker 4, Jar Blå, Frisk Asker 1, Ringerike 4, Tønsberg, Holmen Hockey Sort</t>
+          <t>Jutul Rød, Jar Svart, Ringerike 1, Holmen Hockey Hvit</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -9131,42 +9131,42 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>U12 Turnering — Baerum ishall</t>
+          <t>U9 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U9</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Jutul, Jar, Ringerike, Holmen</t>
+          <t>Frisk Asker, Jar, Jutul, Kongsberg, Ringerike, Tønsberg</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>Jutul Rød, Jar Svart, Ringerike 1, Holmen Hockey Hvit</t>
+          <t>Frisk Asker 1, Frisk Asker 4, Jar Blå, Jutul Hvit, Jar Rød, Kongsberg, Ringerike 1, Tønsberg</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -9178,12 +9178,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>06.03.2027</t>
+          <t>07.03.2027</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>U9 Turnering — Askerhallen</t>
+          <t>U10 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -9193,17 +9193,17 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Jutul, Kongsberg, Ringerike, Tønsberg</t>
+          <t>Frisk Asker, Jar, Ringerike, Holmen, Jutul</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>Frisk Asker 1, Frisk Asker 4, Jar Blå, Jutul Hvit, Jar Rød, Kongsberg, Ringerike 1, Tønsberg</t>
+          <t>Frisk Asker 2, Frisk Asker 6, Jar Svart, Ringerike 3, Holmen Hockey Hvit, Jutul Grønn</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -9235,42 +9235,42 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>U10 Turnering — Askerhallen</t>
+          <t>U12 Turnering — Kongsberghallen</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Kongsberghallen</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Ringerike, Holmen, Jutul</t>
+          <t>Kongsberg, Jar, Ringerike</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>Frisk Asker 2, Frisk Asker 6, Jar Svart, Ringerike 3, Holmen Hockey Hvit, Jutul Grønn</t>
+          <t>Kongsberg, Jar Rød, Ringerike 2, Jar Blå</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -9287,42 +9287,42 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>U12 Turnering — Kongsberghallen</t>
+          <t>U8 Turnering — Holmen ishall</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Kongsberghallen</t>
+          <t>Holmen ishall</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U8</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Kongsberg, Jar, Ringerike</t>
+          <t>Holmen, Ringerike, Jar, Frisk Asker, Skien, Jutul, Tønsberg</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>Kongsberg, Jar Rød, Ringerike 2, Jar Blå</t>
+          <t>Holmen Hockey Hvit, Ringerike 1, Jar Rød, Frisk Asker 3, Skien, Jutul Rød, Tønsberg, Holmen Hockey Blå</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -9339,42 +9339,42 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>U8 Turnering — Holmen ishall</t>
+          <t>U11 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Holmen ishall</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Holmen, Ringerike, Jar, Frisk Asker, Skien, Jutul, Tønsberg</t>
+          <t>Frisk Asker, Jar, Ringerike, Sandefjord Penguins, Jutul</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>Holmen Hockey Hvit, Ringerike 1, Jar Rød, Frisk Asker 3, Skien, Jutul Rød, Tønsberg, Holmen Hockey Blå</t>
+          <t>Frisk Asker 4, Jar Svart, Ringerike Gul, Sandefjord, Jar Lilla, Jutul Rød</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -9386,47 +9386,47 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>07.03.2027</t>
+          <t>13.03.2027</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>U11 Turnering — Askerhallen</t>
+          <t>U10 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Ringerike, Sandefjord Penguins, Jutul</t>
+          <t>Jutul, Jar, Frisk Asker, Holmen, Ringerike</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Frisk Asker 4, Jar Svart, Ringerike Gul, Sandefjord, Jar Lilla, Jutul Rød</t>
+          <t>Jutul Rød, Jar Blå, Frisk Asker 2, Holmen Hockey Sort, Jar Hvit, Ringerike 2</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -9443,7 +9443,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>U10 Turnering — Baerum ishall</t>
+          <t>JU12 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -9453,17 +9453,17 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>JU12</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -9473,12 +9473,12 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Jutul, Jar, Frisk Asker, Holmen, Ringerike</t>
+          <t>Jutul, Skien, Frisk Asker, Kongsberg/Tønsberg</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>Jutul Rød, Jar Blå, Frisk Asker 2, Holmen Hockey Sort, Jar Hvit, Ringerike 2</t>
+          <t>Jutul/Jar Kittens, Skien, Frisk Asker Svart, Kongsberg/Tønsberg</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -9495,42 +9495,42 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>JU12 Turnering — Baerum ishall</t>
+          <t>U11 Turnering — Bugården ishall</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Bugården ishall</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Sandefjord Penguins</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Jutul, Skien, Frisk Asker, Kongsberg/Tønsberg</t>
+          <t>Sandefjord Penguins, Jar, Frisk Asker, Ringerike</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>Jutul/Jar Kittens, Skien, Frisk Asker Svart, Kongsberg/Tønsberg</t>
+          <t>Sandefjord, Jar Gul, Frisk Asker 3, Ringerike Svart, Frisk Asker 4, Jar Lilla</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">

--- a/latest/season_plan_spond.xlsx
+++ b/latest/season_plan_spond.xlsx
@@ -514,7 +514,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1705,12 +1705,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4981,12 +4981,12 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -5501,12 +5501,12 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -6234,7 +6234,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -6645,12 +6645,12 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -7321,12 +7321,12 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -7430,7 +7430,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -8574,7 +8574,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -9146,7 +9146,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -9193,12 +9193,12 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -9349,12 +9349,12 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -9666,7 +9666,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -9770,7 +9770,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">

--- a/latest/season_plan_spond.xlsx
+++ b/latest/season_plan_spond.xlsx
@@ -774,7 +774,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -6021,12 +6021,12 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -8985,12 +8985,12 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -9713,12 +9713,12 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">

--- a/latest/season_plan_spond.xlsx
+++ b/latest/season_plan_spond.xlsx
@@ -5610,7 +5610,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -6286,7 +6286,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -6598,7 +6598,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -7482,7 +7482,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">

--- a/latest/season_plan_spond.xlsx
+++ b/latest/season_plan_spond.xlsx
@@ -1435,7 +1435,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>U10 Turnering — Askerhallen</t>
+          <t>AVLYST: U10 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1549,12 +1549,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>U10 Turnering — Askerhallen</t>
+          <t>AVLYST: U10 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>U11 Turnering — Baerum ishall</t>
+          <t>AVLYST: U11 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2121,12 +2121,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>U12 Turnering — Jar Isforum</t>
+          <t>AVLYST: U12 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>U9 Turnering — Baerum ishall</t>
+          <t>AVLYST: U9 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>U9 Turnering — Jar Isforum</t>
+          <t>AVLYST: U9 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -4149,12 +4149,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -7586,7 +7586,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -7861,12 +7861,12 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Jar, Holmen, Frisk Asker, Ringerike</t>
+          <t>Jar, Holmen, Jutul, Ringerike</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Jar Svart, Jar Rød, Holmen Hockey Blå, Frisk Asker 5, Ringerike 4, Ringerike 2</t>
+          <t>Jar Svart, Jar Rød, Holmen Hockey Blå, Jutul Grønn, Ringerike 4, Ringerike 2</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -7997,12 +7997,12 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -9079,7 +9079,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>U12 Turnering — Baerum ishall</t>
+          <t>AVLYST: U12 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -9401,12 +9401,12 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -9453,12 +9453,12 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">

--- a/latest/season_plan_spond.xlsx
+++ b/latest/season_plan_spond.xlsx
@@ -841,12 +841,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Holmen, Frisk Asker, Jutul, Kongsberg, Ringerike, Skien</t>
+          <t>Holmen, Frisk Asker, Jutul, Kongsberg, Ringerike, Sandefjord Penguins</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Holmen Hockey Hvit, Frisk Asker 1, Holmen Hockey Rød, Jutul Rød, Kongsberg, Ringerike 1, Frisk Asker 4, Skien</t>
+          <t>Holmen Hockey Hvit, Frisk Asker 1, Holmen Hockey Rød, Jutul Rød, Kongsberg, Ringerike 1, Frisk Asker 4, Sandefjord</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Skien, Jar, Frisk Asker, Jutul, Ringerike</t>
+          <t>Jar, Frisk Asker, Jutul, Ringerike</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Skien, Jar Oransje, Jar Rød, Frisk Asker 2, Jutul Grønn, Ringerike Svart</t>
+          <t>Jar Svart, Jar Oransje, Jar Rød, Frisk Asker 2, Jutul Grønn, Ringerike Svart</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Jutul, Holmen, Tønsberg, Ringerike, Sandefjord Penguins</t>
+          <t>Frisk Asker, Jar, Jutul, Holmen, Tønsberg, Ringerike, Skien</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Frisk Asker 1, Frisk Asker 4, Jar Hvit, Jutul Grønn, Holmen Hockey Hvit, Tønsberg, Ringerike 1, Sandefjord</t>
+          <t>Frisk Asker 1, Frisk Asker 4, Jar Hvit, Jutul Grønn, Holmen Hockey Hvit, Tønsberg, Ringerike 1, Skien</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Frisk Asker, Holmen, Ringerike, Jutul, Jar</t>
+          <t>Frisk Asker, Holmen, Ringerike, Jar</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Frisk Asker 1, Frisk Asker 4, Holmen Hockey Rød, Ringerike 1, Jutul Rød, Jar Rød</t>
+          <t>Frisk Asker 1, Frisk Asker 4, Holmen Hockey Rød, Ringerike 1, Frisk Asker 5, Jar Rød</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -8381,12 +8381,12 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Kongsberg, Frisk Asker, Jar, Jutul, Sandefjord Penguins, Ringerike</t>
+          <t>Kongsberg, Frisk Asker, Jar, Jutul, Holmen, Ringerike</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Kongsberg, Frisk Asker 2, Jar Rød, Jutul Rød, Jutul Hvit, Sandefjord, Ringerike 1, Jar Hvit</t>
+          <t>Kongsberg, Frisk Asker 2, Jar Rød, Jutul Rød, Jutul Hvit, Holmen Hockey Hvit, Ringerike 1, Jar Hvit</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -9941,12 +9941,12 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Jar, Frisk Asker, Jutul, Tønsberg</t>
+          <t>Jar, Frisk Asker, Jutul, Skien, Tønsberg</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>Jar Gul, Frisk Asker 1, Jar Hvit, Jutul Grønn, Jar Svart, Tønsberg Rød</t>
+          <t>Jar Gul, Frisk Asker 1, Jar Hvit, Jutul Grønn, Skien, Tønsberg Rød</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">

--- a/latest/season_plan_spond.xlsx
+++ b/latest/season_plan_spond.xlsx
@@ -2037,12 +2037,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Holmen, Jar, Frisk Asker, Skien, Jutul</t>
+          <t>Holmen, Jar, Frisk Asker, Ringerike, Jutul</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Holmen Hockey Rød, Holmen Hockey Sort, Jar Blå, Jar Hvit, Frisk Asker 4, Skien, Jutul Grønn, Frisk Asker 2</t>
+          <t>Holmen Hockey Rød, Holmen Hockey Sort, Jar Blå, Jar Hvit, Frisk Asker 4, Ringerike 1, Jutul Grønn, Frisk Asker 2</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -8069,12 +8069,12 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Ringerike, Jutul, Frisk Asker, Holmen, Jar</t>
+          <t>Ringerike, Jutul, Skien, Holmen, Jar, Frisk Asker</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Ringerike 1, Jutul Rød, Frisk Asker 3, Holmen Hockey Rød, Jar Rød, Frisk Asker 1, Jar Hvit, Holmen Hockey Sort</t>
+          <t>Ringerike 1, Jutul Rød, Skien, Holmen Hockey Rød, Jar Rød, Frisk Asker 1, Jar Hvit, Holmen Hockey Sort</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -8693,12 +8693,12 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Tønsberg, Holmen, Kongsberg, Jutul, Sandefjord Penguins, Skien, Frisk Asker</t>
+          <t>Tønsberg, Holmen, Kongsberg, Jutul, Sandefjord Penguins, Frisk Asker</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Tønsberg, Holmen Hockey Rød, Holmen Hockey Sort, Kongsberg, Jutul Grønn, Sandefjord, Skien, Frisk Asker 2</t>
+          <t>Tønsberg, Holmen Hockey Rød, Holmen Hockey Sort, Kongsberg, Jutul Grønn, Sandefjord, Frisk Asker 3, Frisk Asker 2</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -9161,12 +9161,12 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Jutul, Kongsberg, Ringerike, Tønsberg</t>
+          <t>Frisk Asker, Jar, Jutul, Kongsberg, Skien, Tønsberg</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>Frisk Asker 1, Frisk Asker 4, Jar Blå, Jutul Hvit, Jar Rød, Kongsberg, Ringerike 1, Tønsberg</t>
+          <t>Frisk Asker 1, Frisk Asker 4, Jar Blå, Jutul Hvit, Jar Rød, Kongsberg, Skien, Tønsberg</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">

--- a/latest/season_plan_spond.xlsx
+++ b/latest/season_plan_spond.xlsx
@@ -1678,7 +1678,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Ringerike 2, Frisk Asker Orange, Frisk Asker Svart, Jutul/Jar Kittens</t>
+          <t>Ringerike 2, Frisk Asker Orange, Ringerike 1, Jutul/Jar Kittens</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Tønsberg, Jar, Holmen, Skien, Ringerike</t>
+          <t>Kongsberg, Jar, Holmen, Skien, Ringerike</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Tønsberg Hvit, Jar Lilla, Jar Gul, Holmen Hockey Hvit, Skien, Ringerike Gul</t>
+          <t>Kongsberg, Jar Lilla, Jar Gul, Holmen Hockey Hvit, Skien, Ringerike Gul</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -5989,12 +5989,12 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Kongsberg, Jar, Frisk Asker, Holmen</t>
+          <t>Kongsberg, Sandefjord Penguins, Frisk Asker, Jar, Holmen</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Kongsberg, Jar Blå, Frisk Asker 2, Jar Oransje, Holmen Hockey Hvit, Frisk Asker 1</t>
+          <t>Kongsberg, Sandefjord, Frisk Asker 2, Jar Oransje, Holmen Hockey Hvit, Frisk Asker 1</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -7133,12 +7133,12 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Tønsberg, Jar, Holmen, Kongsberg, Ringerike</t>
+          <t>Tønsberg, Jar, Holmen, Ringerike</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Tønsberg Rød, Jar Grønn, Holmen Hockey Rød, Kongsberg, Ringerike Svart, Jar Lilla</t>
+          <t>Tønsberg Rød, Jar Grønn, Holmen Hockey Rød, Tønsberg Hvit, Ringerike Svart, Jar Lilla</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Holmen, Sandefjord Penguins, Jutul, Tønsberg</t>
+          <t>Frisk Asker, Jar, Holmen, Jutul, Tønsberg</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Frisk Asker 1, Jar Grønn, Holmen Hockey Rød, Sandefjord, Jutul Rød, Tønsberg Grå</t>
+          <t>Frisk Asker 1, Jar Grønn, Holmen Hockey Rød, Jar Blå, Jutul Rød, Tønsberg Grå</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -8485,12 +8485,12 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Ringerike, Jutul, Kongsberg/Tønsberg</t>
+          <t>Ringerike, Frisk Asker, Kongsberg/Tønsberg</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Ringerike 2, Ringerike 1, Jutul/Jar Kittens, Kongsberg/Tønsberg</t>
+          <t>Ringerike 2, Frisk Asker Svart, Frisk Asker Orange, Kongsberg/Tønsberg</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Ringerike, Frisk Asker</t>
+          <t>Ringerike, Jutul, Frisk Asker</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Ringerike 1, Ringerike 2, Frisk Asker Orange, Frisk Asker Svart</t>
+          <t>Ringerike 1, Ringerike 2, Jutul/Jar Kittens, Frisk Asker Svart</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">

--- a/latest/season_plan_spond.xlsx
+++ b/latest/season_plan_spond.xlsx
@@ -7861,12 +7861,12 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Jar, Holmen, Jutul, Ringerike</t>
+          <t>Jar, Holmen, Jutul</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Jar Svart, Jar Rød, Holmen Hockey Blå, Jutul Grønn, Ringerike 4, Ringerike 2</t>
+          <t>Jar Svart, Jar Rød, Holmen Hockey Blå, Jutul Grønn, Holmen Hockey Sort, Jar Grønn</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">

--- a/latest/season_plan_spond.xlsx
+++ b/latest/season_plan_spond.xlsx
@@ -67898,7 +67898,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>699156df10e3e75b610eec311cfa38d151d8a5186955e16a3f4b0ccfff1f922d</t>
+          <t>4c54761b2040299818ed893b7081e662bb9b249ce19ac891ba175a75bf89d7cb</t>
         </is>
       </c>
     </row>

--- a/latest/season_plan_spond.xlsx
+++ b/latest/season_plan_spond.xlsx
@@ -20412,38 +20412,38 @@
         <v>46368</v>
       </c>
       <c r="B333" s="5" t="n">
-        <v>0.5694444444444444</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="C333" s="5" t="n"/>
       <c r="D333" s="4" t="n">
         <v>46368</v>
       </c>
       <c r="E333" s="5" t="n">
-        <v>0.6388888888888888</v>
+        <v>0.6736111111111112</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>JU12 Turnering — Skien ishall</t>
+          <t>U12 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>JU12 • Vert: Skien • Lag: Skien, Frisk Asker Orange, Ringerike 2, Frisk Asker Svart • RVV-ID: rvv-0030</t>
+          <t>U12 • Vert: Jutul • Lag: Jutul Grønn, Jar Rød, Jar Hvit, Frisk Asker 1 • RVV-ID: rvv-0080</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t>Frisk Asker · Frisk Asker Orange · JU12</t>
+          <t>Frisk Asker · Frisk Asker 1 · U12</t>
         </is>
       </c>
       <c r="J333" t="inlineStr">
         <is>
-          <t>Frisk Asker Orange</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="K333" t="inlineStr">
@@ -20453,17 +20453,17 @@
       </c>
       <c r="L333" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
         <is>
-          <t>rvv-0030</t>
+          <t>rvv-0080</t>
         </is>
       </c>
     </row>
@@ -20472,58 +20472,58 @@
         <v>46368</v>
       </c>
       <c r="B334" s="5" t="n">
-        <v>0.5694444444444444</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="C334" s="5" t="n"/>
       <c r="D334" s="4" t="n">
         <v>46368</v>
       </c>
       <c r="E334" s="5" t="n">
-        <v>0.6388888888888888</v>
+        <v>0.6736111111111112</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>JU12 Turnering — Skien ishall</t>
+          <t>U12 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>JU12 • Vert: Skien • Lag: Skien, Frisk Asker Orange, Ringerike 2, Frisk Asker Svart • RVV-ID: rvv-0030</t>
+          <t>U12 • Vert: Jutul • Lag: Jutul Grønn, Jar Rød, Jar Hvit, Frisk Asker 1 • RVV-ID: rvv-0080</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t>Frisk Asker · Frisk Asker Svart · JU12</t>
+          <t>Jar · Jar Hvit · U12</t>
         </is>
       </c>
       <c r="J334" t="inlineStr">
         <is>
-          <t>Frisk Asker Svart</t>
+          <t>Jar Hvit</t>
         </is>
       </c>
       <c r="K334" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="L334" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
         <is>
-          <t>rvv-0030</t>
+          <t>rvv-0080</t>
         </is>
       </c>
     </row>
@@ -20532,58 +20532,58 @@
         <v>46368</v>
       </c>
       <c r="B335" s="5" t="n">
-        <v>0.5694444444444444</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="C335" s="5" t="n"/>
       <c r="D335" s="4" t="n">
         <v>46368</v>
       </c>
       <c r="E335" s="5" t="n">
-        <v>0.6388888888888888</v>
+        <v>0.6736111111111112</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>JU12 Turnering — Skien ishall</t>
+          <t>U12 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>JU12 • Vert: Skien • Lag: Skien, Frisk Asker Orange, Ringerike 2, Frisk Asker Svart • RVV-ID: rvv-0030</t>
+          <t>U12 • Vert: Jutul • Lag: Jutul Grønn, Jar Rød, Jar Hvit, Frisk Asker 1 • RVV-ID: rvv-0080</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>Ringerike · Ringerike 2 · JU12</t>
+          <t>Jar · Jar Rød · U12</t>
         </is>
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="K335" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="L335" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
         <is>
-          <t>rvv-0030</t>
+          <t>rvv-0080</t>
         </is>
       </c>
     </row>
@@ -20592,58 +20592,58 @@
         <v>46368</v>
       </c>
       <c r="B336" s="5" t="n">
-        <v>0.5694444444444444</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="C336" s="5" t="n"/>
       <c r="D336" s="4" t="n">
         <v>46368</v>
       </c>
       <c r="E336" s="5" t="n">
-        <v>0.6388888888888888</v>
+        <v>0.6736111111111112</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>JU12 Turnering — Skien ishall</t>
+          <t>U12 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>JU12 • Vert: Skien • Lag: Skien, Frisk Asker Orange, Ringerike 2, Frisk Asker Svart • RVV-ID: rvv-0030</t>
+          <t>U12 • Vert: Jutul • Lag: Jutul Grønn, Jar Rød, Jar Hvit, Frisk Asker 1 • RVV-ID: rvv-0080</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t>Skien · Skien · JU12</t>
+          <t>Jutul · Jutul Grønn · U12</t>
         </is>
       </c>
       <c r="J336" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Jutul Grønn</t>
         </is>
       </c>
       <c r="K336" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="L336" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
         <is>
-          <t>rvv-0030</t>
+          <t>rvv-0080</t>
         </is>
       </c>
     </row>
@@ -20652,23 +20652,23 @@
         <v>46368</v>
       </c>
       <c r="B337" s="5" t="n">
-        <v>0.6041666666666666</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="C337" s="5" t="n"/>
       <c r="D337" s="4" t="n">
         <v>46368</v>
       </c>
       <c r="E337" s="5" t="n">
-        <v>0.6736111111111112</v>
+        <v>0.7847222222222222</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>U12 Turnering — Baerum ishall</t>
+          <t>U8 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>U12 • Vert: Jutul • Lag: Jutul Grønn, Jar Rød, Jar Hvit, Frisk Asker 1 • RVV-ID: rvv-0080</t>
+          <t>U8 • Vert: Jutul • Lag: Jutul Hvit, Jutul Grønn, Frisk Asker 1, Holmen Hockey Hvit, Tønsberg, Ringerike 2, Frisk Asker 3, Jar Blå • RVV-ID: rvv-0015</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
@@ -20678,7 +20678,7 @@
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t>Frisk Asker · Frisk Asker 1 · U12</t>
+          <t>Frisk Asker · Frisk Asker 1 · U8</t>
         </is>
       </c>
       <c r="J337" t="inlineStr">
@@ -20693,7 +20693,7 @@
       </c>
       <c r="L337" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U8</t>
         </is>
       </c>
       <c r="M337" t="inlineStr">
@@ -20703,7 +20703,7 @@
       </c>
       <c r="N337" t="inlineStr">
         <is>
-          <t>rvv-0080</t>
+          <t>rvv-0015</t>
         </is>
       </c>
     </row>
@@ -20712,23 +20712,23 @@
         <v>46368</v>
       </c>
       <c r="B338" s="5" t="n">
-        <v>0.6041666666666666</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="C338" s="5" t="n"/>
       <c r="D338" s="4" t="n">
         <v>46368</v>
       </c>
       <c r="E338" s="5" t="n">
-        <v>0.6736111111111112</v>
+        <v>0.7847222222222222</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>U12 Turnering — Baerum ishall</t>
+          <t>U8 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>U12 • Vert: Jutul • Lag: Jutul Grønn, Jar Rød, Jar Hvit, Frisk Asker 1 • RVV-ID: rvv-0080</t>
+          <t>U8 • Vert: Jutul • Lag: Jutul Hvit, Jutul Grønn, Frisk Asker 1, Holmen Hockey Hvit, Tønsberg, Ringerike 2, Frisk Asker 3, Jar Blå • RVV-ID: rvv-0015</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -20738,22 +20738,22 @@
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t>Jar · Jar Hvit · U12</t>
+          <t>Frisk Asker · Frisk Asker 3 · U8</t>
         </is>
       </c>
       <c r="J338" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="K338" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="L338" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U8</t>
         </is>
       </c>
       <c r="M338" t="inlineStr">
@@ -20763,7 +20763,7 @@
       </c>
       <c r="N338" t="inlineStr">
         <is>
-          <t>rvv-0080</t>
+          <t>rvv-0015</t>
         </is>
       </c>
     </row>
@@ -20772,23 +20772,23 @@
         <v>46368</v>
       </c>
       <c r="B339" s="5" t="n">
-        <v>0.6041666666666666</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="C339" s="5" t="n"/>
       <c r="D339" s="4" t="n">
         <v>46368</v>
       </c>
       <c r="E339" s="5" t="n">
-        <v>0.6736111111111112</v>
+        <v>0.7847222222222222</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>U12 Turnering — Baerum ishall</t>
+          <t>U8 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>U12 • Vert: Jutul • Lag: Jutul Grønn, Jar Rød, Jar Hvit, Frisk Asker 1 • RVV-ID: rvv-0080</t>
+          <t>U8 • Vert: Jutul • Lag: Jutul Hvit, Jutul Grønn, Frisk Asker 1, Holmen Hockey Hvit, Tønsberg, Ringerike 2, Frisk Asker 3, Jar Blå • RVV-ID: rvv-0015</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -20798,22 +20798,22 @@
       </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t>Jar · Jar Rød · U12</t>
+          <t>Holmen · Holmen Hockey Hvit · U8</t>
         </is>
       </c>
       <c r="J339" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Holmen Hockey Hvit</t>
         </is>
       </c>
       <c r="K339" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="L339" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U8</t>
         </is>
       </c>
       <c r="M339" t="inlineStr">
@@ -20823,7 +20823,7 @@
       </c>
       <c r="N339" t="inlineStr">
         <is>
-          <t>rvv-0080</t>
+          <t>rvv-0015</t>
         </is>
       </c>
     </row>
@@ -20832,23 +20832,23 @@
         <v>46368</v>
       </c>
       <c r="B340" s="5" t="n">
-        <v>0.6041666666666666</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="C340" s="5" t="n"/>
       <c r="D340" s="4" t="n">
         <v>46368</v>
       </c>
       <c r="E340" s="5" t="n">
-        <v>0.6736111111111112</v>
+        <v>0.7847222222222222</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>U12 Turnering — Baerum ishall</t>
+          <t>U8 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>U12 • Vert: Jutul • Lag: Jutul Grønn, Jar Rød, Jar Hvit, Frisk Asker 1 • RVV-ID: rvv-0080</t>
+          <t>U8 • Vert: Jutul • Lag: Jutul Hvit, Jutul Grønn, Frisk Asker 1, Holmen Hockey Hvit, Tønsberg, Ringerike 2, Frisk Asker 3, Jar Blå • RVV-ID: rvv-0015</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -20858,32 +20858,32 @@
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t>Jutul · Jutul Grønn · U12</t>
+          <t>Jar · Jar Blå · U8</t>
         </is>
       </c>
       <c r="J340" t="inlineStr">
         <is>
-          <t>Jutul Grønn</t>
+          <t>Jar Blå</t>
         </is>
       </c>
       <c r="K340" t="inlineStr">
         <is>
+          <t>Jar</t>
+        </is>
+      </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>U8</t>
+        </is>
+      </c>
+      <c r="M340" t="inlineStr">
+        <is>
           <t>Jutul</t>
         </is>
       </c>
-      <c r="L340" t="inlineStr">
-        <is>
-          <t>U12</t>
-        </is>
-      </c>
-      <c r="M340" t="inlineStr">
-        <is>
-          <t>Jutul</t>
-        </is>
-      </c>
       <c r="N340" t="inlineStr">
         <is>
-          <t>rvv-0080</t>
+          <t>rvv-0015</t>
         </is>
       </c>
     </row>
@@ -20918,17 +20918,17 @@
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t>Frisk Asker · Frisk Asker 1 · U8</t>
+          <t>Jutul · Jutul Grønn · U8</t>
         </is>
       </c>
       <c r="J341" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Jutul Grønn</t>
         </is>
       </c>
       <c r="K341" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="L341" t="inlineStr">
@@ -20978,17 +20978,17 @@
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t>Frisk Asker · Frisk Asker 3 · U8</t>
+          <t>Jutul · Jutul Hvit · U8</t>
         </is>
       </c>
       <c r="J342" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Jutul Hvit</t>
         </is>
       </c>
       <c r="K342" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="L342" t="inlineStr">
@@ -21038,17 +21038,17 @@
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t>Holmen · Holmen Hockey Hvit · U8</t>
+          <t>Ringerike · Ringerike 2 · U8</t>
         </is>
       </c>
       <c r="J343" t="inlineStr">
         <is>
-          <t>Holmen Hockey Hvit</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="K343" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="L343" t="inlineStr">
@@ -21098,17 +21098,17 @@
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t>Jar · Jar Blå · U8</t>
+          <t>Tønsberg · Tønsberg · U8</t>
         </is>
       </c>
       <c r="J344" t="inlineStr">
         <is>
-          <t>Jar Blå</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="K344" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="L344" t="inlineStr">
@@ -21129,241 +21129,241 @@
     </row>
     <row r="345">
       <c r="A345" s="4" t="n">
-        <v>46368</v>
+        <v>46369</v>
       </c>
       <c r="B345" s="5" t="n">
-        <v>0.6770833333333334</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="C345" s="5" t="n"/>
       <c r="D345" s="4" t="n">
-        <v>46368</v>
+        <v>46369</v>
       </c>
       <c r="E345" s="5" t="n">
-        <v>0.7847222222222222</v>
+        <v>0.5138888888888888</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>U8 Turnering — Baerum ishall</t>
+          <t>U10 Turnering — Schjongshallen</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>U8 • Vert: Jutul • Lag: Jutul Hvit, Jutul Grønn, Frisk Asker 1, Holmen Hockey Hvit, Tønsberg, Ringerike 2, Frisk Asker 3, Jar Blå • RVV-ID: rvv-0015</t>
+          <t>U10 • Vert: Ringerike • Lag: Ringerike 2, Frisk Asker 1, Jar Gul, Holmen Hockey Sort, Jutul Hvit, Kongsberg • RVV-ID: rvv-0073</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Schjongshallen</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t>Jutul · Jutul Grønn · U8</t>
+          <t>Frisk Asker · Frisk Asker 1 · U10</t>
         </is>
       </c>
       <c r="J345" t="inlineStr">
         <is>
-          <t>Jutul Grønn</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="K345" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="L345" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
         <is>
-          <t>rvv-0015</t>
+          <t>rvv-0073</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="4" t="n">
-        <v>46368</v>
+        <v>46369</v>
       </c>
       <c r="B346" s="5" t="n">
-        <v>0.6770833333333334</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="C346" s="5" t="n"/>
       <c r="D346" s="4" t="n">
-        <v>46368</v>
+        <v>46369</v>
       </c>
       <c r="E346" s="5" t="n">
-        <v>0.7847222222222222</v>
+        <v>0.5138888888888888</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>U8 Turnering — Baerum ishall</t>
+          <t>U10 Turnering — Schjongshallen</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>U8 • Vert: Jutul • Lag: Jutul Hvit, Jutul Grønn, Frisk Asker 1, Holmen Hockey Hvit, Tønsberg, Ringerike 2, Frisk Asker 3, Jar Blå • RVV-ID: rvv-0015</t>
+          <t>U10 • Vert: Ringerike • Lag: Ringerike 2, Frisk Asker 1, Jar Gul, Holmen Hockey Sort, Jutul Hvit, Kongsberg • RVV-ID: rvv-0073</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Schjongshallen</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t>Jutul · Jutul Hvit · U8</t>
+          <t>Holmen · Holmen Hockey Sort · U10</t>
         </is>
       </c>
       <c r="J346" t="inlineStr">
         <is>
-          <t>Jutul Hvit</t>
+          <t>Holmen Hockey Sort</t>
         </is>
       </c>
       <c r="K346" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="L346" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
         <is>
-          <t>rvv-0015</t>
+          <t>rvv-0073</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="4" t="n">
-        <v>46368</v>
+        <v>46369</v>
       </c>
       <c r="B347" s="5" t="n">
-        <v>0.6770833333333334</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="C347" s="5" t="n"/>
       <c r="D347" s="4" t="n">
-        <v>46368</v>
+        <v>46369</v>
       </c>
       <c r="E347" s="5" t="n">
-        <v>0.7847222222222222</v>
+        <v>0.5138888888888888</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>U8 Turnering — Baerum ishall</t>
+          <t>U10 Turnering — Schjongshallen</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>U8 • Vert: Jutul • Lag: Jutul Hvit, Jutul Grønn, Frisk Asker 1, Holmen Hockey Hvit, Tønsberg, Ringerike 2, Frisk Asker 3, Jar Blå • RVV-ID: rvv-0015</t>
+          <t>U10 • Vert: Ringerike • Lag: Ringerike 2, Frisk Asker 1, Jar Gul, Holmen Hockey Sort, Jutul Hvit, Kongsberg • RVV-ID: rvv-0073</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Schjongshallen</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t>Ringerike · Ringerike 2 · U8</t>
+          <t>Jar · Jar Gul · U10</t>
         </is>
       </c>
       <c r="J347" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Jar Gul</t>
         </is>
       </c>
       <c r="K347" t="inlineStr">
         <is>
+          <t>Jar</t>
+        </is>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>U10</t>
+        </is>
+      </c>
+      <c r="M347" t="inlineStr">
+        <is>
           <t>Ringerike</t>
         </is>
       </c>
-      <c r="L347" t="inlineStr">
-        <is>
-          <t>U8</t>
-        </is>
-      </c>
-      <c r="M347" t="inlineStr">
-        <is>
-          <t>Jutul</t>
-        </is>
-      </c>
       <c r="N347" t="inlineStr">
         <is>
-          <t>rvv-0015</t>
+          <t>rvv-0073</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="4" t="n">
-        <v>46368</v>
+        <v>46369</v>
       </c>
       <c r="B348" s="5" t="n">
-        <v>0.6770833333333334</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="C348" s="5" t="n"/>
       <c r="D348" s="4" t="n">
-        <v>46368</v>
+        <v>46369</v>
       </c>
       <c r="E348" s="5" t="n">
-        <v>0.7847222222222222</v>
+        <v>0.5138888888888888</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>U8 Turnering — Baerum ishall</t>
+          <t>U10 Turnering — Schjongshallen</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>U8 • Vert: Jutul • Lag: Jutul Hvit, Jutul Grønn, Frisk Asker 1, Holmen Hockey Hvit, Tønsberg, Ringerike 2, Frisk Asker 3, Jar Blå • RVV-ID: rvv-0015</t>
+          <t>U10 • Vert: Ringerike • Lag: Ringerike 2, Frisk Asker 1, Jar Gul, Holmen Hockey Sort, Jutul Hvit, Kongsberg • RVV-ID: rvv-0073</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Schjongshallen</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t>Tønsberg · Tønsberg · U8</t>
+          <t>Jutul · Jutul Hvit · U10</t>
         </is>
       </c>
       <c r="J348" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Jutul Hvit</t>
         </is>
       </c>
       <c r="K348" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="L348" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
         <is>
-          <t>rvv-0015</t>
+          <t>rvv-0073</t>
         </is>
       </c>
     </row>
@@ -21398,17 +21398,17 @@
       </c>
       <c r="I349" t="inlineStr">
         <is>
-          <t>Frisk Asker · Frisk Asker 1 · U10</t>
+          <t>Kongsberg · Kongsberg · U10</t>
         </is>
       </c>
       <c r="J349" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="K349" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="L349" t="inlineStr">
@@ -21458,17 +21458,17 @@
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t>Holmen · Holmen Hockey Sort · U10</t>
+          <t>Ringerike · Ringerike 2 · U10</t>
         </is>
       </c>
       <c r="J350" t="inlineStr">
         <is>
-          <t>Holmen Hockey Sort</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="K350" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="L350" t="inlineStr">
@@ -21499,51 +21499,51 @@
         <v>46369</v>
       </c>
       <c r="E351" s="5" t="n">
-        <v>0.5138888888888888</v>
+        <v>0.4861111111111111</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>U10 Turnering — Schjongshallen</t>
+          <t>U12 Turnering — Tonsberghallen</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>U10 • Vert: Ringerike • Lag: Ringerike 2, Frisk Asker 1, Jar Gul, Holmen Hockey Sort, Jutul Hvit, Kongsberg • RVV-ID: rvv-0073</t>
+          <t>U12 • Vert: Tønsberg • Lag: Ringerike 2, Jutul Rød, Ringerike 1, Tønsberg Rød • RVV-ID: rvv-0091</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>Schjongshallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
         <is>
-          <t>Jar · Jar Gul · U10</t>
+          <t>Jutul · Jutul Rød · U12</t>
         </is>
       </c>
       <c r="J351" t="inlineStr">
         <is>
-          <t>Jar Gul</t>
+          <t>Jutul Rød</t>
         </is>
       </c>
       <c r="K351" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="L351" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
         <is>
-          <t>rvv-0073</t>
+          <t>rvv-0091</t>
         </is>
       </c>
     </row>
@@ -21559,51 +21559,51 @@
         <v>46369</v>
       </c>
       <c r="E352" s="5" t="n">
-        <v>0.5138888888888888</v>
+        <v>0.4861111111111111</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>U10 Turnering — Schjongshallen</t>
+          <t>U12 Turnering — Tonsberghallen</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>U10 • Vert: Ringerike • Lag: Ringerike 2, Frisk Asker 1, Jar Gul, Holmen Hockey Sort, Jutul Hvit, Kongsberg • RVV-ID: rvv-0073</t>
+          <t>U12 • Vert: Tønsberg • Lag: Ringerike 2, Jutul Rød, Ringerike 1, Tønsberg Rød • RVV-ID: rvv-0091</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>Schjongshallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t>Jutul · Jutul Hvit · U10</t>
+          <t>Ringerike · Ringerike 1 · U12</t>
         </is>
       </c>
       <c r="J352" t="inlineStr">
         <is>
-          <t>Jutul Hvit</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="K352" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="L352" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
         <is>
-          <t>rvv-0073</t>
+          <t>rvv-0091</t>
         </is>
       </c>
     </row>
@@ -21619,51 +21619,51 @@
         <v>46369</v>
       </c>
       <c r="E353" s="5" t="n">
-        <v>0.5138888888888888</v>
+        <v>0.4861111111111111</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>U10 Turnering — Schjongshallen</t>
+          <t>U12 Turnering — Tonsberghallen</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>U10 • Vert: Ringerike • Lag: Ringerike 2, Frisk Asker 1, Jar Gul, Holmen Hockey Sort, Jutul Hvit, Kongsberg • RVV-ID: rvv-0073</t>
+          <t>U12 • Vert: Tønsberg • Lag: Ringerike 2, Jutul Rød, Ringerike 1, Tønsberg Rød • RVV-ID: rvv-0091</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>Schjongshallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
         <is>
-          <t>Kongsberg · Kongsberg · U10</t>
+          <t>Ringerike · Ringerike 2 · U12</t>
         </is>
       </c>
       <c r="J353" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="K353" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="L353" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
         <is>
-          <t>rvv-0073</t>
+          <t>rvv-0091</t>
         </is>
       </c>
     </row>
@@ -21679,51 +21679,51 @@
         <v>46369</v>
       </c>
       <c r="E354" s="5" t="n">
-        <v>0.5138888888888888</v>
+        <v>0.4861111111111111</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>U10 Turnering — Schjongshallen</t>
+          <t>U12 Turnering — Tonsberghallen</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>U10 • Vert: Ringerike • Lag: Ringerike 2, Frisk Asker 1, Jar Gul, Holmen Hockey Sort, Jutul Hvit, Kongsberg • RVV-ID: rvv-0073</t>
+          <t>U12 • Vert: Tønsberg • Lag: Ringerike 2, Jutul Rød, Ringerike 1, Tønsberg Rød • RVV-ID: rvv-0091</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>Schjongshallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t>Ringerike · Ringerike 2 · U10</t>
+          <t>Tønsberg · Tønsberg Rød · U12</t>
         </is>
       </c>
       <c r="J354" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Tønsberg Rød</t>
         </is>
       </c>
       <c r="K354" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="L354" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
         <is>
-          <t>rvv-0073</t>
+          <t>rvv-0091</t>
         </is>
       </c>
     </row>
@@ -21732,58 +21732,58 @@
         <v>46369</v>
       </c>
       <c r="B355" s="5" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.5520833333333334</v>
       </c>
       <c r="C355" s="5" t="n"/>
       <c r="D355" s="4" t="n">
         <v>46369</v>
       </c>
       <c r="E355" s="5" t="n">
-        <v>0.4861111111111111</v>
+        <v>0.625</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>U12 Turnering — Tonsberghallen</t>
+          <t>JU12 Turnering — Skien ishall</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>U12 • Vert: Tønsberg • Lag: Ringerike 2, Jutul Rød, Ringerike 1, Tønsberg Rød • RVV-ID: rvv-0091</t>
+          <t>JU12 • Vert: Skien • Lag: Skien, Frisk Asker Orange, Ringerike 2, Frisk Asker Svart • RVV-ID: rvv-0030</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
         <is>
-          <t>Jutul · Jutul Rød · U12</t>
+          <t>Frisk Asker · Frisk Asker Orange · JU12</t>
         </is>
       </c>
       <c r="J355" t="inlineStr">
         <is>
-          <t>Jutul Rød</t>
+          <t>Frisk Asker Orange</t>
         </is>
       </c>
       <c r="K355" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="L355" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>JU12</t>
         </is>
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
         <is>
-          <t>rvv-0091</t>
+          <t>rvv-0030</t>
         </is>
       </c>
     </row>
@@ -21792,58 +21792,58 @@
         <v>46369</v>
       </c>
       <c r="B356" s="5" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.5520833333333334</v>
       </c>
       <c r="C356" s="5" t="n"/>
       <c r="D356" s="4" t="n">
         <v>46369</v>
       </c>
       <c r="E356" s="5" t="n">
-        <v>0.4861111111111111</v>
+        <v>0.625</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>U12 Turnering — Tonsberghallen</t>
+          <t>JU12 Turnering — Skien ishall</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>U12 • Vert: Tønsberg • Lag: Ringerike 2, Jutul Rød, Ringerike 1, Tønsberg Rød • RVV-ID: rvv-0091</t>
+          <t>JU12 • Vert: Skien • Lag: Skien, Frisk Asker Orange, Ringerike 2, Frisk Asker Svart • RVV-ID: rvv-0030</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
         <is>
-          <t>Ringerike · Ringerike 1 · U12</t>
+          <t>Frisk Asker · Frisk Asker Svart · JU12</t>
         </is>
       </c>
       <c r="J356" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Frisk Asker Svart</t>
         </is>
       </c>
       <c r="K356" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="L356" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>JU12</t>
         </is>
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
         <is>
-          <t>rvv-0091</t>
+          <t>rvv-0030</t>
         </is>
       </c>
     </row>
@@ -21852,33 +21852,33 @@
         <v>46369</v>
       </c>
       <c r="B357" s="5" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.5520833333333334</v>
       </c>
       <c r="C357" s="5" t="n"/>
       <c r="D357" s="4" t="n">
         <v>46369</v>
       </c>
       <c r="E357" s="5" t="n">
-        <v>0.4861111111111111</v>
+        <v>0.625</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>U12 Turnering — Tonsberghallen</t>
+          <t>JU12 Turnering — Skien ishall</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>U12 • Vert: Tønsberg • Lag: Ringerike 2, Jutul Rød, Ringerike 1, Tønsberg Rød • RVV-ID: rvv-0091</t>
+          <t>JU12 • Vert: Skien • Lag: Skien, Frisk Asker Orange, Ringerike 2, Frisk Asker Svart • RVV-ID: rvv-0030</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
         <is>
-          <t>Ringerike · Ringerike 2 · U12</t>
+          <t>Ringerike · Ringerike 2 · JU12</t>
         </is>
       </c>
       <c r="J357" t="inlineStr">
@@ -21893,17 +21893,17 @@
       </c>
       <c r="L357" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>JU12</t>
         </is>
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
         <is>
-          <t>rvv-0091</t>
+          <t>rvv-0030</t>
         </is>
       </c>
     </row>
@@ -21912,58 +21912,58 @@
         <v>46369</v>
       </c>
       <c r="B358" s="5" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.5520833333333334</v>
       </c>
       <c r="C358" s="5" t="n"/>
       <c r="D358" s="4" t="n">
         <v>46369</v>
       </c>
       <c r="E358" s="5" t="n">
-        <v>0.4861111111111111</v>
+        <v>0.625</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>U12 Turnering — Tonsberghallen</t>
+          <t>JU12 Turnering — Skien ishall</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>U12 • Vert: Tønsberg • Lag: Ringerike 2, Jutul Rød, Ringerike 1, Tønsberg Rød • RVV-ID: rvv-0091</t>
+          <t>JU12 • Vert: Skien • Lag: Skien, Frisk Asker Orange, Ringerike 2, Frisk Asker Svart • RVV-ID: rvv-0030</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
         <is>
-          <t>Tønsberg · Tønsberg Rød · U12</t>
+          <t>Skien · Skien · JU12</t>
         </is>
       </c>
       <c r="J358" t="inlineStr">
         <is>
-          <t>Tønsberg Rød</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="K358" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="L358" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>JU12</t>
         </is>
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
         <is>
-          <t>rvv-0091</t>
+          <t>rvv-0030</t>
         </is>
       </c>
     </row>
@@ -61887,42 +61887,42 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>JU12 Turnering — Skien ishall</t>
+          <t>U12 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Skien, Frisk Asker, Ringerike</t>
+          <t>Jutul, Jar, Frisk Asker</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Skien, Frisk Asker Orange, Ringerike 2, Frisk Asker Svart</t>
+          <t>Jutul Grønn, Jar Rød, Jar Hvit, Frisk Asker 1</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -61939,42 +61939,42 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>U12 Turnering — Baerum ishall</t>
+          <t>JU10 Turnering — Schjongshallen</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Schjongshallen</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>JU10</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Jutul, Jar, Frisk Asker</t>
+          <t>Ringerike, Jar, Frisk Asker</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Jutul Grønn, Jar Rød, Jar Hvit, Frisk Asker 1</t>
+          <t>Ringerike 1, Jar Hvit, Frisk Asker Svart, Jar Rød, Frisk Asker Orange</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -61991,7 +61991,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>JU10 Turnering — Schjongshallen</t>
+          <t>U11 Turnering — Schjongshallen</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -62001,17 +62001,17 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>JU10</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -62021,12 +62021,12 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Ringerike, Jar, Frisk Asker</t>
+          <t>Ringerike, Frisk Asker, Tønsberg, Kongsberg, Sandefjord Penguins, Jar</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Ringerike 1, Jar Hvit, Frisk Asker Svart, Jar Rød, Frisk Asker Orange</t>
+          <t>Ringerike Gul, Frisk Asker 3, Tønsberg Rød, Kongsberg, Sandefjord, Jar Gul</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -62038,47 +62038,47 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>12.12.2026</t>
+          <t>13.12.2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>U11 Turnering — Schjongshallen</t>
+          <t>JU12 Turnering — Skien ishall</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Schjongshallen</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>JU12</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Ringerike, Frisk Asker, Tønsberg, Kongsberg, Sandefjord Penguins, Jar</t>
+          <t>Skien, Frisk Asker, Ringerike</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Ringerike Gul, Frisk Asker 3, Tønsberg Rød, Kongsberg, Sandefjord, Jar Gul</t>
+          <t>Skien, Frisk Asker Orange, Ringerike 2, Frisk Asker Svart</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -67898,7 +67898,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4c54761b2040299818ed893b7081e662bb9b249ce19ac891ba175a75bf89d7cb</t>
+          <t>899655001fbfce313ceddfded6afa4ced743fd714fce8d6471295350ee2b96a2</t>
         </is>
       </c>
     </row>

--- a/latest/season_plan_spond.xlsx
+++ b/latest/season_plan_spond.xlsx
@@ -552,58 +552,58 @@
         <v>46305</v>
       </c>
       <c r="B2" s="5" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="C2" s="5" t="n"/>
       <c r="D2" s="4" t="n">
         <v>46305</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0.6180555555555556</v>
+        <v>0.5763888888888888</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>U10 Turnering — Askerhallen</t>
+          <t>U12 Turnering — Holmen ishall</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>U10 • Vert: Frisk Asker • Lag: Frisk Asker 1, Frisk Asker 3, Jar Hvit, Holmen Hockey Blå, Ringerike 1, Jutul Grønn • RVV-ID: rvv-0001</t>
+          <t>U12 • Vert: Holmen • Lag: Holmen Hockey Rød, Jutul Grønn, Ringerike 1, Kongsberg • RVV-ID: rvv-0004</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Holmen ishall</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Frisk Asker · Frisk Asker 1 · U10</t>
+          <t>Holmen · Holmen Hockey Rød · U12</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Holmen Hockey Rød</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>rvv-0001</t>
+          <t>rvv-0004</t>
         </is>
       </c>
     </row>
@@ -612,58 +612,58 @@
         <v>46305</v>
       </c>
       <c r="B3" s="5" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="C3" s="5" t="n"/>
       <c r="D3" s="4" t="n">
         <v>46305</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>0.6180555555555556</v>
+        <v>0.5763888888888888</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>U10 Turnering — Askerhallen</t>
+          <t>U12 Turnering — Holmen ishall</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>U10 • Vert: Frisk Asker • Lag: Frisk Asker 1, Frisk Asker 3, Jar Hvit, Holmen Hockey Blå, Ringerike 1, Jutul Grønn • RVV-ID: rvv-0001</t>
+          <t>U12 • Vert: Holmen • Lag: Holmen Hockey Rød, Jutul Grønn, Ringerike 1, Kongsberg • RVV-ID: rvv-0004</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Holmen ishall</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Frisk Asker · Frisk Asker 3 · U10</t>
+          <t>Jutul · Jutul Grønn · U12</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Jutul Grønn</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>rvv-0001</t>
+          <t>rvv-0004</t>
         </is>
       </c>
     </row>
@@ -672,58 +672,58 @@
         <v>46305</v>
       </c>
       <c r="B4" s="5" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="C4" s="5" t="n"/>
       <c r="D4" s="4" t="n">
         <v>46305</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0.6180555555555556</v>
+        <v>0.5763888888888888</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>U10 Turnering — Askerhallen</t>
+          <t>U12 Turnering — Holmen ishall</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>U10 • Vert: Frisk Asker • Lag: Frisk Asker 1, Frisk Asker 3, Jar Hvit, Holmen Hockey Blå, Ringerike 1, Jutul Grønn • RVV-ID: rvv-0001</t>
+          <t>U12 • Vert: Holmen • Lag: Holmen Hockey Rød, Jutul Grønn, Ringerike 1, Kongsberg • RVV-ID: rvv-0004</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Holmen ishall</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Holmen · Holmen Hockey Blå · U10</t>
+          <t>Kongsberg · Kongsberg · U12</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Holmen Hockey Blå</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>Kongsberg</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
           <t>Holmen</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>U10</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Frisk Asker</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>rvv-0001</t>
+          <t>rvv-0004</t>
         </is>
       </c>
     </row>
@@ -732,58 +732,58 @@
         <v>46305</v>
       </c>
       <c r="B5" s="5" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="C5" s="5" t="n"/>
       <c r="D5" s="4" t="n">
         <v>46305</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.6180555555555556</v>
+        <v>0.5763888888888888</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>U10 Turnering — Askerhallen</t>
+          <t>U12 Turnering — Holmen ishall</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>U10 • Vert: Frisk Asker • Lag: Frisk Asker 1, Frisk Asker 3, Jar Hvit, Holmen Hockey Blå, Ringerike 1, Jutul Grønn • RVV-ID: rvv-0001</t>
+          <t>U12 • Vert: Holmen • Lag: Holmen Hockey Rød, Jutul Grønn, Ringerike 1, Kongsberg • RVV-ID: rvv-0004</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Holmen ishall</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Jar · Jar Hvit · U10</t>
+          <t>Ringerike · Ringerike 1 · U12</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>rvv-0001</t>
+          <t>rvv-0004</t>
         </is>
       </c>
     </row>
@@ -818,17 +818,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Jutul · Jutul Grønn · U10</t>
+          <t>Frisk Asker · Frisk Asker 1 · U10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Jutul Grønn</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -878,17 +878,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Ringerike · Ringerike 1 · U10</t>
+          <t>Frisk Asker · Frisk Asker 3 · U10</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -919,31 +919,31 @@
         <v>46305</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.6180555555555556</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>U12 Turnering — Holmen ishall</t>
+          <t>U10 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>U12 • Vert: Holmen • Lag: Holmen Hockey Rød, Jutul Grønn, Ringerike 1, Kongsberg • RVV-ID: rvv-0004</t>
+          <t>U10 • Vert: Frisk Asker • Lag: Frisk Asker 1, Frisk Asker 3, Jar Hvit, Holmen Hockey Blå, Ringerike 1, Jutul Grønn • RVV-ID: rvv-0001</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Holmen ishall</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Holmen · Holmen Hockey Rød · U12</t>
+          <t>Holmen · Holmen Hockey Blå · U10</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Holmen Hockey Rød</t>
+          <t>Holmen Hockey Blå</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -953,17 +953,17 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>rvv-0004</t>
+          <t>rvv-0001</t>
         </is>
       </c>
     </row>
@@ -979,51 +979,51 @@
         <v>46305</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.6180555555555556</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>U12 Turnering — Holmen ishall</t>
+          <t>U10 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>U12 • Vert: Holmen • Lag: Holmen Hockey Rød, Jutul Grønn, Ringerike 1, Kongsberg • RVV-ID: rvv-0004</t>
+          <t>U10 • Vert: Frisk Asker • Lag: Frisk Asker 1, Frisk Asker 3, Jar Hvit, Holmen Hockey Blå, Ringerike 1, Jutul Grønn • RVV-ID: rvv-0001</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Holmen ishall</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Jutul · Jutul Grønn · U12</t>
+          <t>Jar · Jar Hvit · U10</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Jutul Grønn</t>
+          <t>Jar Hvit</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>rvv-0004</t>
+          <t>rvv-0001</t>
         </is>
       </c>
     </row>
@@ -1039,51 +1039,51 @@
         <v>46305</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.6180555555555556</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>U12 Turnering — Holmen ishall</t>
+          <t>U10 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>U12 • Vert: Holmen • Lag: Holmen Hockey Rød, Jutul Grønn, Ringerike 1, Kongsberg • RVV-ID: rvv-0004</t>
+          <t>U10 • Vert: Frisk Asker • Lag: Frisk Asker 1, Frisk Asker 3, Jar Hvit, Holmen Hockey Blå, Ringerike 1, Jutul Grønn • RVV-ID: rvv-0001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Holmen ishall</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Kongsberg · Kongsberg · U12</t>
+          <t>Jutul · Jutul Grønn · U10</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Jutul Grønn</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>rvv-0004</t>
+          <t>rvv-0001</t>
         </is>
       </c>
     </row>
@@ -1099,26 +1099,26 @@
         <v>46305</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.6180555555555556</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>U12 Turnering — Holmen ishall</t>
+          <t>U10 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>U12 • Vert: Holmen • Lag: Holmen Hockey Rød, Jutul Grønn, Ringerike 1, Kongsberg • RVV-ID: rvv-0004</t>
+          <t>U10 • Vert: Frisk Asker • Lag: Frisk Asker 1, Frisk Asker 3, Jar Hvit, Holmen Hockey Blå, Ringerike 1, Jutul Grønn • RVV-ID: rvv-0001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Holmen ishall</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Ringerike · Ringerike 1 · U12</t>
+          <t>Ringerike · Ringerike 1 · U10</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1133,17 +1133,17 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>rvv-0004</t>
+          <t>rvv-0001</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
         <v>46305</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0.625</v>
+        <v>0.6597222222222222</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>46305</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0.625</v>
+        <v>0.6597222222222222</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>46305</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0.625</v>
+        <v>0.6597222222222222</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>46305</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0.625</v>
+        <v>0.6597222222222222</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3192,14 +3192,14 @@
         <v>46313</v>
       </c>
       <c r="B46" s="5" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="C46" s="5" t="n"/>
       <c r="D46" s="4" t="n">
         <v>46313</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>0.6180555555555556</v>
+        <v>0.5763888888888888</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3252,14 +3252,14 @@
         <v>46313</v>
       </c>
       <c r="B47" s="5" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="C47" s="5" t="n"/>
       <c r="D47" s="4" t="n">
         <v>46313</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>0.6180555555555556</v>
+        <v>0.5763888888888888</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3312,14 +3312,14 @@
         <v>46313</v>
       </c>
       <c r="B48" s="5" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="C48" s="5" t="n"/>
       <c r="D48" s="4" t="n">
         <v>46313</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>0.6180555555555556</v>
+        <v>0.5763888888888888</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3372,14 +3372,14 @@
         <v>46313</v>
       </c>
       <c r="B49" s="5" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="C49" s="5" t="n"/>
       <c r="D49" s="4" t="n">
         <v>46313</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>0.6180555555555556</v>
+        <v>0.5763888888888888</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3432,14 +3432,14 @@
         <v>46313</v>
       </c>
       <c r="B50" s="5" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="C50" s="5" t="n"/>
       <c r="D50" s="4" t="n">
         <v>46313</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>0.6180555555555556</v>
+        <v>0.5763888888888888</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3492,14 +3492,14 @@
         <v>46313</v>
       </c>
       <c r="B51" s="5" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="C51" s="5" t="n"/>
       <c r="D51" s="4" t="n">
         <v>46313</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>0.6180555555555556</v>
+        <v>0.5763888888888888</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -58423,7 +58423,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -58470,12 +58470,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -58886,12 +58886,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -67898,7 +67898,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>899655001fbfce313ceddfded6afa4ced743fd714fce8d6471295350ee2b96a2</t>
+          <t>733cff02efb97ac68d6b200f090ce013b8c03e21a44cd6ae1a2557211f672e8f</t>
         </is>
       </c>
     </row>

--- a/latest/season_plan_spond.xlsx
+++ b/latest/season_plan_spond.xlsx
@@ -54312,14 +54312,14 @@
         <v>46459</v>
       </c>
       <c r="B898" s="5" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4375</v>
       </c>
       <c r="C898" s="5" t="n"/>
       <c r="D898" s="4" t="n">
         <v>46459</v>
       </c>
       <c r="E898" s="5" t="n">
-        <v>0.5659722222222222</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -54372,14 +54372,14 @@
         <v>46459</v>
       </c>
       <c r="B899" s="5" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4375</v>
       </c>
       <c r="C899" s="5" t="n"/>
       <c r="D899" s="4" t="n">
         <v>46459</v>
       </c>
       <c r="E899" s="5" t="n">
-        <v>0.5659722222222222</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -54432,14 +54432,14 @@
         <v>46459</v>
       </c>
       <c r="B900" s="5" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4375</v>
       </c>
       <c r="C900" s="5" t="n"/>
       <c r="D900" s="4" t="n">
         <v>46459</v>
       </c>
       <c r="E900" s="5" t="n">
-        <v>0.5659722222222222</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -54492,14 +54492,14 @@
         <v>46459</v>
       </c>
       <c r="B901" s="5" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4375</v>
       </c>
       <c r="C901" s="5" t="n"/>
       <c r="D901" s="4" t="n">
         <v>46459</v>
       </c>
       <c r="E901" s="5" t="n">
-        <v>0.5659722222222222</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -54552,14 +54552,14 @@
         <v>46459</v>
       </c>
       <c r="B902" s="5" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4375</v>
       </c>
       <c r="C902" s="5" t="n"/>
       <c r="D902" s="4" t="n">
         <v>46459</v>
       </c>
       <c r="E902" s="5" t="n">
-        <v>0.5659722222222222</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -54612,14 +54612,14 @@
         <v>46459</v>
       </c>
       <c r="B903" s="5" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4375</v>
       </c>
       <c r="C903" s="5" t="n"/>
       <c r="D903" s="4" t="n">
         <v>46459</v>
       </c>
       <c r="E903" s="5" t="n">
-        <v>0.5659722222222222</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -54672,14 +54672,14 @@
         <v>46459</v>
       </c>
       <c r="B904" s="5" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4375</v>
       </c>
       <c r="C904" s="5" t="n"/>
       <c r="D904" s="4" t="n">
         <v>46459</v>
       </c>
       <c r="E904" s="5" t="n">
-        <v>0.5659722222222222</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -54732,14 +54732,14 @@
         <v>46459</v>
       </c>
       <c r="B905" s="5" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4375</v>
       </c>
       <c r="C905" s="5" t="n"/>
       <c r="D905" s="4" t="n">
         <v>46459</v>
       </c>
       <c r="E905" s="5" t="n">
-        <v>0.5659722222222222</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -67201,12 +67201,12 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -67898,7 +67898,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>733cff02efb97ac68d6b200f090ce013b8c03e21a44cd6ae1a2557211f672e8f</t>
+          <t>245e425ef51ba508c04a5ca42d5c20220ecafb0d9e4acf8d35e5e27b41ef89ee</t>
         </is>
       </c>
     </row>

--- a/latest/season_plan_spond.xlsx
+++ b/latest/season_plan_spond.xlsx
@@ -67898,7 +67898,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>245e425ef51ba508c04a5ca42d5c20220ecafb0d9e4acf8d35e5e27b41ef89ee</t>
+          <t>f3f96bf6f522111c6518bbf4aac3ba1c51f5c8ede5372c3b411f50db197754cd</t>
         </is>
       </c>
     </row>

--- a/latest/season_plan_spond.xlsx
+++ b/latest/season_plan_spond.xlsx
@@ -6448,7 +6448,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>JU8 • Vert: Jutul • Lag: Frisk Asker, Jar, Jutul Kittens, Skien • RVV-ID: rvv-0089</t>
+          <t>JU8 • Vert: Jutul • Lag: Frisk Asker, Wildcats Turkis, Wildcats Rosa, Skien • RVV-ID: rvv-0089</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>JU8 • Vert: Jutul • Lag: Frisk Asker, Jar, Jutul Kittens, Skien • RVV-ID: rvv-0089</t>
+          <t>JU8 • Vert: Jutul • Lag: Frisk Asker, Wildcats Turkis, Wildcats Rosa, Skien • RVV-ID: rvv-0089</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6518,17 +6518,17 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Jar · Jar · JU8</t>
+          <t>Skien · Skien · JU8</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -6568,7 +6568,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>JU8 • Vert: Jutul • Lag: Frisk Asker, Jar, Jutul Kittens, Skien • RVV-ID: rvv-0089</t>
+          <t>JU8 • Vert: Jutul • Lag: Frisk Asker, Wildcats Turkis, Wildcats Rosa, Skien • RVV-ID: rvv-0089</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6578,12 +6578,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Jutul · Jutul Kittens · JU8</t>
+          <t>Jutul · Wildcats Rosa · JU8</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Jutul Kittens</t>
+          <t>Wildcats Rosa</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -6628,7 +6628,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>JU8 • Vert: Jutul • Lag: Frisk Asker, Jar, Jutul Kittens, Skien • RVV-ID: rvv-0089</t>
+          <t>JU8 • Vert: Jutul • Lag: Frisk Asker, Wildcats Turkis, Wildcats Rosa, Skien • RVV-ID: rvv-0089</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6638,17 +6638,17 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Skien · Skien · JU8</t>
+          <t>Jar · Wildcats Turkis · JU8</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Wildcats Turkis</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -6919,7 +6919,7 @@
         <v>46334</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>0.5763888888888888</v>
+        <v>0.5972222222222222</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -6979,7 +6979,7 @@
         <v>46334</v>
       </c>
       <c r="E109" s="5" t="n">
-        <v>0.5763888888888888</v>
+        <v>0.5972222222222222</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -7039,7 +7039,7 @@
         <v>46334</v>
       </c>
       <c r="E110" s="5" t="n">
-        <v>0.5763888888888888</v>
+        <v>0.5972222222222222</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         <v>46334</v>
       </c>
       <c r="E111" s="5" t="n">
-        <v>0.5763888888888888</v>
+        <v>0.5972222222222222</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -7159,7 +7159,7 @@
         <v>46334</v>
       </c>
       <c r="E112" s="5" t="n">
-        <v>0.5763888888888888</v>
+        <v>0.5972222222222222</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -7219,7 +7219,7 @@
         <v>46334</v>
       </c>
       <c r="E113" s="5" t="n">
-        <v>0.5763888888888888</v>
+        <v>0.5972222222222222</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -7519,7 +7519,7 @@
         <v>46334</v>
       </c>
       <c r="E118" s="5" t="n">
-        <v>0.7847222222222222</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         <v>46334</v>
       </c>
       <c r="E119" s="5" t="n">
-        <v>0.7847222222222222</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         <v>46334</v>
       </c>
       <c r="E120" s="5" t="n">
-        <v>0.7847222222222222</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -7699,7 +7699,7 @@
         <v>46334</v>
       </c>
       <c r="E121" s="5" t="n">
-        <v>0.7847222222222222</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -7759,7 +7759,7 @@
         <v>46334</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>0.7847222222222222</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -7819,7 +7819,7 @@
         <v>46334</v>
       </c>
       <c r="E123" s="5" t="n">
-        <v>0.7847222222222222</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>46340</v>
       </c>
       <c r="E124" s="5" t="n">
-        <v>0.5972222222222222</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -7939,7 +7939,7 @@
         <v>46340</v>
       </c>
       <c r="E125" s="5" t="n">
-        <v>0.5972222222222222</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         <v>46340</v>
       </c>
       <c r="E126" s="5" t="n">
-        <v>0.5972222222222222</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -8059,7 +8059,7 @@
         <v>46340</v>
       </c>
       <c r="E127" s="5" t="n">
-        <v>0.5972222222222222</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         <v>46340</v>
       </c>
       <c r="E128" s="5" t="n">
-        <v>0.5972222222222222</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -8179,7 +8179,7 @@
         <v>46340</v>
       </c>
       <c r="E129" s="5" t="n">
-        <v>0.5972222222222222</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -9559,7 +9559,7 @@
         <v>46340</v>
       </c>
       <c r="E152" s="5" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -9619,7 +9619,7 @@
         <v>46340</v>
       </c>
       <c r="E153" s="5" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         <v>46340</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         <v>46340</v>
       </c>
       <c r="E155" s="5" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         <v>46340</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -9859,7 +9859,7 @@
         <v>46340</v>
       </c>
       <c r="E157" s="5" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -10639,7 +10639,7 @@
         <v>46341</v>
       </c>
       <c r="E170" s="5" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         <v>46341</v>
       </c>
       <c r="E171" s="5" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -10759,7 +10759,7 @@
         <v>46341</v>
       </c>
       <c r="E172" s="5" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -10819,7 +10819,7 @@
         <v>46341</v>
       </c>
       <c r="E173" s="5" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -10879,7 +10879,7 @@
         <v>46341</v>
       </c>
       <c r="E174" s="5" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -10939,7 +10939,7 @@
         <v>46341</v>
       </c>
       <c r="E175" s="5" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
         <v>46341</v>
       </c>
       <c r="E176" s="5" t="n">
-        <v>0.6944444444444444</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
         <v>46341</v>
       </c>
       <c r="E177" s="5" t="n">
-        <v>0.6944444444444444</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -11119,7 +11119,7 @@
         <v>46341</v>
       </c>
       <c r="E178" s="5" t="n">
-        <v>0.6944444444444444</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -11179,7 +11179,7 @@
         <v>46341</v>
       </c>
       <c r="E179" s="5" t="n">
-        <v>0.6944444444444444</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -12192,7 +12192,7 @@
         <v>46347</v>
       </c>
       <c r="B196" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.625</v>
       </c>
       <c r="C196" s="5" t="n"/>
       <c r="D196" s="4" t="n">
@@ -12252,7 +12252,7 @@
         <v>46347</v>
       </c>
       <c r="B197" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.625</v>
       </c>
       <c r="C197" s="5" t="n"/>
       <c r="D197" s="4" t="n">
@@ -12312,7 +12312,7 @@
         <v>46347</v>
       </c>
       <c r="B198" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.625</v>
       </c>
       <c r="C198" s="5" t="n"/>
       <c r="D198" s="4" t="n">
@@ -12372,7 +12372,7 @@
         <v>46347</v>
       </c>
       <c r="B199" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.625</v>
       </c>
       <c r="C199" s="5" t="n"/>
       <c r="D199" s="4" t="n">
@@ -12432,7 +12432,7 @@
         <v>46347</v>
       </c>
       <c r="B200" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.625</v>
       </c>
       <c r="C200" s="5" t="n"/>
       <c r="D200" s="4" t="n">
@@ -12492,7 +12492,7 @@
         <v>46347</v>
       </c>
       <c r="B201" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.625</v>
       </c>
       <c r="C201" s="5" t="n"/>
       <c r="D201" s="4" t="n">
@@ -12552,7 +12552,7 @@
         <v>46347</v>
       </c>
       <c r="B202" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.625</v>
       </c>
       <c r="C202" s="5" t="n"/>
       <c r="D202" s="4" t="n">
@@ -12612,7 +12612,7 @@
         <v>46347</v>
       </c>
       <c r="B203" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.625</v>
       </c>
       <c r="C203" s="5" t="n"/>
       <c r="D203" s="4" t="n">
@@ -13879,7 +13879,7 @@
         <v>46348</v>
       </c>
       <c r="E224" s="5" t="n">
-        <v>0.5763888888888888</v>
+        <v>0.5972222222222222</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -13939,7 +13939,7 @@
         <v>46348</v>
       </c>
       <c r="E225" s="5" t="n">
-        <v>0.5763888888888888</v>
+        <v>0.5972222222222222</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -13999,7 +13999,7 @@
         <v>46348</v>
       </c>
       <c r="E226" s="5" t="n">
-        <v>0.5763888888888888</v>
+        <v>0.5972222222222222</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         <v>46348</v>
       </c>
       <c r="E227" s="5" t="n">
-        <v>0.5763888888888888</v>
+        <v>0.5972222222222222</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -14119,7 +14119,7 @@
         <v>46348</v>
       </c>
       <c r="E228" s="5" t="n">
-        <v>0.5763888888888888</v>
+        <v>0.5972222222222222</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -14179,7 +14179,7 @@
         <v>46348</v>
       </c>
       <c r="E229" s="5" t="n">
-        <v>0.5763888888888888</v>
+        <v>0.5972222222222222</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>46354</v>
       </c>
       <c r="E240" s="5" t="n">
-        <v>0.5972222222222222</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -14899,7 +14899,7 @@
         <v>46354</v>
       </c>
       <c r="E241" s="5" t="n">
-        <v>0.5972222222222222</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -14959,7 +14959,7 @@
         <v>46354</v>
       </c>
       <c r="E242" s="5" t="n">
-        <v>0.5972222222222222</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -15019,7 +15019,7 @@
         <v>46354</v>
       </c>
       <c r="E243" s="5" t="n">
-        <v>0.5972222222222222</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -15079,7 +15079,7 @@
         <v>46354</v>
       </c>
       <c r="E244" s="5" t="n">
-        <v>0.5972222222222222</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>46354</v>
       </c>
       <c r="E245" s="5" t="n">
-        <v>0.5972222222222222</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -15432,7 +15432,7 @@
         <v>46354</v>
       </c>
       <c r="B250" s="5" t="n">
-        <v>0.625</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="C250" s="5" t="n"/>
       <c r="D250" s="4" t="n">
@@ -15492,7 +15492,7 @@
         <v>46354</v>
       </c>
       <c r="B251" s="5" t="n">
-        <v>0.625</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="C251" s="5" t="n"/>
       <c r="D251" s="4" t="n">
@@ -15552,7 +15552,7 @@
         <v>46354</v>
       </c>
       <c r="B252" s="5" t="n">
-        <v>0.625</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="C252" s="5" t="n"/>
       <c r="D252" s="4" t="n">
@@ -15612,7 +15612,7 @@
         <v>46354</v>
       </c>
       <c r="B253" s="5" t="n">
-        <v>0.625</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="C253" s="5" t="n"/>
       <c r="D253" s="4" t="n">
@@ -15672,7 +15672,7 @@
         <v>46354</v>
       </c>
       <c r="B254" s="5" t="n">
-        <v>0.625</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="C254" s="5" t="n"/>
       <c r="D254" s="4" t="n">
@@ -15732,7 +15732,7 @@
         <v>46354</v>
       </c>
       <c r="B255" s="5" t="n">
-        <v>0.625</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="C255" s="5" t="n"/>
       <c r="D255" s="4" t="n">
@@ -16888,7 +16888,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>JU8 • Vert: Skien • Lag: Frisk Asker, Jar, Jutul Kittens, Skien • RVV-ID: rvv-0020</t>
+          <t>JU8 • Vert: Skien • Lag: Frisk Asker, Wildcats Turkis, Wildcats Rosa, Skien • RVV-ID: rvv-0020</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -16948,7 +16948,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>JU8 • Vert: Skien • Lag: Frisk Asker, Jar, Jutul Kittens, Skien • RVV-ID: rvv-0020</t>
+          <t>JU8 • Vert: Skien • Lag: Frisk Asker, Wildcats Turkis, Wildcats Rosa, Skien • RVV-ID: rvv-0020</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -16958,17 +16958,17 @@
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>Jar · Jar · JU8</t>
+          <t>Skien · Skien · JU8</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
@@ -17008,7 +17008,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>JU8 • Vert: Skien • Lag: Frisk Asker, Jar, Jutul Kittens, Skien • RVV-ID: rvv-0020</t>
+          <t>JU8 • Vert: Skien • Lag: Frisk Asker, Wildcats Turkis, Wildcats Rosa, Skien • RVV-ID: rvv-0020</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -17018,12 +17018,12 @@
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>Jutul · Jutul Kittens · JU8</t>
+          <t>Jutul · Wildcats Rosa · JU8</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>Jutul Kittens</t>
+          <t>Wildcats Rosa</t>
         </is>
       </c>
       <c r="K276" t="inlineStr">
@@ -17068,7 +17068,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>JU8 • Vert: Skien • Lag: Frisk Asker, Jar, Jutul Kittens, Skien • RVV-ID: rvv-0020</t>
+          <t>JU8 • Vert: Skien • Lag: Frisk Asker, Wildcats Turkis, Wildcats Rosa, Skien • RVV-ID: rvv-0020</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -17078,17 +17078,17 @@
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>Skien · Skien · JU8</t>
+          <t>Jar · Wildcats Turkis · JU8</t>
         </is>
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Wildcats Turkis</t>
         </is>
       </c>
       <c r="K277" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
@@ -17839,7 +17839,7 @@
         <v>46355</v>
       </c>
       <c r="E290" s="5" t="n">
-        <v>0.5902777777777778</v>
+        <v>0.5972222222222222</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -17899,7 +17899,7 @@
         <v>46355</v>
       </c>
       <c r="E291" s="5" t="n">
-        <v>0.5902777777777778</v>
+        <v>0.5972222222222222</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -17959,7 +17959,7 @@
         <v>46355</v>
       </c>
       <c r="E292" s="5" t="n">
-        <v>0.5902777777777778</v>
+        <v>0.5972222222222222</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -18019,7 +18019,7 @@
         <v>46355</v>
       </c>
       <c r="E293" s="5" t="n">
-        <v>0.5902777777777778</v>
+        <v>0.5972222222222222</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -18072,14 +18072,14 @@
         <v>46355</v>
       </c>
       <c r="B294" s="5" t="n">
-        <v>0.625</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="C294" s="5" t="n"/>
       <c r="D294" s="4" t="n">
         <v>46355</v>
       </c>
       <c r="E294" s="5" t="n">
-        <v>0.7013888888888888</v>
+        <v>0.6805555555555556</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -18132,14 +18132,14 @@
         <v>46355</v>
       </c>
       <c r="B295" s="5" t="n">
-        <v>0.625</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="C295" s="5" t="n"/>
       <c r="D295" s="4" t="n">
         <v>46355</v>
       </c>
       <c r="E295" s="5" t="n">
-        <v>0.7013888888888888</v>
+        <v>0.6805555555555556</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -18192,14 +18192,14 @@
         <v>46355</v>
       </c>
       <c r="B296" s="5" t="n">
-        <v>0.625</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="C296" s="5" t="n"/>
       <c r="D296" s="4" t="n">
         <v>46355</v>
       </c>
       <c r="E296" s="5" t="n">
-        <v>0.7013888888888888</v>
+        <v>0.6805555555555556</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -18252,14 +18252,14 @@
         <v>46355</v>
       </c>
       <c r="B297" s="5" t="n">
-        <v>0.625</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="C297" s="5" t="n"/>
       <c r="D297" s="4" t="n">
         <v>46355</v>
       </c>
       <c r="E297" s="5" t="n">
-        <v>0.7013888888888888</v>
+        <v>0.6805555555555556</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -18312,14 +18312,14 @@
         <v>46355</v>
       </c>
       <c r="B298" s="5" t="n">
-        <v>0.625</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="C298" s="5" t="n"/>
       <c r="D298" s="4" t="n">
         <v>46355</v>
       </c>
       <c r="E298" s="5" t="n">
-        <v>0.7013888888888888</v>
+        <v>0.6805555555555556</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -18372,14 +18372,14 @@
         <v>46355</v>
       </c>
       <c r="B299" s="5" t="n">
-        <v>0.625</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="C299" s="5" t="n"/>
       <c r="D299" s="4" t="n">
         <v>46355</v>
       </c>
       <c r="E299" s="5" t="n">
-        <v>0.7013888888888888</v>
+        <v>0.6805555555555556</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -18439,7 +18439,7 @@
         <v>46361</v>
       </c>
       <c r="E300" s="5" t="n">
-        <v>0.5972222222222222</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -18499,7 +18499,7 @@
         <v>46361</v>
       </c>
       <c r="E301" s="5" t="n">
-        <v>0.5972222222222222</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -18559,7 +18559,7 @@
         <v>46361</v>
       </c>
       <c r="E302" s="5" t="n">
-        <v>0.5972222222222222</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -18619,7 +18619,7 @@
         <v>46361</v>
       </c>
       <c r="E303" s="5" t="n">
-        <v>0.5972222222222222</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -18679,7 +18679,7 @@
         <v>46361</v>
       </c>
       <c r="E304" s="5" t="n">
-        <v>0.5972222222222222</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -18739,7 +18739,7 @@
         <v>46361</v>
       </c>
       <c r="E305" s="5" t="n">
-        <v>0.5972222222222222</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23419,7 +23419,7 @@
         <v>46375</v>
       </c>
       <c r="E383" s="5" t="n">
-        <v>0.775</v>
+        <v>0.7743055555555556</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -23479,7 +23479,7 @@
         <v>46375</v>
       </c>
       <c r="E384" s="5" t="n">
-        <v>0.775</v>
+        <v>0.7743055555555556</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -23539,7 +23539,7 @@
         <v>46375</v>
       </c>
       <c r="E385" s="5" t="n">
-        <v>0.775</v>
+        <v>0.7743055555555556</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -23599,7 +23599,7 @@
         <v>46375</v>
       </c>
       <c r="E386" s="5" t="n">
-        <v>0.775</v>
+        <v>0.7743055555555556</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -23659,7 +23659,7 @@
         <v>46375</v>
       </c>
       <c r="E387" s="5" t="n">
-        <v>0.775</v>
+        <v>0.7743055555555556</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -23719,7 +23719,7 @@
         <v>46375</v>
       </c>
       <c r="E388" s="5" t="n">
-        <v>0.775</v>
+        <v>0.7743055555555556</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -23779,7 +23779,7 @@
         <v>46375</v>
       </c>
       <c r="E389" s="5" t="n">
-        <v>0.775</v>
+        <v>0.7743055555555556</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -23839,7 +23839,7 @@
         <v>46375</v>
       </c>
       <c r="E390" s="5" t="n">
-        <v>0.775</v>
+        <v>0.7743055555555556</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -26179,7 +26179,7 @@
         <v>46397</v>
       </c>
       <c r="E429" s="5" t="n">
-        <v>0.5763888888888888</v>
+        <v>0.5972222222222222</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -26239,7 +26239,7 @@
         <v>46397</v>
       </c>
       <c r="E430" s="5" t="n">
-        <v>0.5763888888888888</v>
+        <v>0.5972222222222222</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -26299,7 +26299,7 @@
         <v>46397</v>
       </c>
       <c r="E431" s="5" t="n">
-        <v>0.5763888888888888</v>
+        <v>0.5972222222222222</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -26359,7 +26359,7 @@
         <v>46397</v>
       </c>
       <c r="E432" s="5" t="n">
-        <v>0.5763888888888888</v>
+        <v>0.5972222222222222</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -26419,7 +26419,7 @@
         <v>46397</v>
       </c>
       <c r="E433" s="5" t="n">
-        <v>0.5763888888888888</v>
+        <v>0.5972222222222222</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -26479,7 +26479,7 @@
         <v>46397</v>
       </c>
       <c r="E434" s="5" t="n">
-        <v>0.5763888888888888</v>
+        <v>0.5972222222222222</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -26539,7 +26539,7 @@
         <v>46397</v>
       </c>
       <c r="E435" s="5" t="n">
-        <v>0.5763888888888888</v>
+        <v>0.5972222222222222</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -26599,7 +26599,7 @@
         <v>46397</v>
       </c>
       <c r="E436" s="5" t="n">
-        <v>0.5763888888888888</v>
+        <v>0.5972222222222222</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -30268,7 +30268,7 @@
       </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>JU8 • Vert: Frisk Asker • Lag: Frisk Asker, Jar, Jutul Kittens, Skien • RVV-ID: rvv-0104</t>
+          <t>JU8 • Vert: Frisk Asker • Lag: Frisk Asker, Wildcats Turkis, Wildcats Rosa, Skien • RVV-ID: rvv-0104</t>
         </is>
       </c>
       <c r="H497" t="inlineStr">
@@ -30328,7 +30328,7 @@
       </c>
       <c r="G498" t="inlineStr">
         <is>
-          <t>JU8 • Vert: Frisk Asker • Lag: Frisk Asker, Jar, Jutul Kittens, Skien • RVV-ID: rvv-0104</t>
+          <t>JU8 • Vert: Frisk Asker • Lag: Frisk Asker, Wildcats Turkis, Wildcats Rosa, Skien • RVV-ID: rvv-0104</t>
         </is>
       </c>
       <c r="H498" t="inlineStr">
@@ -30338,17 +30338,17 @@
       </c>
       <c r="I498" t="inlineStr">
         <is>
-          <t>Jar · Jar · JU8</t>
+          <t>Skien · Skien · JU8</t>
         </is>
       </c>
       <c r="J498" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="K498" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="L498" t="inlineStr">
@@ -30388,7 +30388,7 @@
       </c>
       <c r="G499" t="inlineStr">
         <is>
-          <t>JU8 • Vert: Frisk Asker • Lag: Frisk Asker, Jar, Jutul Kittens, Skien • RVV-ID: rvv-0104</t>
+          <t>JU8 • Vert: Frisk Asker • Lag: Frisk Asker, Wildcats Turkis, Wildcats Rosa, Skien • RVV-ID: rvv-0104</t>
         </is>
       </c>
       <c r="H499" t="inlineStr">
@@ -30398,12 +30398,12 @@
       </c>
       <c r="I499" t="inlineStr">
         <is>
-          <t>Jutul · Jutul Kittens · JU8</t>
+          <t>Jutul · Wildcats Rosa · JU8</t>
         </is>
       </c>
       <c r="J499" t="inlineStr">
         <is>
-          <t>Jutul Kittens</t>
+          <t>Wildcats Rosa</t>
         </is>
       </c>
       <c r="K499" t="inlineStr">
@@ -30448,7 +30448,7 @@
       </c>
       <c r="G500" t="inlineStr">
         <is>
-          <t>JU8 • Vert: Frisk Asker • Lag: Frisk Asker, Jar, Jutul Kittens, Skien • RVV-ID: rvv-0104</t>
+          <t>JU8 • Vert: Frisk Asker • Lag: Frisk Asker, Wildcats Turkis, Wildcats Rosa, Skien • RVV-ID: rvv-0104</t>
         </is>
       </c>
       <c r="H500" t="inlineStr">
@@ -30458,17 +30458,17 @@
       </c>
       <c r="I500" t="inlineStr">
         <is>
-          <t>Skien · Skien · JU8</t>
+          <t>Jar · Wildcats Turkis · JU8</t>
         </is>
       </c>
       <c r="J500" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Wildcats Turkis</t>
         </is>
       </c>
       <c r="K500" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="L500" t="inlineStr">
@@ -30732,14 +30732,14 @@
         <v>46404</v>
       </c>
       <c r="B505" s="5" t="n">
-        <v>0.6041666666666666</v>
+        <v>0.5625</v>
       </c>
       <c r="C505" s="5" t="n"/>
       <c r="D505" s="4" t="n">
         <v>46404</v>
       </c>
       <c r="E505" s="5" t="n">
-        <v>0.6805555555555556</v>
+        <v>0.6597222222222222</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -30792,14 +30792,14 @@
         <v>46404</v>
       </c>
       <c r="B506" s="5" t="n">
-        <v>0.6041666666666666</v>
+        <v>0.5625</v>
       </c>
       <c r="C506" s="5" t="n"/>
       <c r="D506" s="4" t="n">
         <v>46404</v>
       </c>
       <c r="E506" s="5" t="n">
-        <v>0.6805555555555556</v>
+        <v>0.6597222222222222</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -30852,14 +30852,14 @@
         <v>46404</v>
       </c>
       <c r="B507" s="5" t="n">
-        <v>0.6041666666666666</v>
+        <v>0.5625</v>
       </c>
       <c r="C507" s="5" t="n"/>
       <c r="D507" s="4" t="n">
         <v>46404</v>
       </c>
       <c r="E507" s="5" t="n">
-        <v>0.6805555555555556</v>
+        <v>0.6597222222222222</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -30912,14 +30912,14 @@
         <v>46404</v>
       </c>
       <c r="B508" s="5" t="n">
-        <v>0.6041666666666666</v>
+        <v>0.5625</v>
       </c>
       <c r="C508" s="5" t="n"/>
       <c r="D508" s="4" t="n">
         <v>46404</v>
       </c>
       <c r="E508" s="5" t="n">
-        <v>0.6805555555555556</v>
+        <v>0.6597222222222222</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -30972,14 +30972,14 @@
         <v>46404</v>
       </c>
       <c r="B509" s="5" t="n">
-        <v>0.6041666666666666</v>
+        <v>0.5625</v>
       </c>
       <c r="C509" s="5" t="n"/>
       <c r="D509" s="4" t="n">
         <v>46404</v>
       </c>
       <c r="E509" s="5" t="n">
-        <v>0.6805555555555556</v>
+        <v>0.6597222222222222</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -31032,14 +31032,14 @@
         <v>46404</v>
       </c>
       <c r="B510" s="5" t="n">
-        <v>0.6041666666666666</v>
+        <v>0.5625</v>
       </c>
       <c r="C510" s="5" t="n"/>
       <c r="D510" s="4" t="n">
         <v>46404</v>
       </c>
       <c r="E510" s="5" t="n">
-        <v>0.6805555555555556</v>
+        <v>0.6597222222222222</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -31092,14 +31092,14 @@
         <v>46404</v>
       </c>
       <c r="B511" s="5" t="n">
-        <v>0.6041666666666666</v>
+        <v>0.5625</v>
       </c>
       <c r="C511" s="5" t="n"/>
       <c r="D511" s="4" t="n">
         <v>46404</v>
       </c>
       <c r="E511" s="5" t="n">
-        <v>0.6805555555555556</v>
+        <v>0.6597222222222222</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -31152,14 +31152,14 @@
         <v>46404</v>
       </c>
       <c r="B512" s="5" t="n">
-        <v>0.6041666666666666</v>
+        <v>0.5625</v>
       </c>
       <c r="C512" s="5" t="n"/>
       <c r="D512" s="4" t="n">
         <v>46404</v>
       </c>
       <c r="E512" s="5" t="n">
-        <v>0.6805555555555556</v>
+        <v>0.6597222222222222</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -31219,7 +31219,7 @@
         <v>46404</v>
       </c>
       <c r="E513" s="5" t="n">
-        <v>0.7319444444444444</v>
+        <v>0.7326388888888888</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -31279,7 +31279,7 @@
         <v>46404</v>
       </c>
       <c r="E514" s="5" t="n">
-        <v>0.7319444444444444</v>
+        <v>0.7326388888888888</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -31339,7 +31339,7 @@
         <v>46404</v>
       </c>
       <c r="E515" s="5" t="n">
-        <v>0.7319444444444444</v>
+        <v>0.7326388888888888</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -31399,7 +31399,7 @@
         <v>46404</v>
       </c>
       <c r="E516" s="5" t="n">
-        <v>0.7319444444444444</v>
+        <v>0.7326388888888888</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -31459,7 +31459,7 @@
         <v>46404</v>
       </c>
       <c r="E517" s="5" t="n">
-        <v>0.7319444444444444</v>
+        <v>0.7326388888888888</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -31519,7 +31519,7 @@
         <v>46404</v>
       </c>
       <c r="E518" s="5" t="n">
-        <v>0.7319444444444444</v>
+        <v>0.7326388888888888</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -31579,7 +31579,7 @@
         <v>46404</v>
       </c>
       <c r="E519" s="5" t="n">
-        <v>0.7319444444444444</v>
+        <v>0.7326388888888888</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -31639,7 +31639,7 @@
         <v>46404</v>
       </c>
       <c r="E520" s="5" t="n">
-        <v>0.7319444444444444</v>
+        <v>0.7326388888888888</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -31699,7 +31699,7 @@
         <v>46410</v>
       </c>
       <c r="E521" s="5" t="n">
-        <v>0.5347222222222222</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -31759,7 +31759,7 @@
         <v>46410</v>
       </c>
       <c r="E522" s="5" t="n">
-        <v>0.5347222222222222</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -31819,7 +31819,7 @@
         <v>46410</v>
       </c>
       <c r="E523" s="5" t="n">
-        <v>0.5347222222222222</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -31879,7 +31879,7 @@
         <v>46410</v>
       </c>
       <c r="E524" s="5" t="n">
-        <v>0.5347222222222222</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -31939,7 +31939,7 @@
         <v>46410</v>
       </c>
       <c r="E525" s="5" t="n">
-        <v>0.5347222222222222</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -31999,7 +31999,7 @@
         <v>46410</v>
       </c>
       <c r="E526" s="5" t="n">
-        <v>0.5347222222222222</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -32659,7 +32659,7 @@
         <v>46410</v>
       </c>
       <c r="E537" s="5" t="n">
-        <v>0.6180555555555556</v>
+        <v>0.6388888888888888</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -32719,7 +32719,7 @@
         <v>46410</v>
       </c>
       <c r="E538" s="5" t="n">
-        <v>0.6180555555555556</v>
+        <v>0.6388888888888888</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -32779,7 +32779,7 @@
         <v>46410</v>
       </c>
       <c r="E539" s="5" t="n">
-        <v>0.6180555555555556</v>
+        <v>0.6388888888888888</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -32839,7 +32839,7 @@
         <v>46410</v>
       </c>
       <c r="E540" s="5" t="n">
-        <v>0.6180555555555556</v>
+        <v>0.6388888888888888</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -32899,7 +32899,7 @@
         <v>46410</v>
       </c>
       <c r="E541" s="5" t="n">
-        <v>0.6180555555555556</v>
+        <v>0.6388888888888888</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -32959,7 +32959,7 @@
         <v>46410</v>
       </c>
       <c r="E542" s="5" t="n">
-        <v>0.6180555555555556</v>
+        <v>0.6388888888888888</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -33019,7 +33019,7 @@
         <v>46410</v>
       </c>
       <c r="E543" s="5" t="n">
-        <v>0.6180555555555556</v>
+        <v>0.6388888888888888</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -33079,7 +33079,7 @@
         <v>46410</v>
       </c>
       <c r="E544" s="5" t="n">
-        <v>0.6180555555555556</v>
+        <v>0.6388888888888888</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -33619,7 +33619,7 @@
         <v>46410</v>
       </c>
       <c r="E553" s="5" t="n">
-        <v>0.7215277777777778</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -33679,7 +33679,7 @@
         <v>46410</v>
       </c>
       <c r="E554" s="5" t="n">
-        <v>0.7215277777777778</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -33739,7 +33739,7 @@
         <v>46410</v>
       </c>
       <c r="E555" s="5" t="n">
-        <v>0.7215277777777778</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -33799,7 +33799,7 @@
         <v>46410</v>
       </c>
       <c r="E556" s="5" t="n">
-        <v>0.7215277777777778</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -33859,7 +33859,7 @@
         <v>46410</v>
       </c>
       <c r="E557" s="5" t="n">
-        <v>0.7215277777777778</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -33919,7 +33919,7 @@
         <v>46410</v>
       </c>
       <c r="E558" s="5" t="n">
-        <v>0.7215277777777778</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -33972,38 +33972,38 @@
         <v>46410</v>
       </c>
       <c r="B559" s="5" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.6875</v>
       </c>
       <c r="C559" s="5" t="n"/>
       <c r="D559" s="4" t="n">
         <v>46410</v>
       </c>
       <c r="E559" s="5" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7847222222222222</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>U11 Turnering — Baerum ishall</t>
+          <t>U10 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="G559" t="inlineStr">
         <is>
-          <t>U11 • Vert: Jutul • Lag: Jutul Grønn, Frisk Asker 4, Jar Svart, Jar Hvit, Holmen Hockey Rød, Tønsberg Grå • RVV-ID: rvv-0074</t>
+          <t>U10 • Vert: Frisk Asker • Lag: Frisk Asker 1, Frisk Asker 4, Holmen Hockey Rød, Ringerike 1, Frisk Asker 5, Jar Rød • RVV-ID: rvv-0135</t>
         </is>
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="I559" t="inlineStr">
         <is>
-          <t>Frisk Asker · Frisk Asker 4 · U11</t>
+          <t>Frisk Asker · Frisk Asker 1 · U10</t>
         </is>
       </c>
       <c r="J559" t="inlineStr">
         <is>
-          <t>Frisk Asker 4</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="K559" t="inlineStr">
@@ -34013,17 +34013,17 @@
       </c>
       <c r="L559" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="M559" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="N559" t="inlineStr">
         <is>
-          <t>rvv-0074</t>
+          <t>rvv-0135</t>
         </is>
       </c>
     </row>
@@ -34032,58 +34032,58 @@
         <v>46410</v>
       </c>
       <c r="B560" s="5" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.6875</v>
       </c>
       <c r="C560" s="5" t="n"/>
       <c r="D560" s="4" t="n">
         <v>46410</v>
       </c>
       <c r="E560" s="5" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7847222222222222</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
-          <t>U11 Turnering — Baerum ishall</t>
+          <t>U10 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="G560" t="inlineStr">
         <is>
-          <t>U11 • Vert: Jutul • Lag: Jutul Grønn, Frisk Asker 4, Jar Svart, Jar Hvit, Holmen Hockey Rød, Tønsberg Grå • RVV-ID: rvv-0074</t>
+          <t>U10 • Vert: Frisk Asker • Lag: Frisk Asker 1, Frisk Asker 4, Holmen Hockey Rød, Ringerike 1, Frisk Asker 5, Jar Rød • RVV-ID: rvv-0135</t>
         </is>
       </c>
       <c r="H560" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="I560" t="inlineStr">
         <is>
-          <t>Holmen · Holmen Hockey Rød · U11</t>
+          <t>Frisk Asker · Frisk Asker 4 · U10</t>
         </is>
       </c>
       <c r="J560" t="inlineStr">
         <is>
-          <t>Holmen Hockey Rød</t>
+          <t>Frisk Asker 4</t>
         </is>
       </c>
       <c r="K560" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="L560" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="M560" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="N560" t="inlineStr">
         <is>
-          <t>rvv-0074</t>
+          <t>rvv-0135</t>
         </is>
       </c>
     </row>
@@ -34092,58 +34092,58 @@
         <v>46410</v>
       </c>
       <c r="B561" s="5" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.6875</v>
       </c>
       <c r="C561" s="5" t="n"/>
       <c r="D561" s="4" t="n">
         <v>46410</v>
       </c>
       <c r="E561" s="5" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7847222222222222</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
-          <t>U11 Turnering — Baerum ishall</t>
+          <t>U10 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="G561" t="inlineStr">
         <is>
-          <t>U11 • Vert: Jutul • Lag: Jutul Grønn, Frisk Asker 4, Jar Svart, Jar Hvit, Holmen Hockey Rød, Tønsberg Grå • RVV-ID: rvv-0074</t>
+          <t>U10 • Vert: Frisk Asker • Lag: Frisk Asker 1, Frisk Asker 4, Holmen Hockey Rød, Ringerike 1, Frisk Asker 5, Jar Rød • RVV-ID: rvv-0135</t>
         </is>
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="I561" t="inlineStr">
         <is>
-          <t>Jar · Jar Hvit · U11</t>
+          <t>Frisk Asker · Frisk Asker 5 · U10</t>
         </is>
       </c>
       <c r="J561" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Frisk Asker 5</t>
         </is>
       </c>
       <c r="K561" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="L561" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="M561" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="N561" t="inlineStr">
         <is>
-          <t>rvv-0074</t>
+          <t>rvv-0135</t>
         </is>
       </c>
     </row>
@@ -34152,58 +34152,58 @@
         <v>46410</v>
       </c>
       <c r="B562" s="5" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.6875</v>
       </c>
       <c r="C562" s="5" t="n"/>
       <c r="D562" s="4" t="n">
         <v>46410</v>
       </c>
       <c r="E562" s="5" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7847222222222222</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>U11 Turnering — Baerum ishall</t>
+          <t>U10 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="G562" t="inlineStr">
         <is>
-          <t>U11 • Vert: Jutul • Lag: Jutul Grønn, Frisk Asker 4, Jar Svart, Jar Hvit, Holmen Hockey Rød, Tønsberg Grå • RVV-ID: rvv-0074</t>
+          <t>U10 • Vert: Frisk Asker • Lag: Frisk Asker 1, Frisk Asker 4, Holmen Hockey Rød, Ringerike 1, Frisk Asker 5, Jar Rød • RVV-ID: rvv-0135</t>
         </is>
       </c>
       <c r="H562" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="I562" t="inlineStr">
         <is>
-          <t>Jar · Jar Svart · U11</t>
+          <t>Holmen · Holmen Hockey Rød · U10</t>
         </is>
       </c>
       <c r="J562" t="inlineStr">
         <is>
-          <t>Jar Svart</t>
+          <t>Holmen Hockey Rød</t>
         </is>
       </c>
       <c r="K562" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="L562" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="M562" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="N562" t="inlineStr">
         <is>
-          <t>rvv-0074</t>
+          <t>rvv-0135</t>
         </is>
       </c>
     </row>
@@ -34212,58 +34212,58 @@
         <v>46410</v>
       </c>
       <c r="B563" s="5" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.6875</v>
       </c>
       <c r="C563" s="5" t="n"/>
       <c r="D563" s="4" t="n">
         <v>46410</v>
       </c>
       <c r="E563" s="5" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7847222222222222</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
-          <t>U11 Turnering — Baerum ishall</t>
+          <t>U10 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="G563" t="inlineStr">
         <is>
-          <t>U11 • Vert: Jutul • Lag: Jutul Grønn, Frisk Asker 4, Jar Svart, Jar Hvit, Holmen Hockey Rød, Tønsberg Grå • RVV-ID: rvv-0074</t>
+          <t>U10 • Vert: Frisk Asker • Lag: Frisk Asker 1, Frisk Asker 4, Holmen Hockey Rød, Ringerike 1, Frisk Asker 5, Jar Rød • RVV-ID: rvv-0135</t>
         </is>
       </c>
       <c r="H563" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="I563" t="inlineStr">
         <is>
-          <t>Jutul · Jutul Grønn · U11</t>
+          <t>Jar · Jar Rød · U10</t>
         </is>
       </c>
       <c r="J563" t="inlineStr">
         <is>
-          <t>Jutul Grønn</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="K563" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="L563" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="M563" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="N563" t="inlineStr">
         <is>
-          <t>rvv-0074</t>
+          <t>rvv-0135</t>
         </is>
       </c>
     </row>
@@ -34272,58 +34272,58 @@
         <v>46410</v>
       </c>
       <c r="B564" s="5" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.6875</v>
       </c>
       <c r="C564" s="5" t="n"/>
       <c r="D564" s="4" t="n">
         <v>46410</v>
       </c>
       <c r="E564" s="5" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7847222222222222</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
-          <t>U11 Turnering — Baerum ishall</t>
+          <t>U10 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="G564" t="inlineStr">
         <is>
-          <t>U11 • Vert: Jutul • Lag: Jutul Grønn, Frisk Asker 4, Jar Svart, Jar Hvit, Holmen Hockey Rød, Tønsberg Grå • RVV-ID: rvv-0074</t>
+          <t>U10 • Vert: Frisk Asker • Lag: Frisk Asker 1, Frisk Asker 4, Holmen Hockey Rød, Ringerike 1, Frisk Asker 5, Jar Rød • RVV-ID: rvv-0135</t>
         </is>
       </c>
       <c r="H564" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="I564" t="inlineStr">
         <is>
-          <t>Tønsberg · Tønsberg Grå · U11</t>
+          <t>Ringerike · Ringerike 1 · U10</t>
         </is>
       </c>
       <c r="J564" t="inlineStr">
         <is>
-          <t>Tønsberg Grå</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="K564" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="L564" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="M564" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="N564" t="inlineStr">
         <is>
-          <t>rvv-0074</t>
+          <t>rvv-0135</t>
         </is>
       </c>
     </row>
@@ -34339,31 +34339,31 @@
         <v>46410</v>
       </c>
       <c r="E565" s="5" t="n">
-        <v>0.7847222222222222</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
-          <t>U10 Turnering — Askerhallen</t>
+          <t>U11 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="G565" t="inlineStr">
         <is>
-          <t>U10 • Vert: Frisk Asker • Lag: Frisk Asker 1, Frisk Asker 4, Holmen Hockey Rød, Ringerike 1, Frisk Asker 5, Jar Rød • RVV-ID: rvv-0135</t>
+          <t>U11 • Vert: Jutul • Lag: Jutul Grønn, Frisk Asker 4, Jar Svart, Jar Hvit, Holmen Hockey Rød, Tønsberg Grå • RVV-ID: rvv-0074</t>
         </is>
       </c>
       <c r="H565" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="I565" t="inlineStr">
         <is>
-          <t>Frisk Asker · Frisk Asker 1 · U10</t>
+          <t>Frisk Asker · Frisk Asker 4 · U11</t>
         </is>
       </c>
       <c r="J565" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Frisk Asker 4</t>
         </is>
       </c>
       <c r="K565" t="inlineStr">
@@ -34373,17 +34373,17 @@
       </c>
       <c r="L565" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="M565" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="N565" t="inlineStr">
         <is>
-          <t>rvv-0135</t>
+          <t>rvv-0074</t>
         </is>
       </c>
     </row>
@@ -34399,51 +34399,51 @@
         <v>46410</v>
       </c>
       <c r="E566" s="5" t="n">
-        <v>0.7847222222222222</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
-          <t>U10 Turnering — Askerhallen</t>
+          <t>U11 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="G566" t="inlineStr">
         <is>
-          <t>U10 • Vert: Frisk Asker • Lag: Frisk Asker 1, Frisk Asker 4, Holmen Hockey Rød, Ringerike 1, Frisk Asker 5, Jar Rød • RVV-ID: rvv-0135</t>
+          <t>U11 • Vert: Jutul • Lag: Jutul Grønn, Frisk Asker 4, Jar Svart, Jar Hvit, Holmen Hockey Rød, Tønsberg Grå • RVV-ID: rvv-0074</t>
         </is>
       </c>
       <c r="H566" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="I566" t="inlineStr">
         <is>
-          <t>Frisk Asker · Frisk Asker 4 · U10</t>
+          <t>Holmen · Holmen Hockey Rød · U11</t>
         </is>
       </c>
       <c r="J566" t="inlineStr">
         <is>
-          <t>Frisk Asker 4</t>
+          <t>Holmen Hockey Rød</t>
         </is>
       </c>
       <c r="K566" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="L566" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="M566" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="N566" t="inlineStr">
         <is>
-          <t>rvv-0135</t>
+          <t>rvv-0074</t>
         </is>
       </c>
     </row>
@@ -34459,51 +34459,51 @@
         <v>46410</v>
       </c>
       <c r="E567" s="5" t="n">
-        <v>0.7847222222222222</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
-          <t>U10 Turnering — Askerhallen</t>
+          <t>U11 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="G567" t="inlineStr">
         <is>
-          <t>U10 • Vert: Frisk Asker • Lag: Frisk Asker 1, Frisk Asker 4, Holmen Hockey Rød, Ringerike 1, Frisk Asker 5, Jar Rød • RVV-ID: rvv-0135</t>
+          <t>U11 • Vert: Jutul • Lag: Jutul Grønn, Frisk Asker 4, Jar Svart, Jar Hvit, Holmen Hockey Rød, Tønsberg Grå • RVV-ID: rvv-0074</t>
         </is>
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="I567" t="inlineStr">
         <is>
-          <t>Frisk Asker · Frisk Asker 5 · U10</t>
+          <t>Jar · Jar Hvit · U11</t>
         </is>
       </c>
       <c r="J567" t="inlineStr">
         <is>
-          <t>Frisk Asker 5</t>
+          <t>Jar Hvit</t>
         </is>
       </c>
       <c r="K567" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="L567" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="M567" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="N567" t="inlineStr">
         <is>
-          <t>rvv-0135</t>
+          <t>rvv-0074</t>
         </is>
       </c>
     </row>
@@ -34519,51 +34519,51 @@
         <v>46410</v>
       </c>
       <c r="E568" s="5" t="n">
-        <v>0.7847222222222222</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
-          <t>U10 Turnering — Askerhallen</t>
+          <t>U11 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="G568" t="inlineStr">
         <is>
-          <t>U10 • Vert: Frisk Asker • Lag: Frisk Asker 1, Frisk Asker 4, Holmen Hockey Rød, Ringerike 1, Frisk Asker 5, Jar Rød • RVV-ID: rvv-0135</t>
+          <t>U11 • Vert: Jutul • Lag: Jutul Grønn, Frisk Asker 4, Jar Svart, Jar Hvit, Holmen Hockey Rød, Tønsberg Grå • RVV-ID: rvv-0074</t>
         </is>
       </c>
       <c r="H568" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="I568" t="inlineStr">
         <is>
-          <t>Holmen · Holmen Hockey Rød · U10</t>
+          <t>Jar · Jar Svart · U11</t>
         </is>
       </c>
       <c r="J568" t="inlineStr">
         <is>
-          <t>Holmen Hockey Rød</t>
+          <t>Jar Svart</t>
         </is>
       </c>
       <c r="K568" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="L568" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="M568" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="N568" t="inlineStr">
         <is>
-          <t>rvv-0135</t>
+          <t>rvv-0074</t>
         </is>
       </c>
     </row>
@@ -34579,51 +34579,51 @@
         <v>46410</v>
       </c>
       <c r="E569" s="5" t="n">
-        <v>0.7847222222222222</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
-          <t>U10 Turnering — Askerhallen</t>
+          <t>U11 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="G569" t="inlineStr">
         <is>
-          <t>U10 • Vert: Frisk Asker • Lag: Frisk Asker 1, Frisk Asker 4, Holmen Hockey Rød, Ringerike 1, Frisk Asker 5, Jar Rød • RVV-ID: rvv-0135</t>
+          <t>U11 • Vert: Jutul • Lag: Jutul Grønn, Frisk Asker 4, Jar Svart, Jar Hvit, Holmen Hockey Rød, Tønsberg Grå • RVV-ID: rvv-0074</t>
         </is>
       </c>
       <c r="H569" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="I569" t="inlineStr">
         <is>
-          <t>Jar · Jar Rød · U10</t>
+          <t>Jutul · Jutul Grønn · U11</t>
         </is>
       </c>
       <c r="J569" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Jutul Grønn</t>
         </is>
       </c>
       <c r="K569" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="L569" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="M569" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="N569" t="inlineStr">
         <is>
-          <t>rvv-0135</t>
+          <t>rvv-0074</t>
         </is>
       </c>
     </row>
@@ -34639,51 +34639,51 @@
         <v>46410</v>
       </c>
       <c r="E570" s="5" t="n">
-        <v>0.7847222222222222</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
-          <t>U10 Turnering — Askerhallen</t>
+          <t>U11 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="G570" t="inlineStr">
         <is>
-          <t>U10 • Vert: Frisk Asker • Lag: Frisk Asker 1, Frisk Asker 4, Holmen Hockey Rød, Ringerike 1, Frisk Asker 5, Jar Rød • RVV-ID: rvv-0135</t>
+          <t>U11 • Vert: Jutul • Lag: Jutul Grønn, Frisk Asker 4, Jar Svart, Jar Hvit, Holmen Hockey Rød, Tønsberg Grå • RVV-ID: rvv-0074</t>
         </is>
       </c>
       <c r="H570" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="I570" t="inlineStr">
         <is>
-          <t>Ringerike · Ringerike 1 · U10</t>
+          <t>Tønsberg · Tønsberg Grå · U11</t>
         </is>
       </c>
       <c r="J570" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Tønsberg Grå</t>
         </is>
       </c>
       <c r="K570" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="L570" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="M570" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="N570" t="inlineStr">
         <is>
-          <t>rvv-0135</t>
+          <t>rvv-0074</t>
         </is>
       </c>
     </row>
@@ -34999,7 +34999,7 @@
         <v>46411</v>
       </c>
       <c r="E576" s="5" t="n">
-        <v>0.5763888888888888</v>
+        <v>0.5972222222222222</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -35059,7 +35059,7 @@
         <v>46411</v>
       </c>
       <c r="E577" s="5" t="n">
-        <v>0.5763888888888888</v>
+        <v>0.5972222222222222</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -35119,7 +35119,7 @@
         <v>46411</v>
       </c>
       <c r="E578" s="5" t="n">
-        <v>0.5763888888888888</v>
+        <v>0.5972222222222222</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -35179,7 +35179,7 @@
         <v>46411</v>
       </c>
       <c r="E579" s="5" t="n">
-        <v>0.5763888888888888</v>
+        <v>0.5972222222222222</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -35239,7 +35239,7 @@
         <v>46411</v>
       </c>
       <c r="E580" s="5" t="n">
-        <v>0.5763888888888888</v>
+        <v>0.5972222222222222</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -35299,7 +35299,7 @@
         <v>46411</v>
       </c>
       <c r="E581" s="5" t="n">
-        <v>0.5763888888888888</v>
+        <v>0.5972222222222222</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -35359,7 +35359,7 @@
         <v>46411</v>
       </c>
       <c r="E582" s="5" t="n">
-        <v>0.5895833333333333</v>
+        <v>0.5902777777777778</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -35419,7 +35419,7 @@
         <v>46411</v>
       </c>
       <c r="E583" s="5" t="n">
-        <v>0.5895833333333333</v>
+        <v>0.5902777777777778</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -35479,7 +35479,7 @@
         <v>46411</v>
       </c>
       <c r="E584" s="5" t="n">
-        <v>0.5895833333333333</v>
+        <v>0.5902777777777778</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -35539,7 +35539,7 @@
         <v>46411</v>
       </c>
       <c r="E585" s="5" t="n">
-        <v>0.5895833333333333</v>
+        <v>0.5902777777777778</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -35959,7 +35959,7 @@
         <v>46411</v>
       </c>
       <c r="E592" s="5" t="n">
-        <v>0.7006944444444444</v>
+        <v>0.7013888888888888</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -36019,7 +36019,7 @@
         <v>46411</v>
       </c>
       <c r="E593" s="5" t="n">
-        <v>0.7006944444444444</v>
+        <v>0.7013888888888888</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -36079,7 +36079,7 @@
         <v>46411</v>
       </c>
       <c r="E594" s="5" t="n">
-        <v>0.7006944444444444</v>
+        <v>0.7013888888888888</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -36139,7 +36139,7 @@
         <v>46411</v>
       </c>
       <c r="E595" s="5" t="n">
-        <v>0.7006944444444444</v>
+        <v>0.7013888888888888</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -36199,7 +36199,7 @@
         <v>46411</v>
       </c>
       <c r="E596" s="5" t="n">
-        <v>0.7006944444444444</v>
+        <v>0.7013888888888888</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -36259,7 +36259,7 @@
         <v>46411</v>
       </c>
       <c r="E597" s="5" t="n">
-        <v>0.7006944444444444</v>
+        <v>0.7013888888888888</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -36319,7 +36319,7 @@
         <v>46411</v>
       </c>
       <c r="E598" s="5" t="n">
-        <v>0.7006944444444444</v>
+        <v>0.7013888888888888</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -36379,7 +36379,7 @@
         <v>46411</v>
       </c>
       <c r="E599" s="5" t="n">
-        <v>0.7006944444444444</v>
+        <v>0.7013888888888888</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -39799,7 +39799,7 @@
         <v>46418</v>
       </c>
       <c r="E656" s="5" t="n">
-        <v>0.63125</v>
+        <v>0.6319444444444444</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -39859,7 +39859,7 @@
         <v>46418</v>
       </c>
       <c r="E657" s="5" t="n">
-        <v>0.63125</v>
+        <v>0.6319444444444444</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -39919,7 +39919,7 @@
         <v>46418</v>
       </c>
       <c r="E658" s="5" t="n">
-        <v>0.63125</v>
+        <v>0.6319444444444444</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -39979,7 +39979,7 @@
         <v>46418</v>
       </c>
       <c r="E659" s="5" t="n">
-        <v>0.63125</v>
+        <v>0.6319444444444444</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -40039,7 +40039,7 @@
         <v>46418</v>
       </c>
       <c r="E660" s="5" t="n">
-        <v>0.6805555555555556</v>
+        <v>0.7013888888888888</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -40099,7 +40099,7 @@
         <v>46418</v>
       </c>
       <c r="E661" s="5" t="n">
-        <v>0.6805555555555556</v>
+        <v>0.7013888888888888</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -40159,7 +40159,7 @@
         <v>46418</v>
       </c>
       <c r="E662" s="5" t="n">
-        <v>0.6805555555555556</v>
+        <v>0.7013888888888888</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -40219,7 +40219,7 @@
         <v>46418</v>
       </c>
       <c r="E663" s="5" t="n">
-        <v>0.6805555555555556</v>
+        <v>0.7013888888888888</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -40279,7 +40279,7 @@
         <v>46418</v>
       </c>
       <c r="E664" s="5" t="n">
-        <v>0.6805555555555556</v>
+        <v>0.7013888888888888</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -40339,7 +40339,7 @@
         <v>46418</v>
       </c>
       <c r="E665" s="5" t="n">
-        <v>0.6805555555555556</v>
+        <v>0.7013888888888888</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -40392,38 +40392,38 @@
         <v>46424</v>
       </c>
       <c r="B666" s="5" t="n">
-        <v>0.5625</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="C666" s="5" t="n"/>
       <c r="D666" s="4" t="n">
         <v>46424</v>
       </c>
       <c r="E666" s="5" t="n">
-        <v>0.6597222222222222</v>
+        <v>0.6180555555555556</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
-          <t>U10 Turnering — Holmen ishall</t>
+          <t>U7 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="G666" t="inlineStr">
         <is>
-          <t>U10 • Vert: Holmen • Lag: Holmen Hockey Hvit, Frisk Asker 6, Jar Blå, Jutul Hvit, Ringerike 4, Kongsberg • RVV-ID: rvv-0131</t>
+          <t>U7 • Vert: Frisk Asker • Lag: Frisk Asker 1, Jar Grønn, Jar Blå, Holmen Hockey Hvit, Jar Hvit, Jutul Grønn, Sandefjord, Holmen Hockey Rød • RVV-ID: rvv-0134</t>
         </is>
       </c>
       <c r="H666" t="inlineStr">
         <is>
-          <t>Holmen ishall</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="I666" t="inlineStr">
         <is>
-          <t>Frisk Asker · Frisk Asker 6 · U10</t>
+          <t>Frisk Asker · Frisk Asker 1 · U7</t>
         </is>
       </c>
       <c r="J666" t="inlineStr">
         <is>
-          <t>Frisk Asker 6</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="K666" t="inlineStr">
@@ -40433,17 +40433,17 @@
       </c>
       <c r="L666" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U7</t>
         </is>
       </c>
       <c r="M666" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="N666" t="inlineStr">
         <is>
-          <t>rvv-0131</t>
+          <t>rvv-0134</t>
         </is>
       </c>
     </row>
@@ -40452,33 +40452,33 @@
         <v>46424</v>
       </c>
       <c r="B667" s="5" t="n">
-        <v>0.5625</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="C667" s="5" t="n"/>
       <c r="D667" s="4" t="n">
         <v>46424</v>
       </c>
       <c r="E667" s="5" t="n">
-        <v>0.6597222222222222</v>
+        <v>0.6180555555555556</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
-          <t>U10 Turnering — Holmen ishall</t>
+          <t>U7 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="G667" t="inlineStr">
         <is>
-          <t>U10 • Vert: Holmen • Lag: Holmen Hockey Hvit, Frisk Asker 6, Jar Blå, Jutul Hvit, Ringerike 4, Kongsberg • RVV-ID: rvv-0131</t>
+          <t>U7 • Vert: Frisk Asker • Lag: Frisk Asker 1, Jar Grønn, Jar Blå, Holmen Hockey Hvit, Jar Hvit, Jutul Grønn, Sandefjord, Holmen Hockey Rød • RVV-ID: rvv-0134</t>
         </is>
       </c>
       <c r="H667" t="inlineStr">
         <is>
-          <t>Holmen ishall</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="I667" t="inlineStr">
         <is>
-          <t>Holmen · Holmen Hockey Hvit · U10</t>
+          <t>Holmen · Holmen Hockey Hvit · U7</t>
         </is>
       </c>
       <c r="J667" t="inlineStr">
@@ -40493,17 +40493,17 @@
       </c>
       <c r="L667" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U7</t>
         </is>
       </c>
       <c r="M667" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="N667" t="inlineStr">
         <is>
-          <t>rvv-0131</t>
+          <t>rvv-0134</t>
         </is>
       </c>
     </row>
@@ -40512,58 +40512,58 @@
         <v>46424</v>
       </c>
       <c r="B668" s="5" t="n">
-        <v>0.5625</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="C668" s="5" t="n"/>
       <c r="D668" s="4" t="n">
         <v>46424</v>
       </c>
       <c r="E668" s="5" t="n">
-        <v>0.6597222222222222</v>
+        <v>0.6180555555555556</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
-          <t>U10 Turnering — Holmen ishall</t>
+          <t>U7 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="G668" t="inlineStr">
         <is>
-          <t>U10 • Vert: Holmen • Lag: Holmen Hockey Hvit, Frisk Asker 6, Jar Blå, Jutul Hvit, Ringerike 4, Kongsberg • RVV-ID: rvv-0131</t>
+          <t>U7 • Vert: Frisk Asker • Lag: Frisk Asker 1, Jar Grønn, Jar Blå, Holmen Hockey Hvit, Jar Hvit, Jutul Grønn, Sandefjord, Holmen Hockey Rød • RVV-ID: rvv-0134</t>
         </is>
       </c>
       <c r="H668" t="inlineStr">
         <is>
-          <t>Holmen ishall</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="I668" t="inlineStr">
         <is>
-          <t>Jar · Jar Blå · U10</t>
+          <t>Holmen · Holmen Hockey Rød · U7</t>
         </is>
       </c>
       <c r="J668" t="inlineStr">
         <is>
-          <t>Jar Blå</t>
+          <t>Holmen Hockey Rød</t>
         </is>
       </c>
       <c r="K668" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="L668" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U7</t>
         </is>
       </c>
       <c r="M668" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="N668" t="inlineStr">
         <is>
-          <t>rvv-0131</t>
+          <t>rvv-0134</t>
         </is>
       </c>
     </row>
@@ -40572,58 +40572,58 @@
         <v>46424</v>
       </c>
       <c r="B669" s="5" t="n">
-        <v>0.5625</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="C669" s="5" t="n"/>
       <c r="D669" s="4" t="n">
         <v>46424</v>
       </c>
       <c r="E669" s="5" t="n">
-        <v>0.6597222222222222</v>
+        <v>0.6180555555555556</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
-          <t>U10 Turnering — Holmen ishall</t>
+          <t>U7 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="G669" t="inlineStr">
         <is>
-          <t>U10 • Vert: Holmen • Lag: Holmen Hockey Hvit, Frisk Asker 6, Jar Blå, Jutul Hvit, Ringerike 4, Kongsberg • RVV-ID: rvv-0131</t>
+          <t>U7 • Vert: Frisk Asker • Lag: Frisk Asker 1, Jar Grønn, Jar Blå, Holmen Hockey Hvit, Jar Hvit, Jutul Grønn, Sandefjord, Holmen Hockey Rød • RVV-ID: rvv-0134</t>
         </is>
       </c>
       <c r="H669" t="inlineStr">
         <is>
-          <t>Holmen ishall</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="I669" t="inlineStr">
         <is>
-          <t>Jutul · Jutul Hvit · U10</t>
+          <t>Jar · Jar Blå · U7</t>
         </is>
       </c>
       <c r="J669" t="inlineStr">
         <is>
-          <t>Jutul Hvit</t>
+          <t>Jar Blå</t>
         </is>
       </c>
       <c r="K669" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="L669" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U7</t>
         </is>
       </c>
       <c r="M669" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="N669" t="inlineStr">
         <is>
-          <t>rvv-0131</t>
+          <t>rvv-0134</t>
         </is>
       </c>
     </row>
@@ -40632,58 +40632,58 @@
         <v>46424</v>
       </c>
       <c r="B670" s="5" t="n">
-        <v>0.5625</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="C670" s="5" t="n"/>
       <c r="D670" s="4" t="n">
         <v>46424</v>
       </c>
       <c r="E670" s="5" t="n">
-        <v>0.6597222222222222</v>
+        <v>0.6180555555555556</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
-          <t>U10 Turnering — Holmen ishall</t>
+          <t>U7 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="G670" t="inlineStr">
         <is>
-          <t>U10 • Vert: Holmen • Lag: Holmen Hockey Hvit, Frisk Asker 6, Jar Blå, Jutul Hvit, Ringerike 4, Kongsberg • RVV-ID: rvv-0131</t>
+          <t>U7 • Vert: Frisk Asker • Lag: Frisk Asker 1, Jar Grønn, Jar Blå, Holmen Hockey Hvit, Jar Hvit, Jutul Grønn, Sandefjord, Holmen Hockey Rød • RVV-ID: rvv-0134</t>
         </is>
       </c>
       <c r="H670" t="inlineStr">
         <is>
-          <t>Holmen ishall</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="I670" t="inlineStr">
         <is>
-          <t>Kongsberg · Kongsberg · U10</t>
+          <t>Jar · Jar Grønn · U7</t>
         </is>
       </c>
       <c r="J670" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Jar Grønn</t>
         </is>
       </c>
       <c r="K670" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="L670" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U7</t>
         </is>
       </c>
       <c r="M670" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="N670" t="inlineStr">
         <is>
-          <t>rvv-0131</t>
+          <t>rvv-0134</t>
         </is>
       </c>
     </row>
@@ -40692,58 +40692,58 @@
         <v>46424</v>
       </c>
       <c r="B671" s="5" t="n">
-        <v>0.5625</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="C671" s="5" t="n"/>
       <c r="D671" s="4" t="n">
         <v>46424</v>
       </c>
       <c r="E671" s="5" t="n">
-        <v>0.6597222222222222</v>
+        <v>0.6180555555555556</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
-          <t>U10 Turnering — Holmen ishall</t>
+          <t>U7 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="G671" t="inlineStr">
         <is>
-          <t>U10 • Vert: Holmen • Lag: Holmen Hockey Hvit, Frisk Asker 6, Jar Blå, Jutul Hvit, Ringerike 4, Kongsberg • RVV-ID: rvv-0131</t>
+          <t>U7 • Vert: Frisk Asker • Lag: Frisk Asker 1, Jar Grønn, Jar Blå, Holmen Hockey Hvit, Jar Hvit, Jutul Grønn, Sandefjord, Holmen Hockey Rød • RVV-ID: rvv-0134</t>
         </is>
       </c>
       <c r="H671" t="inlineStr">
         <is>
-          <t>Holmen ishall</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="I671" t="inlineStr">
         <is>
-          <t>Ringerike · Ringerike 4 · U10</t>
+          <t>Jar · Jar Hvit · U7</t>
         </is>
       </c>
       <c r="J671" t="inlineStr">
         <is>
-          <t>Ringerike 4</t>
+          <t>Jar Hvit</t>
         </is>
       </c>
       <c r="K671" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="L671" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U7</t>
         </is>
       </c>
       <c r="M671" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="N671" t="inlineStr">
         <is>
-          <t>rvv-0131</t>
+          <t>rvv-0134</t>
         </is>
       </c>
     </row>
@@ -40752,58 +40752,58 @@
         <v>46424</v>
       </c>
       <c r="B672" s="5" t="n">
-        <v>0.5625</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="C672" s="5" t="n"/>
       <c r="D672" s="4" t="n">
         <v>46424</v>
       </c>
       <c r="E672" s="5" t="n">
-        <v>0.6319444444444444</v>
+        <v>0.6180555555555556</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
-          <t>U12 Turnering — Jar Isforum</t>
+          <t>U7 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="G672" t="inlineStr">
         <is>
-          <t>U12 • Vert: Jar • Lag: Jar Blå, Frisk Asker 2, Tønsberg Rød, Jutul Rød • RVV-ID: rvv-0133</t>
+          <t>U7 • Vert: Frisk Asker • Lag: Frisk Asker 1, Jar Grønn, Jar Blå, Holmen Hockey Hvit, Jar Hvit, Jutul Grønn, Sandefjord, Holmen Hockey Rød • RVV-ID: rvv-0134</t>
         </is>
       </c>
       <c r="H672" t="inlineStr">
         <is>
-          <t>Jar Isforum</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="I672" t="inlineStr">
         <is>
-          <t>Frisk Asker · Frisk Asker 2 · U12</t>
+          <t>Jutul · Jutul Grønn · U7</t>
         </is>
       </c>
       <c r="J672" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Jutul Grønn</t>
         </is>
       </c>
       <c r="K672" t="inlineStr">
         <is>
+          <t>Jutul</t>
+        </is>
+      </c>
+      <c r="L672" t="inlineStr">
+        <is>
+          <t>U7</t>
+        </is>
+      </c>
+      <c r="M672" t="inlineStr">
+        <is>
           <t>Frisk Asker</t>
         </is>
       </c>
-      <c r="L672" t="inlineStr">
-        <is>
-          <t>U12</t>
-        </is>
-      </c>
-      <c r="M672" t="inlineStr">
-        <is>
-          <t>Jar</t>
-        </is>
-      </c>
       <c r="N672" t="inlineStr">
         <is>
-          <t>rvv-0133</t>
+          <t>rvv-0134</t>
         </is>
       </c>
     </row>
@@ -40812,58 +40812,58 @@
         <v>46424</v>
       </c>
       <c r="B673" s="5" t="n">
-        <v>0.5625</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="C673" s="5" t="n"/>
       <c r="D673" s="4" t="n">
         <v>46424</v>
       </c>
       <c r="E673" s="5" t="n">
-        <v>0.6319444444444444</v>
+        <v>0.6180555555555556</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
-          <t>U12 Turnering — Jar Isforum</t>
+          <t>U7 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="G673" t="inlineStr">
         <is>
-          <t>U12 • Vert: Jar • Lag: Jar Blå, Frisk Asker 2, Tønsberg Rød, Jutul Rød • RVV-ID: rvv-0133</t>
+          <t>U7 • Vert: Frisk Asker • Lag: Frisk Asker 1, Jar Grønn, Jar Blå, Holmen Hockey Hvit, Jar Hvit, Jutul Grønn, Sandefjord, Holmen Hockey Rød • RVV-ID: rvv-0134</t>
         </is>
       </c>
       <c r="H673" t="inlineStr">
         <is>
-          <t>Jar Isforum</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="I673" t="inlineStr">
         <is>
-          <t>Jar · Jar Blå · U12</t>
+          <t>Sandefjord Penguins · Sandefjord · U7</t>
         </is>
       </c>
       <c r="J673" t="inlineStr">
         <is>
-          <t>Jar Blå</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="K673" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Sandefjord Penguins</t>
         </is>
       </c>
       <c r="L673" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U7</t>
         </is>
       </c>
       <c r="M673" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="N673" t="inlineStr">
         <is>
-          <t>rvv-0133</t>
+          <t>rvv-0134</t>
         </is>
       </c>
     </row>
@@ -40879,51 +40879,51 @@
         <v>46424</v>
       </c>
       <c r="E674" s="5" t="n">
-        <v>0.6319444444444444</v>
+        <v>0.6597222222222222</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
-          <t>U12 Turnering — Jar Isforum</t>
+          <t>U10 Turnering — Holmen ishall</t>
         </is>
       </c>
       <c r="G674" t="inlineStr">
         <is>
-          <t>U12 • Vert: Jar • Lag: Jar Blå, Frisk Asker 2, Tønsberg Rød, Jutul Rød • RVV-ID: rvv-0133</t>
+          <t>U10 • Vert: Holmen • Lag: Holmen Hockey Hvit, Frisk Asker 6, Jar Blå, Jutul Hvit, Ringerike 4, Kongsberg • RVV-ID: rvv-0131</t>
         </is>
       </c>
       <c r="H674" t="inlineStr">
         <is>
-          <t>Jar Isforum</t>
+          <t>Holmen ishall</t>
         </is>
       </c>
       <c r="I674" t="inlineStr">
         <is>
-          <t>Jutul · Jutul Rød · U12</t>
+          <t>Frisk Asker · Frisk Asker 6 · U10</t>
         </is>
       </c>
       <c r="J674" t="inlineStr">
         <is>
-          <t>Jutul Rød</t>
+          <t>Frisk Asker 6</t>
         </is>
       </c>
       <c r="K674" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="L674" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="M674" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="N674" t="inlineStr">
         <is>
-          <t>rvv-0133</t>
+          <t>rvv-0131</t>
         </is>
       </c>
     </row>
@@ -40939,51 +40939,51 @@
         <v>46424</v>
       </c>
       <c r="E675" s="5" t="n">
-        <v>0.6319444444444444</v>
+        <v>0.6597222222222222</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
-          <t>U12 Turnering — Jar Isforum</t>
+          <t>U10 Turnering — Holmen ishall</t>
         </is>
       </c>
       <c r="G675" t="inlineStr">
         <is>
-          <t>U12 • Vert: Jar • Lag: Jar Blå, Frisk Asker 2, Tønsberg Rød, Jutul Rød • RVV-ID: rvv-0133</t>
+          <t>U10 • Vert: Holmen • Lag: Holmen Hockey Hvit, Frisk Asker 6, Jar Blå, Jutul Hvit, Ringerike 4, Kongsberg • RVV-ID: rvv-0131</t>
         </is>
       </c>
       <c r="H675" t="inlineStr">
         <is>
-          <t>Jar Isforum</t>
+          <t>Holmen ishall</t>
         </is>
       </c>
       <c r="I675" t="inlineStr">
         <is>
-          <t>Tønsberg · Tønsberg Rød · U12</t>
+          <t>Holmen · Holmen Hockey Hvit · U10</t>
         </is>
       </c>
       <c r="J675" t="inlineStr">
         <is>
-          <t>Tønsberg Rød</t>
+          <t>Holmen Hockey Hvit</t>
         </is>
       </c>
       <c r="K675" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="L675" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="M675" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="N675" t="inlineStr">
         <is>
-          <t>rvv-0133</t>
+          <t>rvv-0131</t>
         </is>
       </c>
     </row>
@@ -40999,51 +40999,51 @@
         <v>46424</v>
       </c>
       <c r="E676" s="5" t="n">
-        <v>0.6388888888888888</v>
+        <v>0.6597222222222222</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
-          <t>U7 Turnering — Askerhallen</t>
+          <t>U10 Turnering — Holmen ishall</t>
         </is>
       </c>
       <c r="G676" t="inlineStr">
         <is>
-          <t>U7 • Vert: Frisk Asker • Lag: Frisk Asker 1, Jar Grønn, Jar Blå, Holmen Hockey Hvit, Jar Hvit, Jutul Grønn, Sandefjord, Holmen Hockey Rød • RVV-ID: rvv-0134</t>
+          <t>U10 • Vert: Holmen • Lag: Holmen Hockey Hvit, Frisk Asker 6, Jar Blå, Jutul Hvit, Ringerike 4, Kongsberg • RVV-ID: rvv-0131</t>
         </is>
       </c>
       <c r="H676" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Holmen ishall</t>
         </is>
       </c>
       <c r="I676" t="inlineStr">
         <is>
-          <t>Frisk Asker · Frisk Asker 1 · U7</t>
+          <t>Jar · Jar Blå · U10</t>
         </is>
       </c>
       <c r="J676" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Jar Blå</t>
         </is>
       </c>
       <c r="K676" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="L676" t="inlineStr">
         <is>
-          <t>U7</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="M676" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="N676" t="inlineStr">
         <is>
-          <t>rvv-0134</t>
+          <t>rvv-0131</t>
         </is>
       </c>
     </row>
@@ -41059,51 +41059,51 @@
         <v>46424</v>
       </c>
       <c r="E677" s="5" t="n">
-        <v>0.6388888888888888</v>
+        <v>0.6597222222222222</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
-          <t>U7 Turnering — Askerhallen</t>
+          <t>U10 Turnering — Holmen ishall</t>
         </is>
       </c>
       <c r="G677" t="inlineStr">
         <is>
-          <t>U7 • Vert: Frisk Asker • Lag: Frisk Asker 1, Jar Grønn, Jar Blå, Holmen Hockey Hvit, Jar Hvit, Jutul Grønn, Sandefjord, Holmen Hockey Rød • RVV-ID: rvv-0134</t>
+          <t>U10 • Vert: Holmen • Lag: Holmen Hockey Hvit, Frisk Asker 6, Jar Blå, Jutul Hvit, Ringerike 4, Kongsberg • RVV-ID: rvv-0131</t>
         </is>
       </c>
       <c r="H677" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Holmen ishall</t>
         </is>
       </c>
       <c r="I677" t="inlineStr">
         <is>
-          <t>Holmen · Holmen Hockey Hvit · U7</t>
+          <t>Jutul · Jutul Hvit · U10</t>
         </is>
       </c>
       <c r="J677" t="inlineStr">
         <is>
-          <t>Holmen Hockey Hvit</t>
+          <t>Jutul Hvit</t>
         </is>
       </c>
       <c r="K677" t="inlineStr">
         <is>
+          <t>Jutul</t>
+        </is>
+      </c>
+      <c r="L677" t="inlineStr">
+        <is>
+          <t>U10</t>
+        </is>
+      </c>
+      <c r="M677" t="inlineStr">
+        <is>
           <t>Holmen</t>
         </is>
       </c>
-      <c r="L677" t="inlineStr">
-        <is>
-          <t>U7</t>
-        </is>
-      </c>
-      <c r="M677" t="inlineStr">
-        <is>
-          <t>Frisk Asker</t>
-        </is>
-      </c>
       <c r="N677" t="inlineStr">
         <is>
-          <t>rvv-0134</t>
+          <t>rvv-0131</t>
         </is>
       </c>
     </row>
@@ -41119,51 +41119,51 @@
         <v>46424</v>
       </c>
       <c r="E678" s="5" t="n">
-        <v>0.6388888888888888</v>
+        <v>0.6597222222222222</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
-          <t>U7 Turnering — Askerhallen</t>
+          <t>U10 Turnering — Holmen ishall</t>
         </is>
       </c>
       <c r="G678" t="inlineStr">
         <is>
-          <t>U7 • Vert: Frisk Asker • Lag: Frisk Asker 1, Jar Grønn, Jar Blå, Holmen Hockey Hvit, Jar Hvit, Jutul Grønn, Sandefjord, Holmen Hockey Rød • RVV-ID: rvv-0134</t>
+          <t>U10 • Vert: Holmen • Lag: Holmen Hockey Hvit, Frisk Asker 6, Jar Blå, Jutul Hvit, Ringerike 4, Kongsberg • RVV-ID: rvv-0131</t>
         </is>
       </c>
       <c r="H678" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Holmen ishall</t>
         </is>
       </c>
       <c r="I678" t="inlineStr">
         <is>
-          <t>Holmen · Holmen Hockey Rød · U7</t>
+          <t>Kongsberg · Kongsberg · U10</t>
         </is>
       </c>
       <c r="J678" t="inlineStr">
         <is>
-          <t>Holmen Hockey Rød</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="K678" t="inlineStr">
         <is>
+          <t>Kongsberg</t>
+        </is>
+      </c>
+      <c r="L678" t="inlineStr">
+        <is>
+          <t>U10</t>
+        </is>
+      </c>
+      <c r="M678" t="inlineStr">
+        <is>
           <t>Holmen</t>
         </is>
       </c>
-      <c r="L678" t="inlineStr">
-        <is>
-          <t>U7</t>
-        </is>
-      </c>
-      <c r="M678" t="inlineStr">
-        <is>
-          <t>Frisk Asker</t>
-        </is>
-      </c>
       <c r="N678" t="inlineStr">
         <is>
-          <t>rvv-0134</t>
+          <t>rvv-0131</t>
         </is>
       </c>
     </row>
@@ -41179,51 +41179,51 @@
         <v>46424</v>
       </c>
       <c r="E679" s="5" t="n">
-        <v>0.6388888888888888</v>
+        <v>0.6597222222222222</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
-          <t>U7 Turnering — Askerhallen</t>
+          <t>U10 Turnering — Holmen ishall</t>
         </is>
       </c>
       <c r="G679" t="inlineStr">
         <is>
-          <t>U7 • Vert: Frisk Asker • Lag: Frisk Asker 1, Jar Grønn, Jar Blå, Holmen Hockey Hvit, Jar Hvit, Jutul Grønn, Sandefjord, Holmen Hockey Rød • RVV-ID: rvv-0134</t>
+          <t>U10 • Vert: Holmen • Lag: Holmen Hockey Hvit, Frisk Asker 6, Jar Blå, Jutul Hvit, Ringerike 4, Kongsberg • RVV-ID: rvv-0131</t>
         </is>
       </c>
       <c r="H679" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Holmen ishall</t>
         </is>
       </c>
       <c r="I679" t="inlineStr">
         <is>
-          <t>Jar · Jar Blå · U7</t>
+          <t>Ringerike · Ringerike 4 · U10</t>
         </is>
       </c>
       <c r="J679" t="inlineStr">
         <is>
-          <t>Jar Blå</t>
+          <t>Ringerike 4</t>
         </is>
       </c>
       <c r="K679" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="L679" t="inlineStr">
         <is>
-          <t>U7</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="M679" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="N679" t="inlineStr">
         <is>
-          <t>rvv-0134</t>
+          <t>rvv-0131</t>
         </is>
       </c>
     </row>
@@ -41239,51 +41239,51 @@
         <v>46424</v>
       </c>
       <c r="E680" s="5" t="n">
-        <v>0.6388888888888888</v>
+        <v>0.6319444444444444</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
-          <t>U7 Turnering — Askerhallen</t>
+          <t>U12 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="G680" t="inlineStr">
         <is>
-          <t>U7 • Vert: Frisk Asker • Lag: Frisk Asker 1, Jar Grønn, Jar Blå, Holmen Hockey Hvit, Jar Hvit, Jutul Grønn, Sandefjord, Holmen Hockey Rød • RVV-ID: rvv-0134</t>
+          <t>U12 • Vert: Jar • Lag: Jar Blå, Frisk Asker 2, Tønsberg Rød, Jutul Rød • RVV-ID: rvv-0133</t>
         </is>
       </c>
       <c r="H680" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Jar Isforum</t>
         </is>
       </c>
       <c r="I680" t="inlineStr">
         <is>
-          <t>Jar · Jar Grønn · U7</t>
+          <t>Frisk Asker · Frisk Asker 2 · U12</t>
         </is>
       </c>
       <c r="J680" t="inlineStr">
         <is>
-          <t>Jar Grønn</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="K680" t="inlineStr">
         <is>
+          <t>Frisk Asker</t>
+        </is>
+      </c>
+      <c r="L680" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+      <c r="M680" t="inlineStr">
+        <is>
           <t>Jar</t>
         </is>
       </c>
-      <c r="L680" t="inlineStr">
-        <is>
-          <t>U7</t>
-        </is>
-      </c>
-      <c r="M680" t="inlineStr">
-        <is>
-          <t>Frisk Asker</t>
-        </is>
-      </c>
       <c r="N680" t="inlineStr">
         <is>
-          <t>rvv-0134</t>
+          <t>rvv-0133</t>
         </is>
       </c>
     </row>
@@ -41299,31 +41299,31 @@
         <v>46424</v>
       </c>
       <c r="E681" s="5" t="n">
-        <v>0.6388888888888888</v>
+        <v>0.6319444444444444</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>U7 Turnering — Askerhallen</t>
+          <t>U12 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="G681" t="inlineStr">
         <is>
-          <t>U7 • Vert: Frisk Asker • Lag: Frisk Asker 1, Jar Grønn, Jar Blå, Holmen Hockey Hvit, Jar Hvit, Jutul Grønn, Sandefjord, Holmen Hockey Rød • RVV-ID: rvv-0134</t>
+          <t>U12 • Vert: Jar • Lag: Jar Blå, Frisk Asker 2, Tønsberg Rød, Jutul Rød • RVV-ID: rvv-0133</t>
         </is>
       </c>
       <c r="H681" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Jar Isforum</t>
         </is>
       </c>
       <c r="I681" t="inlineStr">
         <is>
-          <t>Jar · Jar Hvit · U7</t>
+          <t>Jar · Jar Blå · U12</t>
         </is>
       </c>
       <c r="J681" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Jar Blå</t>
         </is>
       </c>
       <c r="K681" t="inlineStr">
@@ -41333,17 +41333,17 @@
       </c>
       <c r="L681" t="inlineStr">
         <is>
-          <t>U7</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="M681" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="N681" t="inlineStr">
         <is>
-          <t>rvv-0134</t>
+          <t>rvv-0133</t>
         </is>
       </c>
     </row>
@@ -41359,31 +41359,31 @@
         <v>46424</v>
       </c>
       <c r="E682" s="5" t="n">
-        <v>0.6388888888888888</v>
+        <v>0.6319444444444444</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
-          <t>U7 Turnering — Askerhallen</t>
+          <t>U12 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="G682" t="inlineStr">
         <is>
-          <t>U7 • Vert: Frisk Asker • Lag: Frisk Asker 1, Jar Grønn, Jar Blå, Holmen Hockey Hvit, Jar Hvit, Jutul Grønn, Sandefjord, Holmen Hockey Rød • RVV-ID: rvv-0134</t>
+          <t>U12 • Vert: Jar • Lag: Jar Blå, Frisk Asker 2, Tønsberg Rød, Jutul Rød • RVV-ID: rvv-0133</t>
         </is>
       </c>
       <c r="H682" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Jar Isforum</t>
         </is>
       </c>
       <c r="I682" t="inlineStr">
         <is>
-          <t>Jutul · Jutul Grønn · U7</t>
+          <t>Jutul · Jutul Rød · U12</t>
         </is>
       </c>
       <c r="J682" t="inlineStr">
         <is>
-          <t>Jutul Grønn</t>
+          <t>Jutul Rød</t>
         </is>
       </c>
       <c r="K682" t="inlineStr">
@@ -41393,17 +41393,17 @@
       </c>
       <c r="L682" t="inlineStr">
         <is>
-          <t>U7</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="M682" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="N682" t="inlineStr">
         <is>
-          <t>rvv-0134</t>
+          <t>rvv-0133</t>
         </is>
       </c>
     </row>
@@ -41419,51 +41419,51 @@
         <v>46424</v>
       </c>
       <c r="E683" s="5" t="n">
-        <v>0.6388888888888888</v>
+        <v>0.6319444444444444</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>U7 Turnering — Askerhallen</t>
+          <t>U12 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="G683" t="inlineStr">
         <is>
-          <t>U7 • Vert: Frisk Asker • Lag: Frisk Asker 1, Jar Grønn, Jar Blå, Holmen Hockey Hvit, Jar Hvit, Jutul Grønn, Sandefjord, Holmen Hockey Rød • RVV-ID: rvv-0134</t>
+          <t>U12 • Vert: Jar • Lag: Jar Blå, Frisk Asker 2, Tønsberg Rød, Jutul Rød • RVV-ID: rvv-0133</t>
         </is>
       </c>
       <c r="H683" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Jar Isforum</t>
         </is>
       </c>
       <c r="I683" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins · Sandefjord · U7</t>
+          <t>Tønsberg · Tønsberg Rød · U12</t>
         </is>
       </c>
       <c r="J683" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Tønsberg Rød</t>
         </is>
       </c>
       <c r="K683" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="L683" t="inlineStr">
         <is>
-          <t>U7</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="M683" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="N683" t="inlineStr">
         <is>
-          <t>rvv-0134</t>
+          <t>rvv-0133</t>
         </is>
       </c>
     </row>
@@ -41479,51 +41479,51 @@
         <v>46424</v>
       </c>
       <c r="E684" s="5" t="n">
-        <v>0.6944444444444444</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
-          <t>U12 Turnering — Schjongshallen</t>
+          <t>U11 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="G684" t="inlineStr">
         <is>
-          <t>U12 • Vert: Ringerike • Lag: Ringerike 1, Ringerike 2, Holmen Hockey Rød, Tønsberg Grå • RVV-ID: rvv-0149</t>
+          <t>U11 • Vert: Frisk Asker • Lag: Frisk Asker 1, Jar Grønn, Holmen Hockey Rød, Jar Blå, Jutul Rød, Tønsberg Grå • RVV-ID: rvv-0127</t>
         </is>
       </c>
       <c r="H684" t="inlineStr">
         <is>
-          <t>Schjongshallen</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="I684" t="inlineStr">
         <is>
-          <t>Holmen · Holmen Hockey Rød · U12</t>
+          <t>Frisk Asker · Frisk Asker 1 · U11</t>
         </is>
       </c>
       <c r="J684" t="inlineStr">
         <is>
-          <t>Holmen Hockey Rød</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="K684" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="L684" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="M684" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="N684" t="inlineStr">
         <is>
-          <t>rvv-0149</t>
+          <t>rvv-0127</t>
         </is>
       </c>
     </row>
@@ -41539,51 +41539,51 @@
         <v>46424</v>
       </c>
       <c r="E685" s="5" t="n">
-        <v>0.6944444444444444</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
-          <t>U12 Turnering — Schjongshallen</t>
+          <t>U11 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="G685" t="inlineStr">
         <is>
-          <t>U12 • Vert: Ringerike • Lag: Ringerike 1, Ringerike 2, Holmen Hockey Rød, Tønsberg Grå • RVV-ID: rvv-0149</t>
+          <t>U11 • Vert: Frisk Asker • Lag: Frisk Asker 1, Jar Grønn, Holmen Hockey Rød, Jar Blå, Jutul Rød, Tønsberg Grå • RVV-ID: rvv-0127</t>
         </is>
       </c>
       <c r="H685" t="inlineStr">
         <is>
-          <t>Schjongshallen</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="I685" t="inlineStr">
         <is>
-          <t>Ringerike · Ringerike 1 · U12</t>
+          <t>Holmen · Holmen Hockey Rød · U11</t>
         </is>
       </c>
       <c r="J685" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Holmen Hockey Rød</t>
         </is>
       </c>
       <c r="K685" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="L685" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="M685" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="N685" t="inlineStr">
         <is>
-          <t>rvv-0149</t>
+          <t>rvv-0127</t>
         </is>
       </c>
     </row>
@@ -41599,51 +41599,51 @@
         <v>46424</v>
       </c>
       <c r="E686" s="5" t="n">
-        <v>0.6944444444444444</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
-          <t>U12 Turnering — Schjongshallen</t>
+          <t>U11 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="G686" t="inlineStr">
         <is>
-          <t>U12 • Vert: Ringerike • Lag: Ringerike 1, Ringerike 2, Holmen Hockey Rød, Tønsberg Grå • RVV-ID: rvv-0149</t>
+          <t>U11 • Vert: Frisk Asker • Lag: Frisk Asker 1, Jar Grønn, Holmen Hockey Rød, Jar Blå, Jutul Rød, Tønsberg Grå • RVV-ID: rvv-0127</t>
         </is>
       </c>
       <c r="H686" t="inlineStr">
         <is>
-          <t>Schjongshallen</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="I686" t="inlineStr">
         <is>
-          <t>Ringerike · Ringerike 2 · U12</t>
+          <t>Jar · Jar Blå · U11</t>
         </is>
       </c>
       <c r="J686" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Jar Blå</t>
         </is>
       </c>
       <c r="K686" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="L686" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="M686" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="N686" t="inlineStr">
         <is>
-          <t>rvv-0149</t>
+          <t>rvv-0127</t>
         </is>
       </c>
     </row>
@@ -41659,51 +41659,51 @@
         <v>46424</v>
       </c>
       <c r="E687" s="5" t="n">
-        <v>0.6944444444444444</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
-          <t>U12 Turnering — Schjongshallen</t>
+          <t>U11 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="G687" t="inlineStr">
         <is>
-          <t>U12 • Vert: Ringerike • Lag: Ringerike 1, Ringerike 2, Holmen Hockey Rød, Tønsberg Grå • RVV-ID: rvv-0149</t>
+          <t>U11 • Vert: Frisk Asker • Lag: Frisk Asker 1, Jar Grønn, Holmen Hockey Rød, Jar Blå, Jutul Rød, Tønsberg Grå • RVV-ID: rvv-0127</t>
         </is>
       </c>
       <c r="H687" t="inlineStr">
         <is>
-          <t>Schjongshallen</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="I687" t="inlineStr">
         <is>
-          <t>Tønsberg · Tønsberg Grå · U12</t>
+          <t>Jar · Jar Grønn · U11</t>
         </is>
       </c>
       <c r="J687" t="inlineStr">
         <is>
-          <t>Tønsberg Grå</t>
+          <t>Jar Grønn</t>
         </is>
       </c>
       <c r="K687" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="L687" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="M687" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="N687" t="inlineStr">
         <is>
-          <t>rvv-0149</t>
+          <t>rvv-0127</t>
         </is>
       </c>
     </row>
@@ -41712,7 +41712,7 @@
         <v>46424</v>
       </c>
       <c r="B688" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.625</v>
       </c>
       <c r="C688" s="5" t="n"/>
       <c r="D688" s="4" t="n">
@@ -41738,17 +41738,17 @@
       </c>
       <c r="I688" t="inlineStr">
         <is>
-          <t>Frisk Asker · Frisk Asker 1 · U11</t>
+          <t>Jutul · Jutul Rød · U11</t>
         </is>
       </c>
       <c r="J688" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Jutul Rød</t>
         </is>
       </c>
       <c r="K688" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="L688" t="inlineStr">
@@ -41772,7 +41772,7 @@
         <v>46424</v>
       </c>
       <c r="B689" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.625</v>
       </c>
       <c r="C689" s="5" t="n"/>
       <c r="D689" s="4" t="n">
@@ -41798,17 +41798,17 @@
       </c>
       <c r="I689" t="inlineStr">
         <is>
-          <t>Holmen · Holmen Hockey Rød · U11</t>
+          <t>Tønsberg · Tønsberg Grå · U11</t>
         </is>
       </c>
       <c r="J689" t="inlineStr">
         <is>
-          <t>Holmen Hockey Rød</t>
+          <t>Tønsberg Grå</t>
         </is>
       </c>
       <c r="K689" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="L689" t="inlineStr">
@@ -41832,58 +41832,58 @@
         <v>46424</v>
       </c>
       <c r="B690" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.625</v>
       </c>
       <c r="C690" s="5" t="n"/>
       <c r="D690" s="4" t="n">
         <v>46424</v>
       </c>
       <c r="E690" s="5" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.6944444444444444</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
-          <t>U11 Turnering — Askerhallen</t>
+          <t>U12 Turnering — Schjongshallen</t>
         </is>
       </c>
       <c r="G690" t="inlineStr">
         <is>
-          <t>U11 • Vert: Frisk Asker • Lag: Frisk Asker 1, Jar Grønn, Holmen Hockey Rød, Jar Blå, Jutul Rød, Tønsberg Grå • RVV-ID: rvv-0127</t>
+          <t>U12 • Vert: Ringerike • Lag: Ringerike 1, Ringerike 2, Holmen Hockey Rød, Tønsberg Grå • RVV-ID: rvv-0149</t>
         </is>
       </c>
       <c r="H690" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Schjongshallen</t>
         </is>
       </c>
       <c r="I690" t="inlineStr">
         <is>
-          <t>Jar · Jar Blå · U11</t>
+          <t>Holmen · Holmen Hockey Rød · U12</t>
         </is>
       </c>
       <c r="J690" t="inlineStr">
         <is>
-          <t>Jar Blå</t>
+          <t>Holmen Hockey Rød</t>
         </is>
       </c>
       <c r="K690" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="L690" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="M690" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="N690" t="inlineStr">
         <is>
-          <t>rvv-0127</t>
+          <t>rvv-0149</t>
         </is>
       </c>
     </row>
@@ -41892,58 +41892,58 @@
         <v>46424</v>
       </c>
       <c r="B691" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.625</v>
       </c>
       <c r="C691" s="5" t="n"/>
       <c r="D691" s="4" t="n">
         <v>46424</v>
       </c>
       <c r="E691" s="5" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.6944444444444444</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
-          <t>U11 Turnering — Askerhallen</t>
+          <t>U12 Turnering — Schjongshallen</t>
         </is>
       </c>
       <c r="G691" t="inlineStr">
         <is>
-          <t>U11 • Vert: Frisk Asker • Lag: Frisk Asker 1, Jar Grønn, Holmen Hockey Rød, Jar Blå, Jutul Rød, Tønsberg Grå • RVV-ID: rvv-0127</t>
+          <t>U12 • Vert: Ringerike • Lag: Ringerike 1, Ringerike 2, Holmen Hockey Rød, Tønsberg Grå • RVV-ID: rvv-0149</t>
         </is>
       </c>
       <c r="H691" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Schjongshallen</t>
         </is>
       </c>
       <c r="I691" t="inlineStr">
         <is>
-          <t>Jar · Jar Grønn · U11</t>
+          <t>Ringerike · Ringerike 1 · U12</t>
         </is>
       </c>
       <c r="J691" t="inlineStr">
         <is>
-          <t>Jar Grønn</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="K691" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="L691" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="M691" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="N691" t="inlineStr">
         <is>
-          <t>rvv-0127</t>
+          <t>rvv-0149</t>
         </is>
       </c>
     </row>
@@ -41952,58 +41952,58 @@
         <v>46424</v>
       </c>
       <c r="B692" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.625</v>
       </c>
       <c r="C692" s="5" t="n"/>
       <c r="D692" s="4" t="n">
         <v>46424</v>
       </c>
       <c r="E692" s="5" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.6944444444444444</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
-          <t>U11 Turnering — Askerhallen</t>
+          <t>U12 Turnering — Schjongshallen</t>
         </is>
       </c>
       <c r="G692" t="inlineStr">
         <is>
-          <t>U11 • Vert: Frisk Asker • Lag: Frisk Asker 1, Jar Grønn, Holmen Hockey Rød, Jar Blå, Jutul Rød, Tønsberg Grå • RVV-ID: rvv-0127</t>
+          <t>U12 • Vert: Ringerike • Lag: Ringerike 1, Ringerike 2, Holmen Hockey Rød, Tønsberg Grå • RVV-ID: rvv-0149</t>
         </is>
       </c>
       <c r="H692" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Schjongshallen</t>
         </is>
       </c>
       <c r="I692" t="inlineStr">
         <is>
-          <t>Jutul · Jutul Rød · U11</t>
+          <t>Ringerike · Ringerike 2 · U12</t>
         </is>
       </c>
       <c r="J692" t="inlineStr">
         <is>
-          <t>Jutul Rød</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="K692" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="L692" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="M692" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="N692" t="inlineStr">
         <is>
-          <t>rvv-0127</t>
+          <t>rvv-0149</t>
         </is>
       </c>
     </row>
@@ -42012,33 +42012,33 @@
         <v>46424</v>
       </c>
       <c r="B693" s="5" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.625</v>
       </c>
       <c r="C693" s="5" t="n"/>
       <c r="D693" s="4" t="n">
         <v>46424</v>
       </c>
       <c r="E693" s="5" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.6944444444444444</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
-          <t>U11 Turnering — Askerhallen</t>
+          <t>U12 Turnering — Schjongshallen</t>
         </is>
       </c>
       <c r="G693" t="inlineStr">
         <is>
-          <t>U11 • Vert: Frisk Asker • Lag: Frisk Asker 1, Jar Grønn, Holmen Hockey Rød, Jar Blå, Jutul Rød, Tønsberg Grå • RVV-ID: rvv-0127</t>
+          <t>U12 • Vert: Ringerike • Lag: Ringerike 1, Ringerike 2, Holmen Hockey Rød, Tønsberg Grå • RVV-ID: rvv-0149</t>
         </is>
       </c>
       <c r="H693" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Schjongshallen</t>
         </is>
       </c>
       <c r="I693" t="inlineStr">
         <is>
-          <t>Tønsberg · Tønsberg Grå · U11</t>
+          <t>Tønsberg · Tønsberg Grå · U12</t>
         </is>
       </c>
       <c r="J693" t="inlineStr">
@@ -42053,17 +42053,17 @@
       </c>
       <c r="L693" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="M693" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="N693" t="inlineStr">
         <is>
-          <t>rvv-0127</t>
+          <t>rvv-0149</t>
         </is>
       </c>
     </row>
@@ -42079,7 +42079,7 @@
         <v>46425</v>
       </c>
       <c r="E694" s="5" t="n">
-        <v>0.6902777777777778</v>
+        <v>0.6909722222222222</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -42139,7 +42139,7 @@
         <v>46425</v>
       </c>
       <c r="E695" s="5" t="n">
-        <v>0.6902777777777778</v>
+        <v>0.6909722222222222</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -42199,7 +42199,7 @@
         <v>46425</v>
       </c>
       <c r="E696" s="5" t="n">
-        <v>0.6902777777777778</v>
+        <v>0.6909722222222222</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -42259,7 +42259,7 @@
         <v>46425</v>
       </c>
       <c r="E697" s="5" t="n">
-        <v>0.6902777777777778</v>
+        <v>0.6909722222222222</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -42319,7 +42319,7 @@
         <v>46425</v>
       </c>
       <c r="E698" s="5" t="n">
-        <v>0.6902777777777778</v>
+        <v>0.6909722222222222</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -42379,7 +42379,7 @@
         <v>46425</v>
       </c>
       <c r="E699" s="5" t="n">
-        <v>0.6902777777777778</v>
+        <v>0.6909722222222222</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -43528,7 +43528,7 @@
       </c>
       <c r="G718" t="inlineStr">
         <is>
-          <t>JU8 • Vert: Jar • Lag: Frisk Asker, Jar, Jutul Kittens, Skien • RVV-ID: rvv-0139</t>
+          <t>JU8 • Vert: Jar • Lag: Frisk Asker, Wildcats Turkis, Wildcats Rosa, Skien • RVV-ID: rvv-0139</t>
         </is>
       </c>
       <c r="H718" t="inlineStr">
@@ -43588,7 +43588,7 @@
       </c>
       <c r="G719" t="inlineStr">
         <is>
-          <t>JU8 • Vert: Jar • Lag: Frisk Asker, Jar, Jutul Kittens, Skien • RVV-ID: rvv-0139</t>
+          <t>JU8 • Vert: Jar • Lag: Frisk Asker, Wildcats Turkis, Wildcats Rosa, Skien • RVV-ID: rvv-0139</t>
         </is>
       </c>
       <c r="H719" t="inlineStr">
@@ -43598,17 +43598,17 @@
       </c>
       <c r="I719" t="inlineStr">
         <is>
-          <t>Jar · Jar · JU8</t>
+          <t>Skien · Skien · JU8</t>
         </is>
       </c>
       <c r="J719" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="K719" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="L719" t="inlineStr">
@@ -43648,7 +43648,7 @@
       </c>
       <c r="G720" t="inlineStr">
         <is>
-          <t>JU8 • Vert: Jar • Lag: Frisk Asker, Jar, Jutul Kittens, Skien • RVV-ID: rvv-0139</t>
+          <t>JU8 • Vert: Jar • Lag: Frisk Asker, Wildcats Turkis, Wildcats Rosa, Skien • RVV-ID: rvv-0139</t>
         </is>
       </c>
       <c r="H720" t="inlineStr">
@@ -43658,12 +43658,12 @@
       </c>
       <c r="I720" t="inlineStr">
         <is>
-          <t>Jutul · Jutul Kittens · JU8</t>
+          <t>Jutul · Wildcats Rosa · JU8</t>
         </is>
       </c>
       <c r="J720" t="inlineStr">
         <is>
-          <t>Jutul Kittens</t>
+          <t>Wildcats Rosa</t>
         </is>
       </c>
       <c r="K720" t="inlineStr">
@@ -43708,7 +43708,7 @@
       </c>
       <c r="G721" t="inlineStr">
         <is>
-          <t>JU8 • Vert: Jar • Lag: Frisk Asker, Jar, Jutul Kittens, Skien • RVV-ID: rvv-0139</t>
+          <t>JU8 • Vert: Jar • Lag: Frisk Asker, Wildcats Turkis, Wildcats Rosa, Skien • RVV-ID: rvv-0139</t>
         </is>
       </c>
       <c r="H721" t="inlineStr">
@@ -43718,17 +43718,17 @@
       </c>
       <c r="I721" t="inlineStr">
         <is>
-          <t>Skien · Skien · JU8</t>
+          <t>Jar · Wildcats Turkis · JU8</t>
         </is>
       </c>
       <c r="J721" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Wildcats Turkis</t>
         </is>
       </c>
       <c r="K721" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="L721" t="inlineStr">
@@ -46939,7 +46939,7 @@
         <v>46438</v>
       </c>
       <c r="E775" s="5" t="n">
-        <v>0.6493055555555556</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -46999,7 +46999,7 @@
         <v>46438</v>
       </c>
       <c r="E776" s="5" t="n">
-        <v>0.6493055555555556</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -47059,7 +47059,7 @@
         <v>46438</v>
       </c>
       <c r="E777" s="5" t="n">
-        <v>0.6493055555555556</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -47119,7 +47119,7 @@
         <v>46438</v>
       </c>
       <c r="E778" s="5" t="n">
-        <v>0.6493055555555556</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -47179,7 +47179,7 @@
         <v>46438</v>
       </c>
       <c r="E779" s="5" t="n">
-        <v>0.6493055555555556</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -47239,7 +47239,7 @@
         <v>46438</v>
       </c>
       <c r="E780" s="5" t="n">
-        <v>0.6493055555555556</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -47299,7 +47299,7 @@
         <v>46438</v>
       </c>
       <c r="E781" s="5" t="n">
-        <v>0.6493055555555556</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -47359,7 +47359,7 @@
         <v>46438</v>
       </c>
       <c r="E782" s="5" t="n">
-        <v>0.6493055555555556</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -47419,7 +47419,7 @@
         <v>46438</v>
       </c>
       <c r="E783" s="5" t="n">
-        <v>0.6805555555555556</v>
+        <v>0.7013888888888888</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -47479,7 +47479,7 @@
         <v>46438</v>
       </c>
       <c r="E784" s="5" t="n">
-        <v>0.6805555555555556</v>
+        <v>0.7013888888888888</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -47539,7 +47539,7 @@
         <v>46438</v>
       </c>
       <c r="E785" s="5" t="n">
-        <v>0.6805555555555556</v>
+        <v>0.7013888888888888</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -47599,7 +47599,7 @@
         <v>46438</v>
       </c>
       <c r="E786" s="5" t="n">
-        <v>0.6805555555555556</v>
+        <v>0.7013888888888888</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -47659,7 +47659,7 @@
         <v>46438</v>
       </c>
       <c r="E787" s="5" t="n">
-        <v>0.6805555555555556</v>
+        <v>0.7013888888888888</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -47719,7 +47719,7 @@
         <v>46438</v>
       </c>
       <c r="E788" s="5" t="n">
-        <v>0.6805555555555556</v>
+        <v>0.7013888888888888</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -49699,7 +49699,7 @@
         <v>46439</v>
       </c>
       <c r="E821" s="5" t="n">
-        <v>0.5347222222222222</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -49759,7 +49759,7 @@
         <v>46439</v>
       </c>
       <c r="E822" s="5" t="n">
-        <v>0.5347222222222222</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -49819,7 +49819,7 @@
         <v>46439</v>
       </c>
       <c r="E823" s="5" t="n">
-        <v>0.5347222222222222</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -49879,7 +49879,7 @@
         <v>46439</v>
       </c>
       <c r="E824" s="5" t="n">
-        <v>0.5347222222222222</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -49939,7 +49939,7 @@
         <v>46439</v>
       </c>
       <c r="E825" s="5" t="n">
-        <v>0.5347222222222222</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -49999,7 +49999,7 @@
         <v>46439</v>
       </c>
       <c r="E826" s="5" t="n">
-        <v>0.5347222222222222</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -52519,7 +52519,7 @@
         <v>46452</v>
       </c>
       <c r="E868" s="5" t="n">
-        <v>0.8263888888888888</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -52579,7 +52579,7 @@
         <v>46452</v>
       </c>
       <c r="E869" s="5" t="n">
-        <v>0.8263888888888888</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -52639,7 +52639,7 @@
         <v>46452</v>
       </c>
       <c r="E870" s="5" t="n">
-        <v>0.8263888888888888</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -52699,7 +52699,7 @@
         <v>46452</v>
       </c>
       <c r="E871" s="5" t="n">
-        <v>0.8263888888888888</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -52759,7 +52759,7 @@
         <v>46452</v>
       </c>
       <c r="E872" s="5" t="n">
-        <v>0.8263888888888888</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -52819,7 +52819,7 @@
         <v>46452</v>
       </c>
       <c r="E873" s="5" t="n">
-        <v>0.8263888888888888</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -53119,7 +53119,7 @@
         <v>46453</v>
       </c>
       <c r="E878" s="5" t="n">
-        <v>0.5763888888888888</v>
+        <v>0.5972222222222222</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -53179,7 +53179,7 @@
         <v>46453</v>
       </c>
       <c r="E879" s="5" t="n">
-        <v>0.5763888888888888</v>
+        <v>0.5972222222222222</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -53239,7 +53239,7 @@
         <v>46453</v>
       </c>
       <c r="E880" s="5" t="n">
-        <v>0.5763888888888888</v>
+        <v>0.5972222222222222</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -53299,7 +53299,7 @@
         <v>46453</v>
       </c>
       <c r="E881" s="5" t="n">
-        <v>0.5763888888888888</v>
+        <v>0.5972222222222222</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -53359,7 +53359,7 @@
         <v>46453</v>
       </c>
       <c r="E882" s="5" t="n">
-        <v>0.5763888888888888</v>
+        <v>0.5972222222222222</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -53419,7 +53419,7 @@
         <v>46453</v>
       </c>
       <c r="E883" s="5" t="n">
-        <v>0.5763888888888888</v>
+        <v>0.5972222222222222</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -53952,14 +53952,14 @@
         <v>46453</v>
       </c>
       <c r="B892" s="5" t="n">
-        <v>0.625</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="C892" s="5" t="n"/>
       <c r="D892" s="4" t="n">
         <v>46453</v>
       </c>
       <c r="E892" s="5" t="n">
-        <v>0.7013888888888888</v>
+        <v>0.7430555555555556</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -54012,14 +54012,14 @@
         <v>46453</v>
       </c>
       <c r="B893" s="5" t="n">
-        <v>0.625</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="C893" s="5" t="n"/>
       <c r="D893" s="4" t="n">
         <v>46453</v>
       </c>
       <c r="E893" s="5" t="n">
-        <v>0.7013888888888888</v>
+        <v>0.7430555555555556</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -54072,14 +54072,14 @@
         <v>46453</v>
       </c>
       <c r="B894" s="5" t="n">
-        <v>0.625</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="C894" s="5" t="n"/>
       <c r="D894" s="4" t="n">
         <v>46453</v>
       </c>
       <c r="E894" s="5" t="n">
-        <v>0.7013888888888888</v>
+        <v>0.7430555555555556</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -54132,14 +54132,14 @@
         <v>46453</v>
       </c>
       <c r="B895" s="5" t="n">
-        <v>0.625</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="C895" s="5" t="n"/>
       <c r="D895" s="4" t="n">
         <v>46453</v>
       </c>
       <c r="E895" s="5" t="n">
-        <v>0.7013888888888888</v>
+        <v>0.7430555555555556</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -54192,14 +54192,14 @@
         <v>46453</v>
       </c>
       <c r="B896" s="5" t="n">
-        <v>0.625</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="C896" s="5" t="n"/>
       <c r="D896" s="4" t="n">
         <v>46453</v>
       </c>
       <c r="E896" s="5" t="n">
-        <v>0.7013888888888888</v>
+        <v>0.7430555555555556</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -54252,14 +54252,14 @@
         <v>46453</v>
       </c>
       <c r="B897" s="5" t="n">
-        <v>0.625</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="C897" s="5" t="n"/>
       <c r="D897" s="4" t="n">
         <v>46453</v>
       </c>
       <c r="E897" s="5" t="n">
-        <v>0.7013888888888888</v>
+        <v>0.7430555555555556</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -55039,7 +55039,7 @@
         <v>46459</v>
       </c>
       <c r="E910" s="5" t="n">
-        <v>0.625</v>
+        <v>0.5972222222222222</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -55048,7 +55048,7 @@
       </c>
       <c r="G910" t="inlineStr">
         <is>
-          <t>JU8 • Vert: Frisk Asker • Lag: Frisk Asker, Jar, Jutul Kittens, Skien • RVV-ID: rvv-0179</t>
+          <t>JU8 • Vert: Frisk Asker • Lag: Frisk Asker, Wildcats Turkis, Wildcats Rosa, Skien • RVV-ID: rvv-0179</t>
         </is>
       </c>
       <c r="H910" t="inlineStr">
@@ -55099,7 +55099,7 @@
         <v>46459</v>
       </c>
       <c r="E911" s="5" t="n">
-        <v>0.625</v>
+        <v>0.5972222222222222</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -55108,7 +55108,7 @@
       </c>
       <c r="G911" t="inlineStr">
         <is>
-          <t>JU8 • Vert: Frisk Asker • Lag: Frisk Asker, Jar, Jutul Kittens, Skien • RVV-ID: rvv-0179</t>
+          <t>JU8 • Vert: Frisk Asker • Lag: Frisk Asker, Wildcats Turkis, Wildcats Rosa, Skien • RVV-ID: rvv-0179</t>
         </is>
       </c>
       <c r="H911" t="inlineStr">
@@ -55118,17 +55118,17 @@
       </c>
       <c r="I911" t="inlineStr">
         <is>
-          <t>Jar · Jar · JU8</t>
+          <t>Skien · Skien · JU8</t>
         </is>
       </c>
       <c r="J911" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="K911" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="L911" t="inlineStr">
@@ -55159,7 +55159,7 @@
         <v>46459</v>
       </c>
       <c r="E912" s="5" t="n">
-        <v>0.625</v>
+        <v>0.5972222222222222</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -55168,7 +55168,7 @@
       </c>
       <c r="G912" t="inlineStr">
         <is>
-          <t>JU8 • Vert: Frisk Asker • Lag: Frisk Asker, Jar, Jutul Kittens, Skien • RVV-ID: rvv-0179</t>
+          <t>JU8 • Vert: Frisk Asker • Lag: Frisk Asker, Wildcats Turkis, Wildcats Rosa, Skien • RVV-ID: rvv-0179</t>
         </is>
       </c>
       <c r="H912" t="inlineStr">
@@ -55178,12 +55178,12 @@
       </c>
       <c r="I912" t="inlineStr">
         <is>
-          <t>Jutul · Jutul Kittens · JU8</t>
+          <t>Jutul · Wildcats Rosa · JU8</t>
         </is>
       </c>
       <c r="J912" t="inlineStr">
         <is>
-          <t>Jutul Kittens</t>
+          <t>Wildcats Rosa</t>
         </is>
       </c>
       <c r="K912" t="inlineStr">
@@ -55219,7 +55219,7 @@
         <v>46459</v>
       </c>
       <c r="E913" s="5" t="n">
-        <v>0.625</v>
+        <v>0.5972222222222222</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -55228,7 +55228,7 @@
       </c>
       <c r="G913" t="inlineStr">
         <is>
-          <t>JU8 • Vert: Frisk Asker • Lag: Frisk Asker, Jar, Jutul Kittens, Skien • RVV-ID: rvv-0179</t>
+          <t>JU8 • Vert: Frisk Asker • Lag: Frisk Asker, Wildcats Turkis, Wildcats Rosa, Skien • RVV-ID: rvv-0179</t>
         </is>
       </c>
       <c r="H913" t="inlineStr">
@@ -55238,17 +55238,17 @@
       </c>
       <c r="I913" t="inlineStr">
         <is>
-          <t>Skien · Skien · JU8</t>
+          <t>Jar · Wildcats Turkis · JU8</t>
         </is>
       </c>
       <c r="J913" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Wildcats Turkis</t>
         </is>
       </c>
       <c r="K913" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="L913" t="inlineStr">
@@ -55512,7 +55512,7 @@
         <v>46459</v>
       </c>
       <c r="B918" s="5" t="n">
-        <v>0.625</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="C918" s="5" t="n"/>
       <c r="D918" s="4" t="n">
@@ -55572,7 +55572,7 @@
         <v>46459</v>
       </c>
       <c r="B919" s="5" t="n">
-        <v>0.625</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="C919" s="5" t="n"/>
       <c r="D919" s="4" t="n">
@@ -55632,7 +55632,7 @@
         <v>46459</v>
       </c>
       <c r="B920" s="5" t="n">
-        <v>0.625</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="C920" s="5" t="n"/>
       <c r="D920" s="4" t="n">
@@ -55692,7 +55692,7 @@
         <v>46459</v>
       </c>
       <c r="B921" s="5" t="n">
-        <v>0.625</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="C921" s="5" t="n"/>
       <c r="D921" s="4" t="n">
@@ -55752,7 +55752,7 @@
         <v>46459</v>
       </c>
       <c r="B922" s="5" t="n">
-        <v>0.625</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="C922" s="5" t="n"/>
       <c r="D922" s="4" t="n">
@@ -55812,7 +55812,7 @@
         <v>46459</v>
       </c>
       <c r="B923" s="5" t="n">
-        <v>0.625</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="C923" s="5" t="n"/>
       <c r="D923" s="4" t="n">
@@ -59379,7 +59379,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Jutul Kittens, Skien</t>
+          <t>Frisk Asker, Wildcats Turkis, Wildcats Rosa, Skien</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -59515,7 +59515,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -59567,7 +59567,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -59879,7 +59879,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -59983,7 +59983,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -60243,7 +60243,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -60295,7 +60295,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -60367,7 +60367,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Jutul Kittens, Ringerike 1, Skien</t>
+          <t>Frisk Asker, Wildcats Turkis, Wildcats Rosa, Ringerike 1, Skien</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -60602,7 +60602,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -60966,7 +60966,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -61221,7 +61221,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -61330,7 +61330,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -61402,7 +61402,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Jutul Kittens, Skien</t>
+          <t>Frisk Asker, Wildcats Turkis, Wildcats Rosa, Skien</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -61585,12 +61585,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -61642,7 +61642,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -61694,7 +61694,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -62318,7 +62318,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -62786,7 +62786,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -63326,7 +63326,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Jutul Kittens, Skien</t>
+          <t>Frisk Asker, Wildcats Turkis, Wildcats Rosa, Skien</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -63410,7 +63410,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -63613,12 +63613,12 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -63774,7 +63774,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -63930,7 +63930,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -64029,7 +64029,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -64086,7 +64086,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -64190,7 +64190,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -64242,7 +64242,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -64398,7 +64398,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -64814,7 +64814,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -64970,7 +64970,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -65121,12 +65121,12 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -65225,7 +65225,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -65282,7 +65282,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -65510,7 +65510,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Jutul Kittens, Skien</t>
+          <t>Frisk Asker, Wildcats Turkis, Wildcats Rosa, Skien</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -65906,7 +65906,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -66166,7 +66166,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -66530,7 +66530,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -66686,7 +66686,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -66998,7 +66998,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -67149,12 +67149,12 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -67466,7 +67466,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -67486,7 +67486,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Jutul Kittens, Skien</t>
+          <t>Frisk Asker, Wildcats Turkis, Wildcats Rosa, Skien</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -67513,7 +67513,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -67898,7 +67898,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>f3f96bf6f522111c6518bbf4aac3ba1c51f5c8ede5372c3b411f50db197754cd</t>
+          <t>0757a7674f631f5126e292fcde0a750aa1ff2a07871c85502797310c2a7640c7</t>
         </is>
       </c>
     </row>
